--- a/AutoPaymentScheduleFile/TotalSheet/排款计划参照数据原表.xlsx
+++ b/AutoPaymentScheduleFile/TotalSheet/排款计划参照数据原表.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="14220" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="14720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -785,9 +786,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -830,6 +828,9 @@
       <protection locked="1" hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1383,17 +1384,18 @@
   <dimension ref="A1:BS57"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col width="54" customWidth="1" style="5" min="1" max="1"/>
-    <col width="15.125" customWidth="1" style="5" min="2" max="2"/>
-    <col width="11.125" customWidth="1" style="5" min="3" max="3"/>
-    <col width="10.125" customWidth="1" style="5" min="4" max="4"/>
-    <col width="13.125" customWidth="1" style="5" min="5" max="6"/>
-    <col width="7.25" customWidth="1" style="5" min="7" max="7"/>
+    <col width="54" customWidth="1" style="4" min="1" max="1"/>
+    <col width="15.125" customWidth="1" style="4" min="2" max="2"/>
+    <col width="11.125" customWidth="1" style="4" min="3" max="3"/>
+    <col width="10.125" customWidth="1" style="4" min="4" max="4"/>
+    <col width="13.125" customWidth="1" style="4" min="5" max="6"/>
+    <col width="7.25" customWidth="1" style="4" min="7" max="7"/>
     <col width="15.875" customWidth="1" style="52" min="8" max="8"/>
-    <col width="15.75" customWidth="1" style="5" min="9" max="9"/>
-    <col width="8.50961538461539" customWidth="1" style="5" min="10" max="11"/>
-    <col width="14.75" customWidth="1" style="5" min="12" max="12"/>
-    <col width="16.1923076923077" customWidth="1" style="52" min="13" max="14"/>
+    <col width="15.75" customWidth="1" style="4" min="9" max="9"/>
+    <col width="8.50961538461539" customWidth="1" style="4" min="10" max="11"/>
+    <col width="29.6923076923077" customWidth="1" style="4" min="12" max="12"/>
+    <col width="29.6153846153846" customWidth="1" style="52" min="13" max="13"/>
+    <col width="16.1923076923077" customWidth="1" style="52" min="14" max="14"/>
     <col width="14.5096153846154" customWidth="1" style="52" min="15" max="15"/>
     <col hidden="1" width="9" customWidth="1" style="52" min="16" max="16"/>
     <col width="25" customWidth="1" style="52" min="17" max="17"/>
@@ -1402,43 +1404,43 @@
     <col width="23.5480769230769" customWidth="1" style="52" min="20" max="20"/>
     <col width="18.375" customWidth="1" style="52" min="21" max="21"/>
     <col width="22.5961538461538" customWidth="1" style="52" min="22" max="22"/>
-    <col width="22.125" customWidth="1" style="52" min="23" max="23"/>
+    <col width="28.3076923076923" customWidth="1" style="52" min="23" max="23"/>
     <col width="14.25" customWidth="1" style="52" min="24" max="24"/>
-    <col width="24.375" customWidth="1" style="5" min="25" max="25"/>
-    <col width="20.5096153846154" customWidth="1" style="5" min="26" max="26"/>
-    <col width="16" customWidth="1" style="5" min="27" max="31"/>
-    <col width="16.375" customWidth="1" style="5" min="32" max="32"/>
-    <col width="16" customWidth="1" style="5" min="33" max="35"/>
-    <col width="15.625" customWidth="1" style="5" min="36" max="37"/>
-    <col width="16" customWidth="1" style="5" min="38" max="53"/>
-    <col hidden="1" width="12.125" customWidth="1" style="5" min="54" max="54"/>
-    <col hidden="1" width="17.125" customWidth="1" style="5" min="55" max="55"/>
-    <col hidden="1" width="18.25" customWidth="1" style="5" min="56" max="56"/>
-    <col hidden="1" width="18.75" customWidth="1" style="5" min="57" max="57"/>
-    <col width="9.625" customWidth="1" style="5" min="58" max="58"/>
-    <col width="17.125" customWidth="1" style="5" min="59" max="59"/>
-    <col width="16" customWidth="1" style="5" min="60" max="64"/>
-    <col width="18.5096153846154" customWidth="1" style="5" min="65" max="65"/>
-    <col width="12" customWidth="1" style="5" min="66" max="69"/>
-    <col width="12.7980769230769" customWidth="1" style="5" min="70" max="70"/>
-    <col width="15.125" customWidth="1" style="5" min="71" max="71"/>
-    <col width="9" customWidth="1" style="5" min="72" max="16384"/>
+    <col width="24.375" customWidth="1" style="4" min="25" max="25"/>
+    <col width="20.5096153846154" customWidth="1" style="4" min="26" max="26"/>
+    <col width="16" customWidth="1" style="4" min="27" max="31"/>
+    <col width="16.375" customWidth="1" style="4" min="32" max="32"/>
+    <col width="16" customWidth="1" style="4" min="33" max="35"/>
+    <col width="15.625" customWidth="1" style="4" min="36" max="37"/>
+    <col width="16" customWidth="1" style="4" min="38" max="53"/>
+    <col hidden="1" width="12.125" customWidth="1" style="4" min="54" max="54"/>
+    <col hidden="1" width="17.125" customWidth="1" style="4" min="55" max="55"/>
+    <col hidden="1" width="18.25" customWidth="1" style="4" min="56" max="56"/>
+    <col hidden="1" width="18.75" customWidth="1" style="4" min="57" max="57"/>
+    <col width="9.625" customWidth="1" style="4" min="58" max="58"/>
+    <col width="17.125" customWidth="1" style="4" min="59" max="59"/>
+    <col width="16" customWidth="1" style="4" min="60" max="64"/>
+    <col width="18.5096153846154" customWidth="1" style="4" min="65" max="65"/>
+    <col width="12" customWidth="1" style="4" min="66" max="69"/>
+    <col width="12.7980769230769" customWidth="1" style="4" min="70" max="70"/>
+    <col width="15.125" customWidth="1" style="4" min="71" max="71"/>
+    <col width="9" customWidth="1" style="4" min="72" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customFormat="1" customHeight="1" s="5">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="20" customFormat="1" customHeight="1" s="4">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>截止20260331已到票应付账龄情况-分主体不分部门</t>
         </is>
       </c>
-      <c r="B1" s="9" t="n"/>
-      <c r="C1" s="9" t="n"/>
-      <c r="D1" s="9" t="n"/>
-      <c r="E1" s="9" t="n"/>
-      <c r="F1" s="9" t="n"/>
-      <c r="G1" s="9" t="n"/>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
       <c r="H1" s="53" t="n"/>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>备用筛选字段</t>
         </is>
@@ -1466,8 +1468,8 @@
       <c r="V1" s="54" t="n"/>
       <c r="W1" s="54" t="n"/>
       <c r="X1" s="55" t="n"/>
-      <c r="Y1" s="9" t="n"/>
-      <c r="Z1" s="13" t="inlineStr">
+      <c r="Y1" s="8" t="n"/>
+      <c r="Z1" s="12" t="inlineStr">
         <is>
           <t>应付账龄</t>
         </is>
@@ -1484,9 +1486,9 @@
       <c r="AJ1" s="54" t="n"/>
       <c r="AK1" s="54" t="n"/>
       <c r="AL1" s="55" t="n"/>
-      <c r="AM1" s="13" t="n"/>
-      <c r="AN1" s="13" t="n"/>
-      <c r="AO1" s="14" t="inlineStr">
+      <c r="AM1" s="12" t="n"/>
+      <c r="AN1" s="12" t="n"/>
+      <c r="AO1" s="13" t="inlineStr">
         <is>
           <t>每月采购额</t>
         </is>
@@ -1503,7 +1505,7 @@
       <c r="AY1" s="57" t="n"/>
       <c r="AZ1" s="57" t="n"/>
       <c r="BA1" s="58" t="n"/>
-      <c r="BB1" s="15" t="inlineStr">
+      <c r="BB1" s="14" t="inlineStr">
         <is>
           <t>采购部另外需要数据</t>
         </is>
@@ -1511,7 +1513,7 @@
       <c r="BC1" s="54" t="n"/>
       <c r="BD1" s="54" t="n"/>
       <c r="BE1" s="55" t="n"/>
-      <c r="BF1" s="15" t="inlineStr">
+      <c r="BF1" s="14" t="inlineStr">
         <is>
           <t>日报表数据</t>
         </is>
@@ -1523,7 +1525,7 @@
       <c r="BK1" s="54" t="n"/>
       <c r="BL1" s="54" t="n"/>
       <c r="BM1" s="55" t="n"/>
-      <c r="BN1" s="11" t="inlineStr">
+      <c r="BN1" s="10" t="inlineStr">
         <is>
           <t>补充数据</t>
         </is>
@@ -1534,38 +1536,38 @@
       <c r="BR1" s="54" t="n"/>
       <c r="BS1" s="55" t="n"/>
     </row>
-    <row r="2" ht="141" customFormat="1" customHeight="1" s="6">
-      <c r="A2" s="16" t="inlineStr">
+    <row r="2" ht="141" customFormat="1" customHeight="1" s="5">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>主体</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>客商编码</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>供应商名称</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>付款银行优先级（中国银行、易信、商承）</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>付款优先级（严格按账期-0级，加多1个月-1级，其他-2级且优先处理账龄长的）</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>付款截止日期</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="G2" s="16" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
@@ -1575,27 +1577,27 @@
           <t>1-3月采购额</t>
         </is>
       </c>
-      <c r="I2" s="17" t="inlineStr">
+      <c r="I2" s="16" t="inlineStr">
         <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="J2" s="17" t="inlineStr">
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>合同账期</t>
         </is>
       </c>
-      <c r="K2" s="17" t="inlineStr">
+      <c r="K2" s="16" t="inlineStr">
         <is>
           <t>协议账期</t>
         </is>
       </c>
-      <c r="L2" s="17" t="inlineStr">
+      <c r="L2" s="16" t="inlineStr">
         <is>
           <t>收款方式</t>
         </is>
       </c>
-      <c r="M2" s="17" t="inlineStr">
+      <c r="M2" s="16" t="inlineStr">
         <is>
           <t>收款方式备注</t>
         </is>
@@ -1722,7 +1724,7 @@
       </c>
       <c r="AL2" s="25" t="inlineStr">
         <is>
-          <t>1年以上</t>
+          <t>13个月以上</t>
         </is>
       </c>
       <c r="AM2" s="25" t="inlineStr">
@@ -1891,19 +1893,19 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customFormat="1" customHeight="1" s="6">
-      <c r="A3" s="16" t="n"/>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="17" t="n"/>
-      <c r="D3" s="17" t="n"/>
-      <c r="E3" s="17" t="n"/>
-      <c r="F3" s="17" t="n"/>
-      <c r="G3" s="17" t="n"/>
+    <row r="3" ht="18" customFormat="1" customHeight="1" s="5">
+      <c r="A3" s="15" t="n"/>
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="16" t="n"/>
+      <c r="D3" s="16" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="16" t="n"/>
+      <c r="G3" s="16" t="n"/>
       <c r="H3" s="59" t="n"/>
-      <c r="I3" s="17" t="n"/>
-      <c r="J3" s="17" t="n"/>
-      <c r="K3" s="17" t="n"/>
-      <c r="L3" s="17" t="n"/>
+      <c r="I3" s="16" t="n"/>
+      <c r="J3" s="16" t="n"/>
+      <c r="K3" s="16" t="n"/>
+      <c r="L3" s="16" t="n"/>
       <c r="M3" s="61" t="n"/>
       <c r="N3" s="61" t="n"/>
       <c r="O3" s="61" t="n"/>
@@ -1992,19 +1994,19 @@
       <c r="BR3" s="68" t="n"/>
       <c r="BS3" s="68" t="n"/>
     </row>
-    <row r="4" ht="19" customFormat="1" customHeight="1" s="6">
-      <c r="A4" s="16" t="n"/>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="17" t="n"/>
-      <c r="D4" s="17" t="n"/>
-      <c r="E4" s="17" t="n"/>
-      <c r="F4" s="17" t="n"/>
-      <c r="G4" s="17" t="n"/>
+    <row r="4" ht="19" customFormat="1" customHeight="1" s="5">
+      <c r="A4" s="15" t="n"/>
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="16" t="n"/>
+      <c r="G4" s="16" t="n"/>
       <c r="H4" s="59" t="n"/>
-      <c r="I4" s="17" t="n"/>
-      <c r="J4" s="17" t="n"/>
-      <c r="K4" s="17" t="n"/>
-      <c r="L4" s="17" t="n"/>
+      <c r="I4" s="16" t="n"/>
+      <c r="J4" s="16" t="n"/>
+      <c r="K4" s="16" t="n"/>
+      <c r="L4" s="16" t="n"/>
       <c r="M4" s="61" t="n"/>
       <c r="N4" s="61" t="n"/>
       <c r="O4" s="61" t="n"/>
@@ -2081,19 +2083,19 @@
       <c r="BR4" s="68" t="n"/>
       <c r="BS4" s="68" t="n"/>
     </row>
-    <row r="5" ht="17.6" customFormat="1" customHeight="1" s="6">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="17" t="n"/>
-      <c r="G5" s="17" t="n"/>
+    <row r="5" ht="17.6" customFormat="1" customHeight="1" s="5">
+      <c r="A5" s="15" t="n"/>
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="16" t="n"/>
+      <c r="G5" s="16" t="n"/>
       <c r="H5" s="59" t="n"/>
-      <c r="I5" s="17" t="n"/>
-      <c r="J5" s="17" t="n"/>
-      <c r="K5" s="17" t="n"/>
-      <c r="L5" s="17" t="n"/>
+      <c r="I5" s="16" t="n"/>
+      <c r="J5" s="16" t="n"/>
+      <c r="K5" s="16" t="n"/>
+      <c r="L5" s="16" t="n"/>
       <c r="M5" s="61" t="n"/>
       <c r="N5" s="61" t="n"/>
       <c r="O5" s="61" t="n"/>
@@ -2104,13 +2106,13 @@
         </is>
       </c>
       <c r="R5" s="59" t="n">
-        <v>9450693.01</v>
+        <v>785802.8800000027</v>
       </c>
       <c r="S5" s="59" t="n">
-        <v>14598828.95</v>
+        <v>3254322.640000001</v>
       </c>
       <c r="T5" s="59" t="n">
-        <v>5000000</v>
+        <v>3889773.6</v>
       </c>
       <c r="U5" s="59" t="n">
         <v>8000000</v>
@@ -2119,7 +2121,7 @@
         <v>5220000</v>
       </c>
       <c r="W5" s="59" t="n">
-        <v>2820000</v>
+        <v>2812800</v>
       </c>
       <c r="X5" s="59" t="n"/>
       <c r="Y5" s="69" t="n"/>
@@ -2170,19 +2172,19 @@
       <c r="BR5" s="68" t="n"/>
       <c r="BS5" s="68" t="n"/>
     </row>
-    <row r="6" ht="17.6" customFormat="1" customHeight="1" s="6">
-      <c r="A6" s="16" t="n"/>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="17" t="n"/>
-      <c r="D6" s="17" t="n"/>
-      <c r="E6" s="17" t="n"/>
-      <c r="F6" s="17" t="n"/>
-      <c r="G6" s="17" t="n"/>
+    <row r="6" ht="17.6" customFormat="1" customHeight="1" s="5">
+      <c r="A6" s="15" t="n"/>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="16" t="n"/>
+      <c r="D6" s="16" t="n"/>
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="16" t="n"/>
+      <c r="G6" s="16" t="n"/>
       <c r="H6" s="59" t="n"/>
-      <c r="I6" s="17" t="n"/>
-      <c r="J6" s="17" t="n"/>
-      <c r="K6" s="17" t="n"/>
-      <c r="L6" s="17" t="n"/>
+      <c r="I6" s="16" t="n"/>
+      <c r="J6" s="16" t="n"/>
+      <c r="K6" s="16" t="n"/>
+      <c r="L6" s="16" t="n"/>
       <c r="M6" s="61" t="n"/>
       <c r="N6" s="61" t="n"/>
       <c r="O6" s="61" t="n"/>
@@ -2259,19 +2261,19 @@
       <c r="BR6" s="68" t="n"/>
       <c r="BS6" s="68" t="n"/>
     </row>
-    <row r="7" ht="106" customFormat="1" customHeight="1" s="6">
-      <c r="A7" s="16" t="n"/>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="17" t="n"/>
-      <c r="D7" s="17" t="n"/>
-      <c r="E7" s="17" t="n"/>
-      <c r="F7" s="17" t="n"/>
-      <c r="G7" s="17" t="n"/>
+    <row r="7" ht="106" customFormat="1" customHeight="1" s="5">
+      <c r="A7" s="15" t="n"/>
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="16" t="n"/>
       <c r="H7" s="59" t="n"/>
-      <c r="I7" s="17" t="n"/>
-      <c r="J7" s="17" t="n"/>
-      <c r="K7" s="17" t="n"/>
-      <c r="L7" s="17" t="n"/>
+      <c r="I7" s="16" t="n"/>
+      <c r="J7" s="16" t="n"/>
+      <c r="K7" s="16" t="n"/>
+      <c r="L7" s="16" t="n"/>
       <c r="M7" s="61" t="n"/>
       <c r="N7" s="61" t="n"/>
       <c r="O7" s="61" t="n"/>
@@ -2360,19 +2362,19 @@
       <c r="BR7" s="68" t="n"/>
       <c r="BS7" s="68" t="n"/>
     </row>
-    <row r="8" ht="36" customFormat="1" customHeight="1" s="6">
-      <c r="A8" s="16" t="n"/>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="17" t="n"/>
-      <c r="D8" s="17" t="n"/>
-      <c r="E8" s="17" t="n"/>
-      <c r="F8" s="17" t="n"/>
-      <c r="G8" s="17" t="n"/>
+    <row r="8" ht="36" customFormat="1" customHeight="1" s="5">
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="16" t="n"/>
       <c r="H8" s="59" t="n"/>
-      <c r="I8" s="17" t="n"/>
-      <c r="J8" s="17" t="n"/>
-      <c r="K8" s="17" t="n"/>
-      <c r="L8" s="17" t="n"/>
+      <c r="I8" s="16" t="n"/>
+      <c r="J8" s="16" t="n"/>
+      <c r="K8" s="16" t="n"/>
+      <c r="L8" s="16" t="n"/>
       <c r="M8" s="61" t="n"/>
       <c r="N8" s="61" t="n"/>
       <c r="O8" s="61" t="n"/>
@@ -2461,7 +2463,7 @@
       <c r="BR8" s="68" t="n"/>
       <c r="BS8" s="68" t="n"/>
     </row>
-    <row r="9" customFormat="1" s="5">
+    <row r="9" customFormat="1" s="4">
       <c r="A9" s="48" t="inlineStr">
         <is>
           <t>安徽集泰新材料有限公司</t>
@@ -2672,7 +2674,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" customFormat="1" s="7">
+    <row r="10" customFormat="1" s="6">
       <c r="A10" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -2879,7 +2881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="1" s="5">
+    <row r="11" customFormat="1" s="4">
       <c r="A11" s="48" t="inlineStr">
         <is>
           <t>安庆诚泰新材料有限公司</t>
@@ -2927,12 +2929,16 @@
         </is>
       </c>
       <c r="M11" s="71" t="n"/>
-      <c r="N11" s="71" t="n"/>
+      <c r="N11" s="71" t="n">
+        <v>244496</v>
+      </c>
       <c r="O11" s="71" t="n"/>
       <c r="P11" s="71" t="n"/>
       <c r="Q11" s="71" t="n"/>
       <c r="R11" s="71" t="n"/>
-      <c r="S11" s="71" t="n"/>
+      <c r="S11" s="71" t="n">
+        <v>244496</v>
+      </c>
       <c r="T11" s="71" t="n"/>
       <c r="U11" s="71" t="n"/>
       <c r="V11" s="71" t="n"/>
@@ -3082,7 +3088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="1" s="7">
+    <row r="12" customFormat="1" s="6">
       <c r="A12" s="49" t="inlineStr">
         <is>
           <t>安庆诚泰新材料有限公司</t>
@@ -3130,12 +3136,16 @@
         </is>
       </c>
       <c r="M12" s="72" t="n"/>
-      <c r="N12" s="72" t="n"/>
+      <c r="N12" s="72" t="n">
+        <v>56635</v>
+      </c>
       <c r="O12" s="72" t="n"/>
       <c r="P12" s="72" t="n"/>
       <c r="Q12" s="72" t="n"/>
       <c r="R12" s="72" t="n"/>
-      <c r="S12" s="72" t="n"/>
+      <c r="S12" s="72" t="n">
+        <v>56635</v>
+      </c>
       <c r="T12" s="72" t="n"/>
       <c r="U12" s="72" t="n"/>
       <c r="V12" s="72" t="n"/>
@@ -3285,7 +3295,7 @@
         <v>46000</v>
       </c>
     </row>
-    <row r="13" customFormat="1" s="5">
+    <row r="13" customFormat="1" s="4">
       <c r="A13" s="48" t="inlineStr">
         <is>
           <t>安庆诚泰新材料有限公司</t>
@@ -3488,7 +3498,7 @@
         <v>232320</v>
       </c>
     </row>
-    <row r="14" customFormat="1" s="5">
+    <row r="14" customFormat="1" s="4">
       <c r="A14" s="48" t="inlineStr">
         <is>
           <t>安庆诚泰新材料有限公司</t>
@@ -3540,12 +3550,16 @@
           <t>商承不能只给6个月以上的</t>
         </is>
       </c>
-      <c r="N14" s="71" t="n"/>
+      <c r="N14" s="71" t="n">
+        <v>467695.46</v>
+      </c>
       <c r="O14" s="71" t="n"/>
       <c r="P14" s="71" t="n"/>
       <c r="Q14" s="71" t="n"/>
       <c r="R14" s="71" t="n"/>
-      <c r="S14" s="71" t="n"/>
+      <c r="S14" s="71" t="n">
+        <v>467695.46</v>
+      </c>
       <c r="T14" s="71" t="n"/>
       <c r="U14" s="71" t="n"/>
       <c r="V14" s="71" t="n"/>
@@ -3695,7 +3709,7 @@
         <v>1044516</v>
       </c>
     </row>
-    <row r="15" customFormat="1" s="5">
+    <row r="15" customFormat="1" s="4">
       <c r="A15" s="48" t="inlineStr">
         <is>
           <t>安庆诚泰新材料有限公司</t>
@@ -3747,12 +3761,16 @@
           <t>商承/总付款≤20%</t>
         </is>
       </c>
-      <c r="N15" s="71" t="n"/>
+      <c r="N15" s="71" t="n">
+        <v>191315.42</v>
+      </c>
       <c r="O15" s="71" t="n"/>
       <c r="P15" s="71" t="n"/>
       <c r="Q15" s="71" t="n"/>
       <c r="R15" s="71" t="n"/>
-      <c r="S15" s="71" t="n"/>
+      <c r="S15" s="71" t="n">
+        <v>191315.42</v>
+      </c>
       <c r="T15" s="71" t="n"/>
       <c r="U15" s="71" t="n"/>
       <c r="V15" s="71" t="n"/>
@@ -3902,7 +3920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="1" s="5">
+    <row r="16" customFormat="1" s="4">
       <c r="A16" s="48" t="inlineStr">
         <is>
           <t>广州从化兆舜新材料有限公司</t>
@@ -3950,12 +3968,16 @@
         </is>
       </c>
       <c r="M16" s="71" t="n"/>
-      <c r="N16" s="71" t="n"/>
+      <c r="N16" s="71" t="n">
+        <v>1723380.29</v>
+      </c>
       <c r="O16" s="71" t="n"/>
       <c r="P16" s="71" t="n"/>
       <c r="Q16" s="71" t="n"/>
       <c r="R16" s="71" t="n"/>
-      <c r="S16" s="71" t="n"/>
+      <c r="S16" s="71" t="n">
+        <v>1723380.29</v>
+      </c>
       <c r="T16" s="71" t="n"/>
       <c r="U16" s="71" t="n"/>
       <c r="V16" s="71" t="n"/>
@@ -4105,7 +4127,7 @@
         <v>271656</v>
       </c>
     </row>
-    <row r="17" customFormat="1" s="5">
+    <row r="17" customFormat="1" s="4">
       <c r="A17" s="48" t="inlineStr">
         <is>
           <t>广州从化兆舜新材料有限公司</t>
@@ -4153,12 +4175,16 @@
         </is>
       </c>
       <c r="M17" s="71" t="n"/>
-      <c r="N17" s="71" t="n"/>
+      <c r="N17" s="71" t="n">
+        <v>46005.03</v>
+      </c>
       <c r="O17" s="71" t="n"/>
       <c r="P17" s="71" t="n"/>
       <c r="Q17" s="71" t="n"/>
       <c r="R17" s="71" t="n"/>
-      <c r="S17" s="71" t="n"/>
+      <c r="S17" s="71" t="n">
+        <v>46005.03</v>
+      </c>
       <c r="T17" s="71" t="n"/>
       <c r="U17" s="71" t="n"/>
       <c r="V17" s="71" t="n"/>
@@ -4308,7 +4334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" customFormat="1" s="5">
+    <row r="18" customFormat="1" s="4">
       <c r="A18" s="48" t="inlineStr">
         <is>
           <t>广州从化兆舜新材料有限公司</t>
@@ -4356,12 +4382,16 @@
         </is>
       </c>
       <c r="M18" s="71" t="n"/>
-      <c r="N18" s="71" t="n"/>
+      <c r="N18" s="71" t="n">
+        <v>1140615.78</v>
+      </c>
       <c r="O18" s="71" t="n"/>
       <c r="P18" s="71" t="n"/>
       <c r="Q18" s="71" t="n"/>
       <c r="R18" s="71" t="n"/>
-      <c r="S18" s="71" t="n"/>
+      <c r="S18" s="71" t="n">
+        <v>1140615.78</v>
+      </c>
       <c r="T18" s="71" t="n"/>
       <c r="U18" s="71" t="n"/>
       <c r="V18" s="71" t="n"/>
@@ -4511,7 +4541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" customFormat="1" s="5">
+    <row r="19" customFormat="1" s="4">
       <c r="A19" s="48" t="inlineStr">
         <is>
           <t>广州从化兆舜新材料有限公司</t>
@@ -4714,7 +4744,7 @@
         <v>12600</v>
       </c>
     </row>
-    <row r="20" customFormat="1" s="5">
+    <row r="20" customFormat="1" s="4">
       <c r="A20" s="48" t="inlineStr">
         <is>
           <t>广州从化兆舜新材料有限公司</t>
@@ -4762,12 +4792,16 @@
         </is>
       </c>
       <c r="M20" s="71" t="n"/>
-      <c r="N20" s="71" t="n"/>
+      <c r="N20" s="71" t="n">
+        <v>296313.23</v>
+      </c>
       <c r="O20" s="71" t="n"/>
       <c r="P20" s="71" t="n"/>
       <c r="Q20" s="71" t="n"/>
       <c r="R20" s="71" t="n"/>
-      <c r="S20" s="71" t="n"/>
+      <c r="S20" s="71" t="n">
+        <v>296313.23</v>
+      </c>
       <c r="T20" s="71" t="n"/>
       <c r="U20" s="71" t="n"/>
       <c r="V20" s="71" t="n"/>
@@ -4917,7 +4951,7 @@
         <v>106819</v>
       </c>
     </row>
-    <row r="21" customFormat="1" s="5">
+    <row r="21" customFormat="1" s="4">
       <c r="A21" s="48" t="inlineStr">
         <is>
           <t>广州从化兆舜新材料有限公司</t>
@@ -4965,12 +4999,16 @@
         </is>
       </c>
       <c r="M21" s="71" t="n"/>
-      <c r="N21" s="71" t="n"/>
+      <c r="N21" s="71" t="n">
+        <v>105473.47</v>
+      </c>
       <c r="O21" s="71" t="n"/>
       <c r="P21" s="71" t="n"/>
       <c r="Q21" s="71" t="n"/>
       <c r="R21" s="71" t="n"/>
-      <c r="S21" s="71" t="n"/>
+      <c r="S21" s="71" t="n">
+        <v>105473.47</v>
+      </c>
       <c r="T21" s="71" t="n"/>
       <c r="U21" s="71" t="n"/>
       <c r="V21" s="71" t="n"/>
@@ -5120,7 +5158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="1" s="7">
+    <row r="22" customFormat="1" s="6">
       <c r="A22" s="48" t="inlineStr">
         <is>
           <t>安徽集泰新材料有限公司</t>
@@ -5331,7 +5369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" customFormat="1" s="5">
+    <row r="23" customFormat="1" s="4">
       <c r="A23" s="48" t="inlineStr">
         <is>
           <t>广州从化兆舜新材料有限公司</t>
@@ -5379,12 +5417,16 @@
         </is>
       </c>
       <c r="M23" s="71" t="n"/>
-      <c r="N23" s="71" t="n"/>
+      <c r="N23" s="71" t="n">
+        <v>23807.85</v>
+      </c>
       <c r="O23" s="71" t="n"/>
       <c r="P23" s="71" t="n"/>
       <c r="Q23" s="71" t="n"/>
       <c r="R23" s="71" t="n"/>
-      <c r="S23" s="71" t="n"/>
+      <c r="S23" s="71" t="n">
+        <v>23807.85</v>
+      </c>
       <c r="T23" s="71" t="n"/>
       <c r="U23" s="71" t="n"/>
       <c r="V23" s="71" t="n"/>
@@ -5534,7 +5576,7 @@
         <v>23936.4</v>
       </c>
     </row>
-    <row r="24" customFormat="1" s="5">
+    <row r="24" customFormat="1" s="4">
       <c r="A24" s="48" t="inlineStr">
         <is>
           <t>广州从化兆舜新材料有限公司</t>
@@ -5582,12 +5624,16 @@
         </is>
       </c>
       <c r="M24" s="71" t="n"/>
-      <c r="N24" s="71" t="n"/>
+      <c r="N24" s="71" t="n">
+        <v>159345.93</v>
+      </c>
       <c r="O24" s="71" t="n"/>
       <c r="P24" s="71" t="n"/>
       <c r="Q24" s="71" t="n"/>
       <c r="R24" s="71" t="n"/>
-      <c r="S24" s="71" t="n"/>
+      <c r="S24" s="71" t="n">
+        <v>159345.93</v>
+      </c>
       <c r="T24" s="71" t="n"/>
       <c r="U24" s="71" t="n"/>
       <c r="V24" s="71" t="n"/>
@@ -5737,7 +5783,7 @@
         <v>47470</v>
       </c>
     </row>
-    <row r="25" customFormat="1" s="5">
+    <row r="25" customFormat="1" s="4">
       <c r="A25" s="48" t="inlineStr">
         <is>
           <t>广州从化兆舜新材料有限公司</t>
@@ -5940,7 +5986,7 @@
         <v>12769.3</v>
       </c>
     </row>
-    <row r="26" customFormat="1" s="5">
+    <row r="26" customFormat="1" s="4">
       <c r="A26" s="48" t="inlineStr">
         <is>
           <t>广州从化兆舜新材料有限公司</t>
@@ -5988,12 +6034,16 @@
         </is>
       </c>
       <c r="M26" s="71" t="n"/>
-      <c r="N26" s="71" t="n"/>
+      <c r="N26" s="71" t="n">
+        <v>87343.95999999999</v>
+      </c>
       <c r="O26" s="71" t="n"/>
       <c r="P26" s="71" t="n"/>
       <c r="Q26" s="71" t="n"/>
       <c r="R26" s="71" t="n"/>
-      <c r="S26" s="71" t="n"/>
+      <c r="S26" s="71" t="n">
+        <v>87343.95999999999</v>
+      </c>
       <c r="T26" s="71" t="n"/>
       <c r="U26" s="71" t="n"/>
       <c r="V26" s="71" t="n"/>
@@ -6143,7 +6193,7 @@
         <v>21909</v>
       </c>
     </row>
-    <row r="27" customFormat="1" s="5">
+    <row r="27" customFormat="1" s="4">
       <c r="A27" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -6346,7 +6396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" customFormat="1" s="5">
+    <row r="28" customFormat="1" s="4">
       <c r="A28" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -6394,12 +6444,16 @@
         </is>
       </c>
       <c r="M28" s="71" t="n"/>
-      <c r="N28" s="71" t="n"/>
+      <c r="N28" s="71" t="n">
+        <v>6780714.6</v>
+      </c>
       <c r="O28" s="71" t="n"/>
       <c r="P28" s="71" t="n"/>
       <c r="Q28" s="71" t="n"/>
       <c r="R28" s="71" t="n"/>
-      <c r="S28" s="71" t="n"/>
+      <c r="S28" s="71" t="n">
+        <v>6780714.6</v>
+      </c>
       <c r="T28" s="71" t="n"/>
       <c r="U28" s="71" t="n"/>
       <c r="V28" s="71" t="n"/>
@@ -6549,7 +6603,7 @@
         <v>704750</v>
       </c>
     </row>
-    <row r="29" customFormat="1" s="5">
+    <row r="29" customFormat="1" s="4">
       <c r="A29" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -6597,11 +6651,15 @@
         </is>
       </c>
       <c r="M29" s="71" t="n"/>
-      <c r="N29" s="71" t="n"/>
+      <c r="N29" s="71" t="n">
+        <v>858213.14</v>
+      </c>
       <c r="O29" s="71" t="n"/>
       <c r="P29" s="71" t="n"/>
       <c r="Q29" s="71" t="n"/>
-      <c r="R29" s="71" t="n"/>
+      <c r="R29" s="71" t="n">
+        <v>858213.14</v>
+      </c>
       <c r="S29" s="71" t="n"/>
       <c r="T29" s="71" t="n"/>
       <c r="U29" s="71" t="n"/>
@@ -6752,7 +6810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" customFormat="1" s="5">
+    <row r="30" customFormat="1" s="4">
       <c r="A30" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -6800,11 +6858,15 @@
         </is>
       </c>
       <c r="M30" s="71" t="n"/>
-      <c r="N30" s="71" t="n"/>
+      <c r="N30" s="71" t="n">
+        <v>34197</v>
+      </c>
       <c r="O30" s="71" t="n"/>
       <c r="P30" s="71" t="n"/>
       <c r="Q30" s="71" t="n"/>
-      <c r="R30" s="71" t="n"/>
+      <c r="R30" s="71" t="n">
+        <v>34197</v>
+      </c>
       <c r="S30" s="71" t="n"/>
       <c r="T30" s="71" t="n"/>
       <c r="U30" s="71" t="n"/>
@@ -6955,7 +7017,7 @@
         <v>6500</v>
       </c>
     </row>
-    <row r="31" customFormat="1" s="5">
+    <row r="31" customFormat="1" s="4">
       <c r="A31" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -7003,11 +7065,15 @@
         </is>
       </c>
       <c r="M31" s="71" t="n"/>
-      <c r="N31" s="71" t="n"/>
+      <c r="N31" s="71" t="n">
+        <v>129000</v>
+      </c>
       <c r="O31" s="71" t="n"/>
       <c r="P31" s="71" t="n"/>
       <c r="Q31" s="71" t="n"/>
-      <c r="R31" s="71" t="n"/>
+      <c r="R31" s="71" t="n">
+        <v>129000</v>
+      </c>
       <c r="S31" s="71" t="n"/>
       <c r="T31" s="71" t="n"/>
       <c r="U31" s="71" t="n"/>
@@ -7158,7 +7224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" customFormat="1" s="5">
+    <row r="32" customFormat="1" s="4">
       <c r="A32" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -7206,11 +7272,15 @@
         </is>
       </c>
       <c r="M32" s="71" t="n"/>
-      <c r="N32" s="71" t="n"/>
+      <c r="N32" s="71" t="n">
+        <v>1430588.85</v>
+      </c>
       <c r="O32" s="71" t="n"/>
       <c r="P32" s="71" t="n"/>
       <c r="Q32" s="71" t="n"/>
-      <c r="R32" s="71" t="n"/>
+      <c r="R32" s="71" t="n">
+        <v>1430588.85</v>
+      </c>
       <c r="S32" s="71" t="n"/>
       <c r="T32" s="71" t="n"/>
       <c r="U32" s="71" t="n"/>
@@ -7361,7 +7431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" customFormat="1" s="5">
+    <row r="33" customFormat="1" s="4">
       <c r="A33" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -7409,11 +7479,15 @@
         </is>
       </c>
       <c r="M33" s="71" t="n"/>
-      <c r="N33" s="71" t="n"/>
+      <c r="N33" s="71" t="n">
+        <v>197960</v>
+      </c>
       <c r="O33" s="71" t="n"/>
       <c r="P33" s="71" t="n"/>
       <c r="Q33" s="71" t="n"/>
-      <c r="R33" s="71" t="n"/>
+      <c r="R33" s="71" t="n">
+        <v>197960</v>
+      </c>
       <c r="S33" s="71" t="n"/>
       <c r="T33" s="71" t="n"/>
       <c r="U33" s="71" t="n"/>
@@ -7564,7 +7638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" customFormat="1" s="5">
+    <row r="34" customFormat="1" s="4">
       <c r="A34" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -7767,7 +7841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" customFormat="1" s="5">
+    <row r="35" customFormat="1" s="4">
       <c r="A35" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -7815,11 +7889,15 @@
         </is>
       </c>
       <c r="M35" s="71" t="n"/>
-      <c r="N35" s="71" t="n"/>
+      <c r="N35" s="71" t="n">
+        <v>220153.13</v>
+      </c>
       <c r="O35" s="74" t="n"/>
       <c r="P35" s="71" t="n"/>
       <c r="Q35" s="71" t="n"/>
-      <c r="R35" s="71" t="n"/>
+      <c r="R35" s="71" t="n">
+        <v>220153.13</v>
+      </c>
       <c r="S35" s="71" t="n"/>
       <c r="T35" s="71" t="n"/>
       <c r="U35" s="71" t="n"/>
@@ -7970,7 +8048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" customFormat="1" s="5">
+    <row r="36" customFormat="1" s="4">
       <c r="A36" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -8173,7 +8251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" customFormat="1" s="5">
+    <row r="37" customFormat="1" s="4">
       <c r="A37" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -8221,11 +8299,15 @@
         </is>
       </c>
       <c r="M37" s="71" t="n"/>
-      <c r="N37" s="71" t="n"/>
+      <c r="N37" s="71" t="n">
+        <v>170552.37</v>
+      </c>
       <c r="O37" s="71" t="n"/>
       <c r="P37" s="71" t="n"/>
       <c r="Q37" s="71" t="n"/>
-      <c r="R37" s="71" t="n"/>
+      <c r="R37" s="71" t="n">
+        <v>170552.37</v>
+      </c>
       <c r="S37" s="71" t="n"/>
       <c r="T37" s="71" t="n"/>
       <c r="U37" s="71" t="n"/>
@@ -8376,7 +8458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" customFormat="1" s="5">
+    <row r="38" customFormat="1" s="4">
       <c r="A38" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -8424,11 +8506,15 @@
         </is>
       </c>
       <c r="M38" s="71" t="n"/>
-      <c r="N38" s="71" t="n"/>
+      <c r="N38" s="71" t="n">
+        <v>58732.71</v>
+      </c>
       <c r="O38" s="71" t="n"/>
       <c r="P38" s="71" t="n"/>
       <c r="Q38" s="71" t="n"/>
-      <c r="R38" s="71" t="n"/>
+      <c r="R38" s="71" t="n">
+        <v>58732.71</v>
+      </c>
       <c r="S38" s="71" t="n"/>
       <c r="T38" s="71" t="n"/>
       <c r="U38" s="71" t="n"/>
@@ -8579,7 +8665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" customFormat="1" s="5">
+    <row r="39" customFormat="1" s="4">
       <c r="A39" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -8627,11 +8713,15 @@
         </is>
       </c>
       <c r="M39" s="71" t="n"/>
-      <c r="N39" s="71" t="n"/>
+      <c r="N39" s="71" t="n">
+        <v>36100</v>
+      </c>
       <c r="O39" s="71" t="n"/>
       <c r="P39" s="71" t="n"/>
       <c r="Q39" s="71" t="n"/>
-      <c r="R39" s="71" t="n"/>
+      <c r="R39" s="71" t="n">
+        <v>36100</v>
+      </c>
       <c r="S39" s="71" t="n"/>
       <c r="T39" s="71" t="n"/>
       <c r="U39" s="71" t="n"/>
@@ -8782,7 +8872,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="40" customFormat="1" s="5">
+    <row r="40" customFormat="1" s="4">
       <c r="A40" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -8830,11 +8920,15 @@
         </is>
       </c>
       <c r="M40" s="71" t="n"/>
-      <c r="N40" s="71" t="n"/>
+      <c r="N40" s="71" t="n">
+        <v>112860.5</v>
+      </c>
       <c r="O40" s="71" t="n"/>
       <c r="P40" s="71" t="n"/>
       <c r="Q40" s="71" t="n"/>
-      <c r="R40" s="71" t="n"/>
+      <c r="R40" s="71" t="n">
+        <v>112860.5</v>
+      </c>
       <c r="S40" s="71" t="n"/>
       <c r="T40" s="71" t="n"/>
       <c r="U40" s="71" t="n"/>
@@ -8985,7 +9079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" customFormat="1" s="5">
+    <row r="41" customFormat="1" s="4">
       <c r="A41" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -9033,11 +9127,15 @@
         </is>
       </c>
       <c r="M41" s="71" t="n"/>
-      <c r="N41" s="71" t="n"/>
+      <c r="N41" s="71" t="n">
+        <v>2604892.609999999</v>
+      </c>
       <c r="O41" s="71" t="n"/>
       <c r="P41" s="71" t="n"/>
       <c r="Q41" s="71" t="n"/>
-      <c r="R41" s="71" t="n"/>
+      <c r="R41" s="71" t="n">
+        <v>2604892.609999999</v>
+      </c>
       <c r="S41" s="71" t="n"/>
       <c r="T41" s="71" t="n"/>
       <c r="U41" s="71" t="n"/>
@@ -9188,7 +9286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" customFormat="1" s="5">
+    <row r="42" customFormat="1" s="4">
       <c r="A42" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -9395,7 +9493,7 @@
         <v>236127.13</v>
       </c>
     </row>
-    <row r="43" customFormat="1" s="5">
+    <row r="43" customFormat="1" s="4">
       <c r="A43" s="48" t="inlineStr">
         <is>
           <t>安徽集泰新材料有限公司</t>
@@ -9447,7 +9545,9 @@
         </is>
       </c>
       <c r="M43" s="71" t="n"/>
-      <c r="N43" s="71" t="n"/>
+      <c r="N43" s="71" t="n">
+        <v>7200</v>
+      </c>
       <c r="O43" s="71" t="n"/>
       <c r="P43" s="71" t="n"/>
       <c r="Q43" s="71" t="n"/>
@@ -9456,7 +9556,9 @@
       <c r="T43" s="71" t="n"/>
       <c r="U43" s="71" t="n"/>
       <c r="V43" s="71" t="n"/>
-      <c r="W43" s="71" t="n"/>
+      <c r="W43" s="71" t="n">
+        <v>7200</v>
+      </c>
       <c r="X43" s="71" t="n"/>
       <c r="Y43" s="71" t="n">
         <v>15300</v>
@@ -9602,7 +9704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" customFormat="1" s="5">
+    <row r="44" customFormat="1" s="4">
       <c r="A44" s="48" t="inlineStr">
         <is>
           <t>广州从化兆舜新材料有限公司</t>
@@ -9809,7 +9911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" customFormat="1" s="5">
+    <row r="45" customFormat="1" s="4">
       <c r="A45" s="48" t="inlineStr">
         <is>
           <t>广州从化兆舜新材料有限公司</t>
@@ -9857,12 +9959,16 @@
         </is>
       </c>
       <c r="M45" s="71" t="n"/>
-      <c r="N45" s="71" t="n"/>
+      <c r="N45" s="71" t="n">
+        <v>20800</v>
+      </c>
       <c r="O45" s="71" t="n"/>
       <c r="P45" s="71" t="n"/>
       <c r="Q45" s="71" t="n"/>
       <c r="R45" s="71" t="n"/>
-      <c r="S45" s="71" t="n"/>
+      <c r="S45" s="71" t="n">
+        <v>20800</v>
+      </c>
       <c r="T45" s="71" t="n"/>
       <c r="U45" s="71" t="n"/>
       <c r="V45" s="71" t="n"/>
@@ -10012,7 +10118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" customFormat="1" s="5">
+    <row r="46" customFormat="1" s="4">
       <c r="A46" s="48" t="inlineStr">
         <is>
           <t>广州从化兆舜新材料有限公司</t>
@@ -10060,12 +10166,16 @@
         </is>
       </c>
       <c r="M46" s="71" t="n"/>
-      <c r="N46" s="71" t="n"/>
+      <c r="N46" s="71" t="n">
+        <v>564.290000000037</v>
+      </c>
       <c r="O46" s="71" t="n"/>
       <c r="P46" s="71" t="n"/>
       <c r="Q46" s="71" t="n"/>
       <c r="R46" s="71" t="n"/>
-      <c r="S46" s="71" t="n"/>
+      <c r="S46" s="71" t="n">
+        <v>564.290000000037</v>
+      </c>
       <c r="T46" s="71" t="n"/>
       <c r="U46" s="71" t="n"/>
       <c r="V46" s="71" t="n"/>
@@ -10215,7 +10325,7 @@
         <v>51500</v>
       </c>
     </row>
-    <row r="47" customFormat="1" s="5">
+    <row r="47" customFormat="1" s="4">
       <c r="A47" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -10263,13 +10373,17 @@
         </is>
       </c>
       <c r="M47" s="71" t="n"/>
-      <c r="N47" s="71" t="n"/>
+      <c r="N47" s="71" t="n">
+        <v>1110226.4</v>
+      </c>
       <c r="O47" s="71" t="n"/>
       <c r="P47" s="71" t="n"/>
       <c r="Q47" s="71" t="n"/>
       <c r="R47" s="71" t="n"/>
       <c r="S47" s="71" t="n"/>
-      <c r="T47" s="71" t="n"/>
+      <c r="T47" s="71" t="n">
+        <v>1110226.4</v>
+      </c>
       <c r="U47" s="71" t="n"/>
       <c r="V47" s="71" t="n"/>
       <c r="W47" s="71" t="n"/>
@@ -10418,7 +10532,7 @@
         <v>326272</v>
       </c>
     </row>
-    <row r="48" customFormat="1" s="5">
+    <row r="48" customFormat="1" s="4">
       <c r="A48" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -10621,7 +10735,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="49" customFormat="1" s="5">
+    <row r="49" customFormat="1" s="4">
       <c r="A49" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -10828,7 +10942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" customFormat="1" s="5">
+    <row r="50" customFormat="1" s="4">
       <c r="A50" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -11031,7 +11145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" customFormat="1" s="5">
+    <row r="51" customFormat="1" s="4">
       <c r="A51" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -11234,7 +11348,7 @@
         <v>48800</v>
       </c>
     </row>
-    <row r="52" customFormat="1" s="5">
+    <row r="52" customFormat="1" s="4">
       <c r="A52" s="49" t="inlineStr">
         <is>
           <t>安徽集泰新材料有限公司</t>
@@ -11445,7 +11559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" customFormat="1" s="5">
+    <row r="53" customFormat="1" s="4">
       <c r="A53" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -11648,7 +11762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" customFormat="1" s="5">
+    <row r="54" customFormat="1" s="4">
       <c r="A54" s="49" t="inlineStr">
         <is>
           <t>广州从化兆舜新材料有限公司</t>
@@ -11855,7 +11969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" customFormat="1" s="5">
+    <row r="55" customFormat="1" s="4">
       <c r="A55" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -11907,11 +12021,15 @@
         </is>
       </c>
       <c r="M55" s="71" t="n"/>
-      <c r="N55" s="71" t="n"/>
+      <c r="N55" s="71" t="n">
+        <v>680569.4</v>
+      </c>
       <c r="O55" s="71" t="n"/>
       <c r="P55" s="71" t="n"/>
       <c r="Q55" s="71" t="n"/>
-      <c r="R55" s="71" t="n"/>
+      <c r="R55" s="71" t="n">
+        <v>680569.4</v>
+      </c>
       <c r="S55" s="71" t="n"/>
       <c r="T55" s="71" t="n"/>
       <c r="U55" s="71" t="n"/>
@@ -12062,7 +12180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" customFormat="1" s="5">
+    <row r="56" customFormat="1" s="4">
       <c r="A56" s="48" t="inlineStr">
         <is>
           <t>广州集泰化工股份有限公司</t>
@@ -12110,11 +12228,15 @@
         </is>
       </c>
       <c r="M56" s="73" t="n"/>
-      <c r="N56" s="73" t="n"/>
+      <c r="N56" s="73" t="n">
+        <v>2131070.419999999</v>
+      </c>
       <c r="O56" s="71" t="n"/>
       <c r="P56" s="71" t="n"/>
       <c r="Q56" s="71" t="n"/>
-      <c r="R56" s="71" t="n"/>
+      <c r="R56" s="71" t="n">
+        <v>2131070.419999999</v>
+      </c>
       <c r="S56" s="71" t="n"/>
       <c r="T56" s="71" t="n"/>
       <c r="U56" s="71" t="n"/>
@@ -12266,11 +12388,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="Z57" s="5">
+      <c r="Z57" s="4">
         <f>(AB54+AC54)/Y54</f>
         <v/>
       </c>
-      <c r="AB57" s="5">
+      <c r="AB57" s="4">
         <f>AC54/Y54</f>
         <v/>
       </c>
@@ -12297,173 +12419,1063 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:B105"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col width="26.9134615384615" customWidth="1" style="75" min="2" max="2"/>
-    <col width="10.3076923076923" customWidth="1" style="75" min="3" max="3"/>
-    <col width="12.7692307692308" customWidth="1" style="75" min="4" max="4"/>
+    <col width="15.3846153846154" customWidth="1" style="75" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="48" t="inlineStr">
         <is>
-          <t>序号</t>
+          <t>类别</t>
         </is>
       </c>
       <c r="B1" s="48" t="inlineStr">
         <is>
-          <t>银行名称</t>
-        </is>
-      </c>
-      <c r="C1" s="48" t="inlineStr">
-        <is>
-          <t>付款方式</t>
-        </is>
-      </c>
-      <c r="D1" s="48" t="inlineStr">
-        <is>
-          <t>可支付金额</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="n"/>
-      <c r="F1" s="5" t="n"/>
-      <c r="G1" s="5" t="n"/>
-    </row>
-    <row r="2" ht="17.6" customHeight="1" s="75">
-      <c r="A2" s="48" t="n">
+          <t>类别优先级</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="48" t="inlineStr">
+        <is>
+          <t>107、DMC、硅油</t>
+        </is>
+      </c>
+      <c r="B2" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="48" t="inlineStr">
-        <is>
-          <t>中国银行</t>
-        </is>
-      </c>
-      <c r="C2" s="59" t="n"/>
-      <c r="D2" s="59" t="n"/>
-      <c r="E2" s="76" t="n"/>
-      <c r="F2" s="76" t="n"/>
-      <c r="G2" s="76" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="48" t="n">
+      <c r="A3" s="48" t="inlineStr">
+        <is>
+          <t>橡胶</t>
+        </is>
+      </c>
+      <c r="B3" s="48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="48" t="inlineStr">
+        <is>
+          <t>含氢硅油</t>
+        </is>
+      </c>
+      <c r="B4" s="48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="48" t="inlineStr">
+        <is>
+          <t>封头剂</t>
+        </is>
+      </c>
+      <c r="B5" s="48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="48" t="inlineStr">
+        <is>
+          <t>交联剂</t>
+        </is>
+      </c>
+      <c r="B6" s="48" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="48" t="inlineStr">
-        <is>
-          <t>浦发银行</t>
-        </is>
-      </c>
-      <c r="C3" s="48" t="n"/>
-      <c r="D3" s="48" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="48" t="n">
+    </row>
+    <row r="7">
+      <c r="A7" s="48" t="inlineStr">
+        <is>
+          <t>偶联剂</t>
+        </is>
+      </c>
+      <c r="B7" s="48" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="48" t="inlineStr">
+        <is>
+          <t>组角胶</t>
+        </is>
+      </c>
+      <c r="B8" s="48" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="48" t="inlineStr">
-        <is>
-          <t>中国银行</t>
-        </is>
-      </c>
-      <c r="C4" s="48" t="n"/>
-      <c r="D4" s="48" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="48" t="n">
+    </row>
+    <row r="9">
+      <c r="A9" s="48" t="inlineStr">
+        <is>
+          <t>发泡剂</t>
+        </is>
+      </c>
+      <c r="B9" s="48" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="48" t="inlineStr">
+        <is>
+          <t>外购防火涂料</t>
+        </is>
+      </c>
+      <c r="B10" s="48" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="48" t="inlineStr">
+        <is>
+          <t>外购美缝剂</t>
+        </is>
+      </c>
+      <c r="B11" s="48" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="48" t="inlineStr">
+        <is>
+          <t>外购透明胶</t>
+        </is>
+      </c>
+      <c r="B12" s="48" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="48" t="inlineStr">
+        <is>
+          <t>外购3C涂料</t>
+        </is>
+      </c>
+      <c r="B13" s="48" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="48" t="inlineStr">
+        <is>
+          <t>外购153胶</t>
+        </is>
+      </c>
+      <c r="B14" s="48" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="48" t="inlineStr">
+        <is>
+          <t>外购汽车胶</t>
+        </is>
+      </c>
+      <c r="B15" s="48" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="48" t="inlineStr">
+        <is>
+          <t>外购窗缝胶</t>
+        </is>
+      </c>
+      <c r="B16" s="48" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="48" t="inlineStr">
+        <is>
+          <t>外购胶</t>
+        </is>
+      </c>
+      <c r="B17" s="48" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="48" t="inlineStr">
+        <is>
+          <t>外购垫片</t>
+        </is>
+      </c>
+      <c r="B18" s="48" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="48" t="inlineStr">
+        <is>
+          <t>防火涂料</t>
+        </is>
+      </c>
+      <c r="B19" s="48" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="48" t="inlineStr">
+        <is>
+          <t>PE树脂</t>
+        </is>
+      </c>
+      <c r="B20" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="48" t="inlineStr">
-        <is>
-          <t>平安银行</t>
-        </is>
-      </c>
-      <c r="C5" s="48" t="n"/>
-      <c r="D5" s="48" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="48" t="n">
+    </row>
+    <row r="21">
+      <c r="A21" s="48" t="inlineStr">
+        <is>
+          <t>PE树脂、封端107</t>
+        </is>
+      </c>
+      <c r="B21" s="48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="48" t="inlineStr">
+        <is>
+          <t>催化剂</t>
+        </is>
+      </c>
+      <c r="B22" s="48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="48" t="inlineStr">
+        <is>
+          <t>阻燃剂</t>
+        </is>
+      </c>
+      <c r="B23" s="48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="48" t="inlineStr">
+        <is>
+          <t>蓖麻油</t>
+        </is>
+      </c>
+      <c r="B24" s="48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="48" t="inlineStr">
+        <is>
+          <t>溶剂</t>
+        </is>
+      </c>
+      <c r="B25" s="48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="48" t="inlineStr">
+        <is>
+          <t>聚醚</t>
+        </is>
+      </c>
+      <c r="B26" s="48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="48" t="inlineStr">
+        <is>
+          <t>气硅</t>
+        </is>
+      </c>
+      <c r="B27" s="48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="48" t="inlineStr">
+        <is>
+          <t>抗氧剂</t>
+        </is>
+      </c>
+      <c r="B28" s="48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="48" t="inlineStr">
+        <is>
+          <t>醇酸树脂</t>
+        </is>
+      </c>
+      <c r="B29" s="48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="48" t="inlineStr">
+        <is>
+          <t>PVC树脂</t>
+        </is>
+      </c>
+      <c r="B30" s="48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="48" t="inlineStr">
+        <is>
+          <t>PU树脂</t>
+        </is>
+      </c>
+      <c r="B31" s="48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="48" t="inlineStr">
+        <is>
+          <t>聚异丁烯</t>
+        </is>
+      </c>
+      <c r="B32" s="48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="48" t="inlineStr">
+        <is>
+          <t>增塑剂、成膜助剂</t>
+        </is>
+      </c>
+      <c r="B33" s="48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="48" t="inlineStr">
+        <is>
+          <t>气硅、碳黑</t>
+        </is>
+      </c>
+      <c r="B34" s="48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="48" t="inlineStr">
+        <is>
+          <t>碳黑</t>
+        </is>
+      </c>
+      <c r="B35" s="48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="48" t="inlineStr">
+        <is>
+          <t>碳酸钙</t>
+        </is>
+      </c>
+      <c r="B36" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="48" t="inlineStr">
-        <is>
-          <t>易信</t>
-        </is>
-      </c>
-      <c r="C6" s="48" t="n"/>
-      <c r="D6" s="48" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="48" t="n">
+    </row>
+    <row r="37">
+      <c r="A37" s="48" t="inlineStr">
+        <is>
+          <t>钙粉</t>
+        </is>
+      </c>
+      <c r="B37" s="48" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="48" t="inlineStr">
+        <is>
+          <t>溶剂、硅油</t>
+        </is>
+      </c>
+      <c r="B38" s="48" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="48" t="inlineStr">
+        <is>
+          <t>导热粉</t>
+        </is>
+      </c>
+      <c r="B39" s="48" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="48" t="inlineStr">
+        <is>
+          <t>钛白粉</t>
+        </is>
+      </c>
+      <c r="B40" s="48" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="48" t="inlineStr">
+        <is>
+          <t>胶筒</t>
+        </is>
+      </c>
+      <c r="B41" s="48" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="48" t="inlineStr">
-        <is>
-          <t>资金计划</t>
-        </is>
-      </c>
-      <c r="C7" s="48" t="n"/>
-      <c r="D7" s="48" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="48" t="n"/>
-      <c r="B8" s="48" t="n"/>
-      <c r="C8" s="48" t="n"/>
-      <c r="D8" s="48" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="48" t="n"/>
-      <c r="B9" s="48" t="n"/>
-      <c r="C9" s="48" t="n"/>
-      <c r="D9" s="48" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="48" t="n"/>
-      <c r="B10" s="48" t="n"/>
-      <c r="C10" s="48" t="n"/>
-      <c r="D10" s="48" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="48" t="n"/>
-      <c r="B11" s="48" t="n"/>
-      <c r="C11" s="48" t="n"/>
-      <c r="D11" s="48" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="48" t="n"/>
-      <c r="B12" s="48" t="n"/>
-      <c r="C12" s="48" t="n"/>
-      <c r="D12" s="48" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="48" t="inlineStr">
+        <is>
+          <t>软膜</t>
+        </is>
+      </c>
+      <c r="B42" s="48" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="48" t="inlineStr">
+        <is>
+          <t>纸箱</t>
+        </is>
+      </c>
+      <c r="B43" s="48" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="48" t="inlineStr">
+        <is>
+          <t>胶筒、软膜</t>
+        </is>
+      </c>
+      <c r="B44" s="48" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="48" t="inlineStr">
+        <is>
+          <t>纸箱、软膜、胶筒</t>
+        </is>
+      </c>
+      <c r="B45" s="48" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="48" t="inlineStr">
+        <is>
+          <t>铝卡</t>
+        </is>
+      </c>
+      <c r="B46" s="48" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="48" t="inlineStr">
+        <is>
+          <t>铁桶</t>
+        </is>
+      </c>
+      <c r="B47" s="48" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="48" t="inlineStr">
+        <is>
+          <t>铁桶、木地板</t>
+        </is>
+      </c>
+      <c r="B48" s="48" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="48" t="inlineStr">
+        <is>
+          <t>环氧固化剂</t>
+        </is>
+      </c>
+      <c r="B49" s="48" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="48" t="inlineStr">
+        <is>
+          <t>乳液</t>
+        </is>
+      </c>
+      <c r="B50" s="48" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="48" t="inlineStr">
+        <is>
+          <t>环氧</t>
+        </is>
+      </c>
+      <c r="B51" s="48" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="48" t="inlineStr">
+        <is>
+          <t>聚氨酯树脂</t>
+        </is>
+      </c>
+      <c r="B52" s="48" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="48" t="inlineStr">
+        <is>
+          <t>固化剂</t>
+        </is>
+      </c>
+      <c r="B53" s="48" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="48" t="inlineStr">
+        <is>
+          <t>固化剂、防锈剂</t>
+        </is>
+      </c>
+      <c r="B54" s="48" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="48" t="inlineStr">
+        <is>
+          <t>聚氨酯固化剂</t>
+        </is>
+      </c>
+      <c r="B55" s="48" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="48" t="inlineStr">
+        <is>
+          <t>树脂、分散剂</t>
+        </is>
+      </c>
+      <c r="B56" s="48" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="48" t="inlineStr">
+        <is>
+          <t>溶剂、煤油</t>
+        </is>
+      </c>
+      <c r="B57" s="48" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="48" t="inlineStr">
+        <is>
+          <t>溶剂、树脂</t>
+        </is>
+      </c>
+      <c r="B58" s="48" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="48" t="inlineStr">
+        <is>
+          <t>乳液、消泡剂</t>
+        </is>
+      </c>
+      <c r="B59" s="48" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="48" t="inlineStr">
+        <is>
+          <t>聚氨酯</t>
+        </is>
+      </c>
+      <c r="B60" s="48" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="48" t="inlineStr">
+        <is>
+          <t>乳化沥青</t>
+        </is>
+      </c>
+      <c r="B61" s="48" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="48" t="inlineStr">
+        <is>
+          <t>锌粉</t>
+        </is>
+      </c>
+      <c r="B62" s="48" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="48" t="inlineStr">
+        <is>
+          <t>树脂</t>
+        </is>
+      </c>
+      <c r="B63" s="48" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="48" t="inlineStr">
+        <is>
+          <t>沥青</t>
+        </is>
+      </c>
+      <c r="B64" s="48" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="48" t="inlineStr">
+        <is>
+          <t>增稠剂、防锈剂</t>
+        </is>
+      </c>
+      <c r="B65" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="48" t="inlineStr">
+        <is>
+          <t>增塑剂</t>
+        </is>
+      </c>
+      <c r="B66" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="48" t="inlineStr">
+        <is>
+          <t>色浆</t>
+        </is>
+      </c>
+      <c r="B67" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="48" t="inlineStr">
+        <is>
+          <t>消泡剂、分散剂</t>
+        </is>
+      </c>
+      <c r="B68" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="48" t="inlineStr">
+        <is>
+          <t>无机涂料助剂</t>
+        </is>
+      </c>
+      <c r="B69" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="48" t="inlineStr">
+        <is>
+          <t>消泡剂、增稠剂</t>
+        </is>
+      </c>
+      <c r="B70" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="48" t="inlineStr">
+        <is>
+          <t>消泡剂</t>
+        </is>
+      </c>
+      <c r="B71" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="48" t="inlineStr">
+        <is>
+          <t>成膜助剂</t>
+        </is>
+      </c>
+      <c r="B72" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="48" t="inlineStr">
+        <is>
+          <t>防锈剂</t>
+        </is>
+      </c>
+      <c r="B73" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="48" t="inlineStr">
+        <is>
+          <t>分散剂、增稠剂</t>
+        </is>
+      </c>
+      <c r="B74" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="48" t="inlineStr">
+        <is>
+          <t>防霉剂</t>
+        </is>
+      </c>
+      <c r="B75" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="48" t="inlineStr">
+        <is>
+          <t>中和剂</t>
+        </is>
+      </c>
+      <c r="B76" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="48" t="inlineStr">
+        <is>
+          <t>碳黑、流平剂</t>
+        </is>
+      </c>
+      <c r="B77" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="48" t="inlineStr">
+        <is>
+          <t>润湿剂</t>
+        </is>
+      </c>
+      <c r="B78" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="48" t="inlineStr">
+        <is>
+          <t>润湿剂、流平剂</t>
+        </is>
+      </c>
+      <c r="B79" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="48" t="inlineStr">
+        <is>
+          <t>防锈填料</t>
+        </is>
+      </c>
+      <c r="B80" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="48" t="inlineStr">
+        <is>
+          <t>防腐剂、防霉剂</t>
+        </is>
+      </c>
+      <c r="B81" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="48" t="inlineStr">
+        <is>
+          <t>增粘剂</t>
+        </is>
+      </c>
+      <c r="B82" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="48" t="inlineStr">
+        <is>
+          <t>酒精</t>
+        </is>
+      </c>
+      <c r="B83" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="48" t="inlineStr">
+        <is>
+          <t>聚酰胺蜡</t>
+        </is>
+      </c>
+      <c r="B84" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="48" t="inlineStr">
+        <is>
+          <t>分散剂</t>
+        </is>
+      </c>
+      <c r="B85" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="48" t="inlineStr">
+        <is>
+          <t>增稠剂</t>
+        </is>
+      </c>
+      <c r="B86" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="48" t="inlineStr">
+        <is>
+          <t>硫酸钡</t>
+        </is>
+      </c>
+      <c r="B87" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="48" t="inlineStr">
+        <is>
+          <t>硅微粉</t>
+        </is>
+      </c>
+      <c r="B88" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="48" t="inlineStr">
+        <is>
+          <t>珠光粉</t>
+        </is>
+      </c>
+      <c r="B89" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="48" t="inlineStr">
+        <is>
+          <t>导电粉</t>
+        </is>
+      </c>
+      <c r="B90" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="48" t="inlineStr">
+        <is>
+          <t>硅微粉、云母粉</t>
+        </is>
+      </c>
+      <c r="B91" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="48" t="inlineStr">
+        <is>
+          <t>色粉</t>
+        </is>
+      </c>
+      <c r="B92" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="48" t="inlineStr">
+        <is>
+          <t>膨润土</t>
+        </is>
+      </c>
+      <c r="B93" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="48" t="inlineStr">
+        <is>
+          <t>活化粉</t>
+        </is>
+      </c>
+      <c r="B94" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="48" t="inlineStr">
+        <is>
+          <t>凡士林</t>
+        </is>
+      </c>
+      <c r="B95" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="48" t="inlineStr">
+        <is>
+          <t>防老剂</t>
+        </is>
+      </c>
+      <c r="B96" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="48" t="inlineStr">
+        <is>
+          <t>玻璃微珠</t>
+        </is>
+      </c>
+      <c r="B97" s="48" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="48" t="inlineStr">
+        <is>
+          <t>检测用品</t>
+        </is>
+      </c>
+      <c r="B98" s="48" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="48" t="inlineStr">
+        <is>
+          <t>塑料桶</t>
+        </is>
+      </c>
+      <c r="B99" s="48" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="48" t="inlineStr">
+        <is>
+          <t>木地板</t>
+        </is>
+      </c>
+      <c r="B100" s="48" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="48" t="inlineStr">
+        <is>
+          <t>打包材料</t>
+        </is>
+      </c>
+      <c r="B101" s="48" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="48" t="inlineStr">
+        <is>
+          <t>标签</t>
+        </is>
+      </c>
+      <c r="B102" s="48" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="48" t="inlineStr">
+        <is>
+          <t>木地板、标签</t>
+        </is>
+      </c>
+      <c r="B103" s="48" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="48" t="inlineStr">
+        <is>
+          <t>礼品</t>
+        </is>
+      </c>
+      <c r="B104" s="48" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="48" t="inlineStr">
+        <is>
+          <t>胶枪</t>
+        </is>
+      </c>
+      <c r="B105" s="48" t="n">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12477,87 +13489,205 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col width="26.9134615384615" customWidth="1" style="75" min="2" max="2"/>
+    <col width="12.7692307692308" customWidth="1" style="75" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>分类</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>优先级</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>偶联剂</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
+      <c r="A1" s="48" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="48" t="inlineStr">
+        <is>
+          <t>银行名称</t>
+        </is>
+      </c>
+      <c r="C1" s="48" t="inlineStr">
+        <is>
+          <t>付款优先级</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="17.6" customHeight="1" s="75">
+      <c r="A2" s="48" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="48" t="inlineStr">
+        <is>
+          <t>中国银行</t>
+        </is>
+      </c>
+      <c r="C2" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="76" t="n"/>
+      <c r="E2" s="76" t="n"/>
+      <c r="F2" s="76" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>乳液</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
+      <c r="A3" s="48" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="48" t="inlineStr">
+        <is>
+          <t>浦发银行</t>
+        </is>
+      </c>
+      <c r="C3" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>纸箱</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>3</v>
-      </c>
+      <c r="A4" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" s="48" t="inlineStr">
+        <is>
+          <t>平安银行</t>
+        </is>
+      </c>
+      <c r="C4" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>碳酸钙</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
+      <c r="A5" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" s="48" t="inlineStr">
+        <is>
+          <t>易信</t>
+        </is>
+      </c>
+      <c r="C5" s="48" t="n">
         <v>4</v>
       </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" s="48" t="inlineStr">
+        <is>
+          <t>资金计划</t>
+        </is>
+      </c>
+      <c r="C6" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="48" t="n"/>
+      <c r="B7" s="48" t="n"/>
+      <c r="C7" s="48" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>成本二部</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>曹</t>
-        </is>
-      </c>
+      <c r="A8" s="48" t="n"/>
+      <c r="B8" s="48" t="n"/>
+      <c r="C8" s="48" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>成本三部</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>彭</t>
-        </is>
-      </c>
+      <c r="A9" s="48" t="n"/>
+      <c r="B9" s="48" t="n"/>
+      <c r="C9" s="48" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="48" t="n"/>
+      <c r="B10" s="48" t="n"/>
+      <c r="C10" s="48" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="48" t="n"/>
+      <c r="B11" s="48" t="n"/>
+      <c r="C11" s="48" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="48" t="inlineStr">
+        <is>
+          <t>成本名称</t>
+        </is>
+      </c>
+      <c r="B1" s="48" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="48" t="inlineStr">
+        <is>
+          <t>成本二部</t>
+        </is>
+      </c>
+      <c r="B2" s="48" t="inlineStr">
+        <is>
+          <t>彭</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">成本三部 </t>
+        </is>
+      </c>
+      <c r="B3" s="48" t="inlineStr">
+        <is>
+          <t>曹</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/AutoPaymentScheduleFile/TotalSheet/排款计划参照数据原表.xlsx
+++ b/AutoPaymentScheduleFile/TotalSheet/排款计划参照数据原表.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="14480" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="14360" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -255,7 +255,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="72">
     <fill>
       <patternFill/>
     </fill>
@@ -466,6 +466,572 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.7153346153846154">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.7154346153846154">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.5863679970891177">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.5864679970891177">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.8773836283185841">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.8774836283185841">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.4441206569037658">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.4442206569037658">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.29995">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.30005">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.8857926234979974">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.8858926234979974">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.7655245381433566">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.7656245381433566">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.3784999210747609">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.3785999210747609">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.04818654122695786">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.04828654122695786">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFF00"/>
+        </stop>
+        <stop position="0.89995">
+          <color rgb="FFFFFF00"/>
+        </stop>
+        <stop position="0.90005">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.7931553846153847">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.7932553846153847">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.1178149371069183">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.1179149371069182">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.7913848426556175">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.7914848426556175">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.9294282227784733">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.9295282227784732">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.3972840636268195">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.3973840636268194">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.005516254880423616">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.005616254880423615">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.09904835451287142">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.09914835451287141">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.3962853293413178">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.3963853293413178">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.83995">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.84005">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.2370082823529414">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.2371082823529413">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.5972207204495285">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.5973207204495284">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.3074403035841202">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.3075403035841202">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.7434448656375071">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.7435448656375071">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.4139125136612019">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.4140125136612018">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.77995">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.78005">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.6287600326879558">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.6288600326879558">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.8260196892327526">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.8261196892327526">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.7259446666666666">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.7260446666666666">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.3859595503300329">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.3860595503300329">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.5176963038847803">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.5177963038847803">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.19995">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.20005">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.8548817585301837">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.8549817585301837">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.51995">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.52005">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.1449647773581354">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.1450647773581354">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.3912654200000005">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="0.3913654200000005">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFC6EFCE"/>
+        </stop>
+      </gradientFill>
+    </fill>
   </fills>
   <borders count="14">
     <border>
@@ -782,7 +1348,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1012,16 +1578,124 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="64" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="46" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="70" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="71" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="65" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="47" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="45" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="69" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="66" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="48" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="49" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="50" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="67" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="51" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="52" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="53" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="54" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="55" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="56" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="57" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="58" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="59" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="60" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="61" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="62" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="63" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="37" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="40" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="68" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="42" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="43" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2130,22 +2804,22 @@
         </is>
       </c>
       <c r="R5" s="64" t="n">
-        <v>478272.1300000027</v>
+        <v>15294.5449999999</v>
       </c>
       <c r="S5" s="64" t="n">
-        <v>2119394.24</v>
+        <v>303271.8689999983</v>
       </c>
       <c r="T5" s="64" t="n">
-        <v>3602637.6</v>
+        <v>278932.4879999999</v>
       </c>
       <c r="U5" s="64" t="n">
-        <v>8000000</v>
+        <v>1709493.92</v>
       </c>
       <c r="V5" s="64" t="n">
         <v>5220000</v>
       </c>
       <c r="W5" s="64" t="n">
-        <v>2806500</v>
+        <v>2809290</v>
       </c>
       <c r="X5" s="64" t="n"/>
       <c r="Y5" s="74" t="n"/>
@@ -2415,7 +3089,7 @@
       </c>
       <c r="S8" s="64" t="inlineStr">
         <is>
-          <t>电汇、银承</t>
+          <t>银承</t>
         </is>
       </c>
       <c r="T8" s="64" t="inlineStr">
@@ -2954,24 +3628,24 @@
       </c>
       <c r="M11" s="76" t="n"/>
       <c r="N11" s="76" t="n">
-        <v>244496</v>
+        <v>435596.8</v>
       </c>
       <c r="O11" s="76" t="n"/>
       <c r="P11" s="76" t="n"/>
       <c r="Q11" s="76" t="n"/>
       <c r="R11" s="76" t="n"/>
-      <c r="S11" s="76" t="n">
-        <v>244496</v>
-      </c>
+      <c r="S11" s="76" t="n"/>
       <c r="T11" s="76" t="n"/>
-      <c r="U11" s="76" t="n"/>
+      <c r="U11" s="76" t="n">
+        <v>435596.8</v>
+      </c>
       <c r="V11" s="76" t="n"/>
       <c r="W11" s="76" t="n"/>
       <c r="X11" s="76" t="n"/>
       <c r="Y11" s="76" t="n">
         <v>544496</v>
       </c>
-      <c r="Z11" s="76" t="n">
+      <c r="Z11" s="77" t="n">
         <v>150000</v>
       </c>
       <c r="AA11" s="76" t="n">
@@ -2980,22 +3654,22 @@
       <c r="AB11" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AC11" s="76" t="n">
+      <c r="AC11" s="78" t="n">
         <v>150000</v>
       </c>
-      <c r="AD11" s="76" t="n">
+      <c r="AD11" s="78" t="n">
         <v>100000</v>
       </c>
       <c r="AE11" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AF11" s="76" t="n">
+      <c r="AF11" s="78" t="n">
         <v>100000</v>
       </c>
       <c r="AG11" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AH11" s="76" t="n">
+      <c r="AH11" s="78" t="n">
         <v>44496</v>
       </c>
       <c r="AI11" s="76" t="n">
@@ -3130,7 +3804,7 @@
       </c>
       <c r="D12" s="54" t="n"/>
       <c r="E12" s="54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="56" t="n">
         <v>46142</v>
@@ -3140,7 +3814,7 @@
           <t>曹</t>
         </is>
       </c>
-      <c r="H12" s="77" t="n">
+      <c r="H12" s="79" t="n">
         <v>42900</v>
       </c>
       <c r="I12" s="54" t="inlineStr">
@@ -3152,152 +3826,152 @@
         <v>30</v>
       </c>
       <c r="K12" s="54" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="L12" s="54" t="inlineStr">
         <is>
           <t>电汇</t>
         </is>
       </c>
-      <c r="M12" s="77" t="n"/>
-      <c r="N12" s="77" t="n">
+      <c r="M12" s="79" t="n"/>
+      <c r="N12" s="79" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="O12" s="79" t="n"/>
+      <c r="P12" s="79" t="n"/>
+      <c r="Q12" s="79" t="n"/>
+      <c r="R12" s="79" t="n"/>
+      <c r="S12" s="79" t="n"/>
+      <c r="T12" s="79" t="n"/>
+      <c r="U12" s="79" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="V12" s="79" t="n"/>
+      <c r="W12" s="79" t="n"/>
+      <c r="X12" s="79" t="n"/>
+      <c r="Y12" s="79" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="Z12" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="80" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AC12" s="78" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AD12" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="78" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AF12" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="79" t="n"/>
+      <c r="AN12" s="79" t="n">
+        <v>42900</v>
+      </c>
+      <c r="AO12" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="79" t="n">
+        <v>42900</v>
+      </c>
+      <c r="AR12" s="79" t="n">
+        <v>87000</v>
+      </c>
+      <c r="AS12" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="79" t="n">
         <v>56635</v>
       </c>
-      <c r="O12" s="77" t="n"/>
-      <c r="P12" s="77" t="n"/>
-      <c r="Q12" s="77" t="n"/>
-      <c r="R12" s="77" t="n"/>
-      <c r="S12" s="77" t="n">
+      <c r="AU12" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="79" t="n">
+        <v>51400</v>
+      </c>
+      <c r="AW12" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" s="79" t="n">
+        <v>143810</v>
+      </c>
+      <c r="AY12" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="79" t="n">
+        <v>40050</v>
+      </c>
+      <c r="BA12" s="79" t="n">
+        <v>27210</v>
+      </c>
+      <c r="BB12" s="79" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="BC12" s="79" t="n">
+        <v>51400</v>
+      </c>
+      <c r="BD12" s="79" t="n">
+        <v>192470</v>
+      </c>
+      <c r="BE12" s="79" t="n">
+        <v>46000</v>
+      </c>
+      <c r="BF12" s="54" t="inlineStr">
+        <is>
+          <t>曹</t>
+        </is>
+      </c>
+      <c r="BG12" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" s="79" t="n">
+        <v>42900</v>
+      </c>
+      <c r="BJ12" s="79" t="n">
+        <v>87000</v>
+      </c>
+      <c r="BK12" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" s="79" t="n">
         <v>56635</v>
       </c>
-      <c r="T12" s="77" t="n"/>
-      <c r="U12" s="77" t="n"/>
-      <c r="V12" s="77" t="n"/>
-      <c r="W12" s="77" t="n"/>
-      <c r="X12" s="77" t="n"/>
-      <c r="Y12" s="77" t="n">
-        <v>186535</v>
-      </c>
-      <c r="Z12" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="77" t="n">
-        <v>42900</v>
-      </c>
-      <c r="AC12" s="77" t="n">
-        <v>87000</v>
-      </c>
-      <c r="AD12" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="77" t="n">
-        <v>56635</v>
-      </c>
-      <c r="AF12" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="77" t="n"/>
-      <c r="AN12" s="77" t="n">
-        <v>42900</v>
-      </c>
-      <c r="AO12" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="77" t="n">
-        <v>42900</v>
-      </c>
-      <c r="AR12" s="77" t="n">
-        <v>87000</v>
-      </c>
-      <c r="AS12" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" s="77" t="n">
-        <v>56635</v>
-      </c>
-      <c r="AU12" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" s="77" t="n">
-        <v>51400</v>
-      </c>
-      <c r="AW12" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" s="77" t="n">
-        <v>143810</v>
-      </c>
-      <c r="AY12" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" s="77" t="n">
-        <v>40050</v>
-      </c>
-      <c r="BA12" s="77" t="n">
-        <v>27210</v>
-      </c>
-      <c r="BB12" s="77" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="BC12" s="77" t="n">
-        <v>51400</v>
-      </c>
-      <c r="BD12" s="77" t="n">
-        <v>192470</v>
-      </c>
-      <c r="BE12" s="77" t="n">
-        <v>46000</v>
-      </c>
-      <c r="BF12" s="54" t="inlineStr">
-        <is>
-          <t>曹</t>
-        </is>
-      </c>
-      <c r="BG12" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH12" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI12" s="77" t="n">
-        <v>42900</v>
-      </c>
-      <c r="BJ12" s="77" t="n">
-        <v>87000</v>
-      </c>
-      <c r="BK12" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL12" s="77" t="n">
-        <v>56635</v>
-      </c>
-      <c r="BM12" s="77" t="n">
+      <c r="BM12" s="79" t="n">
         <v>0</v>
       </c>
       <c r="BN12" s="54" t="n">
@@ -3367,14 +4041,18 @@
         </is>
       </c>
       <c r="M13" s="76" t="n"/>
-      <c r="N13" s="76" t="n"/>
+      <c r="N13" s="76" t="n">
+        <v>537386.0079999999</v>
+      </c>
       <c r="O13" s="76" t="n"/>
       <c r="P13" s="76" t="n"/>
       <c r="Q13" s="76" t="n"/>
       <c r="R13" s="76" t="n"/>
       <c r="S13" s="76" t="n"/>
       <c r="T13" s="76" t="n"/>
-      <c r="U13" s="76" t="n"/>
+      <c r="U13" s="76" t="n">
+        <v>537386.0079999999</v>
+      </c>
       <c r="V13" s="76" t="n"/>
       <c r="W13" s="76" t="n"/>
       <c r="X13" s="76" t="n"/>
@@ -3399,7 +4077,7 @@
       <c r="AE13" s="76" t="n">
         <v>32400</v>
       </c>
-      <c r="AF13" s="76" t="n">
+      <c r="AF13" s="81" t="n">
         <v>628532.51</v>
       </c>
       <c r="AG13" s="76" t="n">
@@ -3550,7 +4228,7 @@
           <t>曹</t>
         </is>
       </c>
-      <c r="H14" s="78" t="n">
+      <c r="H14" s="82" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="42" t="inlineStr">
@@ -3569,123 +4247,123 @@
           <t>商承/银承/电汇</t>
         </is>
       </c>
-      <c r="M14" s="78" t="inlineStr">
+      <c r="M14" s="82" t="inlineStr">
         <is>
           <t>商承不能只给6个月以上的</t>
         </is>
       </c>
-      <c r="N14" s="78" t="n">
+      <c r="N14" s="82" t="n">
         <v>883975.46</v>
       </c>
-      <c r="O14" s="78" t="n"/>
-      <c r="P14" s="78" t="n"/>
-      <c r="Q14" s="78" t="n"/>
-      <c r="R14" s="78" t="n"/>
-      <c r="S14" s="78" t="n">
+      <c r="O14" s="82" t="n"/>
+      <c r="P14" s="82" t="n"/>
+      <c r="Q14" s="82" t="n"/>
+      <c r="R14" s="82" t="n"/>
+      <c r="S14" s="82" t="n">
         <v>883975.46</v>
       </c>
-      <c r="T14" s="78" t="n"/>
-      <c r="U14" s="78" t="n"/>
-      <c r="V14" s="78" t="n"/>
-      <c r="W14" s="78" t="n"/>
-      <c r="X14" s="78" t="n"/>
-      <c r="Y14" s="78" t="n">
+      <c r="T14" s="82" t="n"/>
+      <c r="U14" s="82" t="n"/>
+      <c r="V14" s="82" t="n"/>
+      <c r="W14" s="82" t="n"/>
+      <c r="X14" s="82" t="n"/>
+      <c r="Y14" s="82" t="n">
         <v>1097167.46</v>
       </c>
-      <c r="Z14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="78" t="n">
+      <c r="Z14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="82" t="n">
         <v>213192</v>
       </c>
-      <c r="AF14" s="78" t="n">
+      <c r="AF14" s="82" t="n">
         <v>416280</v>
       </c>
-      <c r="AG14" s="78" t="n">
+      <c r="AG14" s="82" t="n">
         <v>265080</v>
       </c>
-      <c r="AH14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="78" t="n">
+      <c r="AH14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="82" t="n">
         <v>202615.46</v>
       </c>
-      <c r="AJ14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" s="78" t="n"/>
-      <c r="AN14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" s="78" t="n">
+      <c r="AJ14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="82" t="n"/>
+      <c r="AN14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" s="82" t="n">
         <v>213192</v>
       </c>
-      <c r="AU14" s="78" t="n">
+      <c r="AU14" s="82" t="n">
         <v>416280</v>
       </c>
-      <c r="AV14" s="78" t="n">
+      <c r="AV14" s="82" t="n">
         <v>265080</v>
       </c>
-      <c r="AW14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" s="78" t="n">
+      <c r="AW14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" s="82" t="n">
         <v>227760</v>
       </c>
-      <c r="AY14" s="78" t="n">
+      <c r="AY14" s="82" t="n">
         <v>998230</v>
       </c>
-      <c r="AZ14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" s="78" t="inlineStr">
+      <c r="AZ14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" s="82" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="BC14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD14" s="78" t="n">
+      <c r="BC14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" s="82" t="n">
         <v>1000000</v>
       </c>
-      <c r="BE14" s="78" t="n">
+      <c r="BE14" s="82" t="n">
         <v>1044516</v>
       </c>
       <c r="BF14" s="42" t="inlineStr">
@@ -3693,25 +4371,25 @@
           <t>曹</t>
         </is>
       </c>
-      <c r="BG14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK14" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL14" s="78" t="n">
+      <c r="BG14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK14" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" s="82" t="n">
         <v>213192</v>
       </c>
-      <c r="BM14" s="78" t="n">
+      <c r="BM14" s="82" t="n">
         <v>883975.46</v>
       </c>
       <c r="BN14" s="42" t="n">
@@ -3786,24 +4464,24 @@
         </is>
       </c>
       <c r="N15" s="76" t="n">
-        <v>191315.42</v>
+        <v>313052.336</v>
       </c>
       <c r="O15" s="76" t="n"/>
       <c r="P15" s="76" t="n"/>
       <c r="Q15" s="76" t="n"/>
       <c r="R15" s="76" t="n"/>
-      <c r="S15" s="76" t="n">
-        <v>191315.42</v>
-      </c>
+      <c r="S15" s="76" t="n"/>
       <c r="T15" s="76" t="n"/>
-      <c r="U15" s="76" t="n"/>
+      <c r="U15" s="76" t="n">
+        <v>313052.336</v>
+      </c>
       <c r="V15" s="76" t="n"/>
       <c r="W15" s="76" t="n"/>
       <c r="X15" s="76" t="n"/>
       <c r="Y15" s="76" t="n">
         <v>391315.42</v>
       </c>
-      <c r="Z15" s="76" t="n">
+      <c r="Z15" s="83" t="n">
         <v>200000</v>
       </c>
       <c r="AA15" s="76" t="n">
@@ -3824,7 +4502,7 @@
       <c r="AF15" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AG15" s="76" t="n">
+      <c r="AG15" s="78" t="n">
         <v>191315.42</v>
       </c>
       <c r="AH15" s="76" t="n">
@@ -3993,17 +4671,17 @@
       </c>
       <c r="M16" s="76" t="n"/>
       <c r="N16" s="76" t="n">
-        <v>1723380.29</v>
+        <v>2303081.832</v>
       </c>
       <c r="O16" s="76" t="n"/>
       <c r="P16" s="76" t="n"/>
       <c r="Q16" s="76" t="n"/>
       <c r="R16" s="76" t="n"/>
-      <c r="S16" s="76" t="n">
-        <v>1723380.29</v>
-      </c>
+      <c r="S16" s="76" t="n"/>
       <c r="T16" s="76" t="n"/>
-      <c r="U16" s="76" t="n"/>
+      <c r="U16" s="76" t="n">
+        <v>2303081.832</v>
+      </c>
       <c r="V16" s="76" t="n"/>
       <c r="W16" s="76" t="n"/>
       <c r="X16" s="76" t="n"/>
@@ -4019,25 +4697,25 @@
       <c r="AB16" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AC16" s="76" t="n">
+      <c r="AC16" s="84" t="n">
         <v>290880</v>
       </c>
-      <c r="AD16" s="76" t="n">
+      <c r="AD16" s="78" t="n">
         <v>401104</v>
       </c>
-      <c r="AE16" s="76" t="n">
+      <c r="AE16" s="78" t="n">
         <v>369600</v>
       </c>
-      <c r="AF16" s="76" t="n">
+      <c r="AF16" s="78" t="n">
         <v>350272</v>
       </c>
-      <c r="AG16" s="76" t="n">
+      <c r="AG16" s="78" t="n">
         <v>456192</v>
       </c>
-      <c r="AH16" s="76" t="n">
+      <c r="AH16" s="78" t="n">
         <v>215702</v>
       </c>
-      <c r="AI16" s="76" t="n">
+      <c r="AI16" s="78" t="n">
         <v>331614.29</v>
       </c>
       <c r="AJ16" s="76" t="n">
@@ -4200,14 +4878,14 @@
       </c>
       <c r="M17" s="76" t="n"/>
       <c r="N17" s="76" t="n">
-        <v>46005.03</v>
+        <v>74244.024</v>
       </c>
       <c r="O17" s="76" t="n"/>
       <c r="P17" s="76" t="n"/>
       <c r="Q17" s="76" t="n"/>
       <c r="R17" s="76" t="n"/>
       <c r="S17" s="76" t="n">
-        <v>46005.03</v>
+        <v>74244.024</v>
       </c>
       <c r="T17" s="76" t="n"/>
       <c r="U17" s="76" t="n"/>
@@ -4217,16 +4895,16 @@
       <c r="Y17" s="76" t="n">
         <v>92805.03</v>
       </c>
-      <c r="Z17" s="76" t="n">
+      <c r="Z17" s="85" t="n">
         <v>23400</v>
       </c>
       <c r="AA17" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AB17" s="76" t="n">
+      <c r="AB17" s="78" t="n">
         <v>23400</v>
       </c>
-      <c r="AC17" s="76" t="n">
+      <c r="AC17" s="78" t="n">
         <v>22750</v>
       </c>
       <c r="AD17" s="76" t="n">
@@ -4235,7 +4913,7 @@
       <c r="AE17" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AF17" s="76" t="n">
+      <c r="AF17" s="78" t="n">
         <v>23255.03</v>
       </c>
       <c r="AG17" s="76" t="n">
@@ -4407,14 +5085,14 @@
       </c>
       <c r="M18" s="76" t="n"/>
       <c r="N18" s="76" t="n">
-        <v>1140615.78</v>
+        <v>2485510.846</v>
       </c>
       <c r="O18" s="76" t="n"/>
       <c r="P18" s="76" t="n"/>
       <c r="Q18" s="76" t="n"/>
       <c r="R18" s="76" t="n"/>
       <c r="S18" s="76" t="n">
-        <v>1140615.78</v>
+        <v>2485510.846</v>
       </c>
       <c r="T18" s="76" t="n"/>
       <c r="U18" s="76" t="n"/>
@@ -4433,13 +5111,13 @@
       <c r="AB18" s="76" t="n">
         <v>997058</v>
       </c>
-      <c r="AC18" s="76" t="n">
+      <c r="AC18" s="86" t="n">
         <v>1413056</v>
       </c>
-      <c r="AD18" s="76" t="n">
+      <c r="AD18" s="78" t="n">
         <v>402368</v>
       </c>
-      <c r="AE18" s="76" t="n">
+      <c r="AE18" s="78" t="n">
         <v>738247.78</v>
       </c>
       <c r="AF18" s="76" t="n">
@@ -4613,12 +5291,16 @@
         </is>
       </c>
       <c r="M19" s="76" t="n"/>
-      <c r="N19" s="76" t="n"/>
+      <c r="N19" s="76" t="n">
+        <v>26208</v>
+      </c>
       <c r="O19" s="76" t="n"/>
       <c r="P19" s="76" t="n"/>
       <c r="Q19" s="76" t="n"/>
       <c r="R19" s="76" t="n"/>
-      <c r="S19" s="76" t="n"/>
+      <c r="S19" s="76" t="n">
+        <v>26208</v>
+      </c>
       <c r="T19" s="76" t="n"/>
       <c r="U19" s="76" t="n"/>
       <c r="V19" s="76" t="n"/>
@@ -4630,13 +5312,13 @@
       <c r="Z19" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AA19" s="76" t="n">
+      <c r="AA19" s="87" t="n">
         <v>12600</v>
       </c>
       <c r="AB19" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AC19" s="76" t="n">
+      <c r="AC19" s="78" t="n">
         <v>20160</v>
       </c>
       <c r="AD19" s="76" t="n">
@@ -4817,17 +5499,17 @@
       </c>
       <c r="M20" s="76" t="n"/>
       <c r="N20" s="76" t="n">
-        <v>296313.23</v>
+        <v>516609.784</v>
       </c>
       <c r="O20" s="76" t="n"/>
       <c r="P20" s="76" t="n"/>
       <c r="Q20" s="76" t="n"/>
       <c r="R20" s="76" t="n"/>
-      <c r="S20" s="76" t="n">
-        <v>296313.23</v>
-      </c>
+      <c r="S20" s="76" t="n"/>
       <c r="T20" s="76" t="n"/>
-      <c r="U20" s="76" t="n"/>
+      <c r="U20" s="76" t="n">
+        <v>516609.784</v>
+      </c>
       <c r="V20" s="76" t="n"/>
       <c r="W20" s="76" t="n"/>
       <c r="X20" s="76" t="n"/>
@@ -4837,22 +5519,22 @@
       <c r="Z20" s="76" t="n">
         <v>30222</v>
       </c>
-      <c r="AA20" s="76" t="n">
+      <c r="AA20" s="88" t="n">
         <v>191079</v>
       </c>
       <c r="AB20" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AC20" s="76" t="n">
+      <c r="AC20" s="78" t="n">
         <v>128148</v>
       </c>
-      <c r="AD20" s="76" t="n">
+      <c r="AD20" s="78" t="n">
         <v>101702</v>
       </c>
-      <c r="AE20" s="76" t="n">
+      <c r="AE20" s="78" t="n">
         <v>99652</v>
       </c>
-      <c r="AF20" s="76" t="n">
+      <c r="AF20" s="78" t="n">
         <v>94959.23</v>
       </c>
       <c r="AG20" s="76" t="n">
@@ -5024,14 +5706,14 @@
       </c>
       <c r="M21" s="76" t="n"/>
       <c r="N21" s="76" t="n">
-        <v>105473.47</v>
+        <v>184018.776</v>
       </c>
       <c r="O21" s="76" t="n"/>
       <c r="P21" s="76" t="n"/>
       <c r="Q21" s="76" t="n"/>
       <c r="R21" s="76" t="n"/>
       <c r="S21" s="76" t="n">
-        <v>105473.47</v>
+        <v>184018.776</v>
       </c>
       <c r="T21" s="76" t="n"/>
       <c r="U21" s="76" t="n"/>
@@ -5053,13 +5735,13 @@
       <c r="AC21" s="76" t="n">
         <v>35510</v>
       </c>
-      <c r="AD21" s="76" t="n">
+      <c r="AD21" s="89" t="n">
         <v>89040</v>
       </c>
       <c r="AE21" s="76" t="n">
         <v>-4000</v>
       </c>
-      <c r="AF21" s="76" t="n">
+      <c r="AF21" s="78" t="n">
         <v>109473.47</v>
       </c>
       <c r="AG21" s="76" t="n">
@@ -5442,17 +6124,17 @@
       </c>
       <c r="M23" s="76" t="n"/>
       <c r="N23" s="76" t="n">
-        <v>35972.25</v>
+        <v>38509.32</v>
       </c>
       <c r="O23" s="76" t="n"/>
       <c r="P23" s="76" t="n"/>
       <c r="Q23" s="76" t="n"/>
       <c r="R23" s="76" t="n"/>
-      <c r="S23" s="76" t="n">
-        <v>35972.25</v>
-      </c>
+      <c r="S23" s="76" t="n"/>
       <c r="T23" s="76" t="n"/>
-      <c r="U23" s="76" t="n"/>
+      <c r="U23" s="76" t="n">
+        <v>38509.32</v>
+      </c>
       <c r="V23" s="76" t="n"/>
       <c r="W23" s="76" t="n"/>
       <c r="X23" s="76" t="n"/>
@@ -5465,16 +6147,16 @@
       <c r="AA23" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AB23" s="76" t="n">
+      <c r="AB23" s="90" t="n">
         <v>12164.4</v>
       </c>
       <c r="AC23" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AD23" s="76" t="n">
+      <c r="AD23" s="78" t="n">
         <v>12164.4</v>
       </c>
-      <c r="AE23" s="76" t="n">
+      <c r="AE23" s="78" t="n">
         <v>23807.85</v>
       </c>
       <c r="AF23" s="76" t="n">
@@ -5649,14 +6331,14 @@
       </c>
       <c r="M24" s="76" t="n"/>
       <c r="N24" s="76" t="n">
-        <v>159345.93</v>
+        <v>242156.744</v>
       </c>
       <c r="O24" s="76" t="n"/>
       <c r="P24" s="76" t="n"/>
       <c r="Q24" s="76" t="n"/>
       <c r="R24" s="76" t="n"/>
       <c r="S24" s="76" t="n">
-        <v>159345.93</v>
+        <v>242156.744</v>
       </c>
       <c r="T24" s="76" t="n"/>
       <c r="U24" s="76" t="n"/>
@@ -5669,25 +6351,25 @@
       <c r="Z24" s="76" t="n">
         <v>15980</v>
       </c>
-      <c r="AA24" s="76" t="n">
+      <c r="AA24" s="91" t="n">
         <v>47940</v>
       </c>
-      <c r="AB24" s="76" t="n">
+      <c r="AB24" s="78" t="n">
         <v>47000</v>
       </c>
-      <c r="AC24" s="76" t="n">
+      <c r="AC24" s="78" t="n">
         <v>32430</v>
       </c>
-      <c r="AD24" s="76" t="n">
+      <c r="AD24" s="78" t="n">
         <v>31960</v>
       </c>
-      <c r="AE24" s="76" t="n">
+      <c r="AE24" s="78" t="n">
         <v>15980</v>
       </c>
-      <c r="AF24" s="76" t="n">
+      <c r="AF24" s="78" t="n">
         <v>46060</v>
       </c>
-      <c r="AG24" s="76" t="n">
+      <c r="AG24" s="78" t="n">
         <v>65345.93</v>
       </c>
       <c r="AH24" s="76" t="n">
@@ -5855,12 +6537,16 @@
         </is>
       </c>
       <c r="M25" s="76" t="n"/>
-      <c r="N25" s="76" t="n"/>
+      <c r="N25" s="76" t="n">
+        <v>10298.88</v>
+      </c>
       <c r="O25" s="76" t="n"/>
       <c r="P25" s="76" t="n"/>
       <c r="Q25" s="76" t="n"/>
       <c r="R25" s="76" t="n"/>
-      <c r="S25" s="76" t="n"/>
+      <c r="S25" s="76" t="n">
+        <v>10298.88</v>
+      </c>
       <c r="T25" s="76" t="n"/>
       <c r="U25" s="76" t="n"/>
       <c r="V25" s="76" t="n"/>
@@ -5872,7 +6558,7 @@
       <c r="Z25" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AA25" s="76" t="n">
+      <c r="AA25" s="92" t="n">
         <v>12873.6</v>
       </c>
       <c r="AB25" s="76" t="n">
@@ -6059,14 +6745,14 @@
       </c>
       <c r="M26" s="76" t="n"/>
       <c r="N26" s="76" t="n">
-        <v>109252.96</v>
+        <v>122456.768</v>
       </c>
       <c r="O26" s="76" t="n"/>
       <c r="P26" s="76" t="n"/>
       <c r="Q26" s="76" t="n"/>
       <c r="R26" s="76" t="n"/>
       <c r="S26" s="76" t="n">
-        <v>109252.96</v>
+        <v>122456.768</v>
       </c>
       <c r="T26" s="76" t="n"/>
       <c r="U26" s="76" t="n"/>
@@ -6085,16 +6771,16 @@
       <c r="AB26" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AC26" s="76" t="n">
+      <c r="AC26" s="93" t="n">
         <v>21909</v>
       </c>
-      <c r="AD26" s="76" t="n">
+      <c r="AD26" s="78" t="n">
         <v>21909</v>
       </c>
-      <c r="AE26" s="76" t="n">
+      <c r="AE26" s="78" t="n">
         <v>43818</v>
       </c>
-      <c r="AF26" s="76" t="n">
+      <c r="AF26" s="78" t="n">
         <v>43525.96</v>
       </c>
       <c r="AG26" s="76" t="n">
@@ -6469,14 +7155,14 @@
       </c>
       <c r="M28" s="76" t="n"/>
       <c r="N28" s="76" t="n">
-        <v>6780714.6</v>
+        <v>9311155.68</v>
       </c>
       <c r="O28" s="76" t="n"/>
       <c r="P28" s="76" t="n"/>
       <c r="Q28" s="76" t="n"/>
       <c r="R28" s="76" t="n"/>
       <c r="S28" s="76" t="n">
-        <v>6780714.6</v>
+        <v>9311155.68</v>
       </c>
       <c r="T28" s="76" t="n"/>
       <c r="U28" s="76" t="n"/>
@@ -6492,16 +7178,16 @@
       <c r="AA28" s="76" t="n">
         <v>531750</v>
       </c>
-      <c r="AB28" s="76" t="n">
+      <c r="AB28" s="94" t="n">
         <v>2544605</v>
       </c>
-      <c r="AC28" s="76" t="n">
+      <c r="AC28" s="78" t="n">
         <v>2401250</v>
       </c>
-      <c r="AD28" s="76" t="n">
+      <c r="AD28" s="78" t="n">
         <v>1900700</v>
       </c>
-      <c r="AE28" s="76" t="n">
+      <c r="AE28" s="78" t="n">
         <v>2478764.6</v>
       </c>
       <c r="AF28" s="76" t="n">
@@ -6676,16 +7362,16 @@
       </c>
       <c r="M29" s="76" t="n"/>
       <c r="N29" s="76" t="n">
-        <v>858213.14</v>
+        <v>1447682.512</v>
       </c>
       <c r="O29" s="76" t="n"/>
       <c r="P29" s="76" t="n"/>
       <c r="Q29" s="76" t="n"/>
-      <c r="R29" s="76" t="n">
-        <v>858213.14</v>
-      </c>
+      <c r="R29" s="76" t="n"/>
       <c r="S29" s="76" t="n"/>
-      <c r="T29" s="76" t="n"/>
+      <c r="T29" s="76" t="n">
+        <v>1447682.512</v>
+      </c>
       <c r="U29" s="76" t="n"/>
       <c r="V29" s="76" t="n"/>
       <c r="W29" s="76" t="n"/>
@@ -6699,16 +7385,16 @@
       <c r="AA29" s="76" t="n">
         <v>61380</v>
       </c>
-      <c r="AB29" s="76" t="n">
+      <c r="AB29" s="95" t="n">
         <v>245520</v>
       </c>
-      <c r="AC29" s="76" t="n">
+      <c r="AC29" s="78" t="n">
         <v>368280</v>
       </c>
-      <c r="AD29" s="76" t="n">
+      <c r="AD29" s="78" t="n">
         <v>276210</v>
       </c>
-      <c r="AE29" s="76" t="n">
+      <c r="AE29" s="78" t="n">
         <v>582003.14</v>
       </c>
       <c r="AF29" s="76" t="n">
@@ -6883,13 +7569,13 @@
       </c>
       <c r="M30" s="76" t="n"/>
       <c r="N30" s="76" t="n">
-        <v>34197</v>
+        <v>39237.6</v>
       </c>
       <c r="O30" s="76" t="n"/>
       <c r="P30" s="76" t="n"/>
       <c r="Q30" s="76" t="n"/>
       <c r="R30" s="76" t="n">
-        <v>34197</v>
+        <v>39237.6</v>
       </c>
       <c r="S30" s="76" t="n"/>
       <c r="T30" s="76" t="n"/>
@@ -6906,25 +7592,25 @@
       <c r="AA30" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AB30" s="76" t="n">
+      <c r="AB30" s="96" t="n">
         <v>8350</v>
       </c>
       <c r="AC30" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AD30" s="76" t="n">
+      <c r="AD30" s="78" t="n">
         <v>6950</v>
       </c>
-      <c r="AE30" s="76" t="n">
+      <c r="AE30" s="78" t="n">
         <v>6500</v>
       </c>
       <c r="AF30" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AG30" s="76" t="n">
+      <c r="AG30" s="78" t="n">
         <v>6500</v>
       </c>
-      <c r="AH30" s="76" t="n">
+      <c r="AH30" s="78" t="n">
         <v>14247</v>
       </c>
       <c r="AI30" s="76" t="n">
@@ -7090,13 +7776,13 @@
       </c>
       <c r="M31" s="76" t="n"/>
       <c r="N31" s="76" t="n">
-        <v>144000</v>
+        <v>151200</v>
       </c>
       <c r="O31" s="76" t="n"/>
       <c r="P31" s="76" t="n"/>
       <c r="Q31" s="76" t="n"/>
       <c r="R31" s="76" t="n">
-        <v>144000</v>
+        <v>151200</v>
       </c>
       <c r="S31" s="76" t="n"/>
       <c r="T31" s="76" t="n"/>
@@ -7107,25 +7793,25 @@
       <c r="Y31" s="76" t="n">
         <v>189000</v>
       </c>
-      <c r="Z31" s="76" t="n">
+      <c r="Z31" s="97" t="n">
         <v>45000</v>
       </c>
-      <c r="AA31" s="76" t="n">
+      <c r="AA31" s="78" t="n">
         <v>15000</v>
       </c>
-      <c r="AB31" s="76" t="n">
+      <c r="AB31" s="78" t="n">
         <v>15000</v>
       </c>
-      <c r="AC31" s="76" t="n">
+      <c r="AC31" s="78" t="n">
         <v>45000</v>
       </c>
-      <c r="AD31" s="76" t="n">
+      <c r="AD31" s="78" t="n">
         <v>45000</v>
       </c>
-      <c r="AE31" s="76" t="n">
+      <c r="AE31" s="78" t="n">
         <v>15000</v>
       </c>
-      <c r="AF31" s="76" t="n">
+      <c r="AF31" s="78" t="n">
         <v>9000</v>
       </c>
       <c r="AG31" s="76" t="n">
@@ -7297,16 +7983,16 @@
       </c>
       <c r="M32" s="76" t="n"/>
       <c r="N32" s="76" t="n">
-        <v>1430588.85</v>
+        <v>1754839.08</v>
       </c>
       <c r="O32" s="76" t="n"/>
       <c r="P32" s="76" t="n"/>
       <c r="Q32" s="76" t="n"/>
-      <c r="R32" s="76" t="n">
-        <v>1430588.85</v>
-      </c>
+      <c r="R32" s="76" t="n"/>
       <c r="S32" s="76" t="n"/>
-      <c r="T32" s="76" t="n"/>
+      <c r="T32" s="76" t="n">
+        <v>1754839.08</v>
+      </c>
       <c r="U32" s="76" t="n"/>
       <c r="V32" s="76" t="n"/>
       <c r="W32" s="76" t="n"/>
@@ -7323,13 +8009,13 @@
       <c r="AB32" s="76" t="n">
         <v>170000</v>
       </c>
-      <c r="AC32" s="76" t="n">
+      <c r="AC32" s="98" t="n">
         <v>425000</v>
       </c>
-      <c r="AD32" s="76" t="n">
+      <c r="AD32" s="78" t="n">
         <v>677500</v>
       </c>
-      <c r="AE32" s="76" t="n">
+      <c r="AE32" s="78" t="n">
         <v>753088.85</v>
       </c>
       <c r="AF32" s="76" t="n">
@@ -7504,13 +8190,13 @@
       </c>
       <c r="M33" s="76" t="n"/>
       <c r="N33" s="76" t="n">
-        <v>197960</v>
+        <v>238096</v>
       </c>
       <c r="O33" s="76" t="n"/>
       <c r="P33" s="76" t="n"/>
       <c r="Q33" s="76" t="n"/>
       <c r="R33" s="76" t="n">
-        <v>197960</v>
+        <v>238096</v>
       </c>
       <c r="S33" s="76" t="n"/>
       <c r="T33" s="76" t="n"/>
@@ -7524,19 +8210,19 @@
       <c r="Z33" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AA33" s="76" t="n">
+      <c r="AA33" s="99" t="n">
         <v>99660</v>
       </c>
       <c r="AB33" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AC33" s="76" t="n">
+      <c r="AC33" s="78" t="n">
         <v>99660</v>
       </c>
       <c r="AD33" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AE33" s="76" t="n">
+      <c r="AE33" s="78" t="n">
         <v>98300</v>
       </c>
       <c r="AF33" s="76" t="n">
@@ -7710,11 +8396,15 @@
         </is>
       </c>
       <c r="M34" s="76" t="n"/>
-      <c r="N34" s="76" t="n"/>
-      <c r="O34" s="79" t="n"/>
+      <c r="N34" s="76" t="n">
+        <v>302847.2</v>
+      </c>
+      <c r="O34" s="100" t="n"/>
       <c r="P34" s="76" t="n"/>
       <c r="Q34" s="76" t="n"/>
-      <c r="R34" s="76" t="n"/>
+      <c r="R34" s="76" t="n">
+        <v>302847.2</v>
+      </c>
       <c r="S34" s="76" t="n"/>
       <c r="T34" s="76" t="n"/>
       <c r="U34" s="76" t="n"/>
@@ -7724,10 +8414,10 @@
       <c r="Y34" s="76" t="n">
         <v>378559</v>
       </c>
-      <c r="Z34" s="76" t="n">
+      <c r="Z34" s="101" t="n">
         <v>246225</v>
       </c>
-      <c r="AA34" s="76" t="n">
+      <c r="AA34" s="78" t="n">
         <v>132334</v>
       </c>
       <c r="AB34" s="76" t="n">
@@ -7914,13 +8604,13 @@
       </c>
       <c r="M35" s="76" t="n"/>
       <c r="N35" s="76" t="n">
-        <v>220153.13</v>
-      </c>
-      <c r="O35" s="80" t="n"/>
+        <v>260074.504</v>
+      </c>
+      <c r="O35" s="102" t="n"/>
       <c r="P35" s="76" t="n"/>
       <c r="Q35" s="76" t="n"/>
       <c r="R35" s="76" t="n">
-        <v>220153.13</v>
+        <v>260074.504</v>
       </c>
       <c r="S35" s="76" t="n"/>
       <c r="T35" s="76" t="n"/>
@@ -7931,25 +8621,25 @@
       <c r="Y35" s="76" t="n">
         <v>325093.13</v>
       </c>
-      <c r="Z35" s="76" t="n">
+      <c r="Z35" s="103" t="n">
         <v>87450</v>
       </c>
       <c r="AA35" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AB35" s="76" t="n">
+      <c r="AB35" s="78" t="n">
         <v>17490</v>
       </c>
-      <c r="AC35" s="76" t="n">
+      <c r="AC35" s="78" t="n">
         <v>88800</v>
       </c>
-      <c r="AD35" s="76" t="n">
+      <c r="AD35" s="78" t="n">
         <v>56280</v>
       </c>
-      <c r="AE35" s="76" t="n">
+      <c r="AE35" s="78" t="n">
         <v>51410</v>
       </c>
-      <c r="AF35" s="76" t="n">
+      <c r="AF35" s="78" t="n">
         <v>23663.13</v>
       </c>
       <c r="AG35" s="76" t="n">
@@ -8324,13 +9014,13 @@
       </c>
       <c r="M37" s="76" t="n"/>
       <c r="N37" s="76" t="n">
-        <v>170552.37</v>
+        <v>244434.659</v>
       </c>
       <c r="O37" s="76" t="n"/>
       <c r="P37" s="76" t="n"/>
       <c r="Q37" s="76" t="n"/>
       <c r="R37" s="76" t="n">
-        <v>170552.37</v>
+        <v>244434.659</v>
       </c>
       <c r="S37" s="76" t="n"/>
       <c r="T37" s="76" t="n"/>
@@ -8341,10 +9031,10 @@
       <c r="Y37" s="76" t="n">
         <v>349192.37</v>
       </c>
-      <c r="Z37" s="76" t="n">
+      <c r="Z37" s="104" t="n">
         <v>178640</v>
       </c>
-      <c r="AA37" s="76" t="n">
+      <c r="AA37" s="78" t="n">
         <v>170552.37</v>
       </c>
       <c r="AB37" s="76" t="n">
@@ -8531,13 +9221,13 @@
       </c>
       <c r="M38" s="76" t="n"/>
       <c r="N38" s="76" t="n">
-        <v>58732.71</v>
+        <v>90906.16800000001</v>
       </c>
       <c r="O38" s="76" t="n"/>
       <c r="P38" s="76" t="n"/>
       <c r="Q38" s="76" t="n"/>
       <c r="R38" s="76" t="n">
-        <v>58732.71</v>
+        <v>90906.16800000001</v>
       </c>
       <c r="S38" s="76" t="n"/>
       <c r="T38" s="76" t="n"/>
@@ -8551,7 +9241,7 @@
       <c r="Z38" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AA38" s="76" t="n">
+      <c r="AA38" s="105" t="n">
         <v>54900</v>
       </c>
       <c r="AB38" s="76" t="n">
@@ -8560,13 +9250,13 @@
       <c r="AC38" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AD38" s="76" t="n">
+      <c r="AD38" s="78" t="n">
         <v>30500</v>
       </c>
-      <c r="AE38" s="76" t="n">
+      <c r="AE38" s="78" t="n">
         <v>15860</v>
       </c>
-      <c r="AF38" s="76" t="n">
+      <c r="AF38" s="78" t="n">
         <v>12372.71</v>
       </c>
       <c r="AG38" s="76" t="n">
@@ -8738,16 +9428,16 @@
       </c>
       <c r="M39" s="76" t="n"/>
       <c r="N39" s="76" t="n">
-        <v>36100</v>
+        <v>59280</v>
       </c>
       <c r="O39" s="76" t="n"/>
       <c r="P39" s="76" t="n"/>
       <c r="Q39" s="76" t="n"/>
-      <c r="R39" s="76" t="n">
-        <v>36100</v>
-      </c>
+      <c r="R39" s="76" t="n"/>
       <c r="S39" s="76" t="n"/>
-      <c r="T39" s="76" t="n"/>
+      <c r="T39" s="76" t="n">
+        <v>59280</v>
+      </c>
       <c r="U39" s="76" t="n"/>
       <c r="V39" s="76" t="n"/>
       <c r="W39" s="76" t="n"/>
@@ -8758,13 +9448,13 @@
       <c r="Z39" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AA39" s="76" t="n">
+      <c r="AA39" s="106" t="n">
         <v>19000</v>
       </c>
-      <c r="AB39" s="76" t="n">
+      <c r="AB39" s="78" t="n">
         <v>19000</v>
       </c>
-      <c r="AC39" s="76" t="n">
+      <c r="AC39" s="78" t="n">
         <v>19000</v>
       </c>
       <c r="AD39" s="76" t="n">
@@ -8773,7 +9463,7 @@
       <c r="AE39" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AF39" s="76" t="n">
+      <c r="AF39" s="78" t="n">
         <v>17100</v>
       </c>
       <c r="AG39" s="76" t="n">
@@ -8945,15 +9635,15 @@
       </c>
       <c r="M40" s="76" t="n"/>
       <c r="N40" s="76" t="n">
-        <v>112860.5</v>
+        <v>400124.4</v>
       </c>
       <c r="O40" s="76" t="n"/>
       <c r="P40" s="76" t="n"/>
       <c r="Q40" s="76" t="n"/>
-      <c r="R40" s="76" t="n">
-        <v>112860.5</v>
-      </c>
-      <c r="S40" s="76" t="n"/>
+      <c r="R40" s="76" t="n"/>
+      <c r="S40" s="76" t="n">
+        <v>400124.4</v>
+      </c>
       <c r="T40" s="76" t="n"/>
       <c r="U40" s="76" t="n"/>
       <c r="V40" s="76" t="n"/>
@@ -8962,22 +9652,22 @@
       <c r="Y40" s="76" t="n">
         <v>500155.5</v>
       </c>
-      <c r="Z40" s="76" t="n">
+      <c r="Z40" s="107" t="n">
         <v>159080</v>
       </c>
-      <c r="AA40" s="76" t="n">
+      <c r="AA40" s="78" t="n">
         <v>29980</v>
       </c>
-      <c r="AB40" s="76" t="n">
+      <c r="AB40" s="78" t="n">
         <v>67075</v>
       </c>
-      <c r="AC40" s="76" t="n">
+      <c r="AC40" s="78" t="n">
         <v>131160</v>
       </c>
-      <c r="AD40" s="76" t="n">
+      <c r="AD40" s="78" t="n">
         <v>58420</v>
       </c>
-      <c r="AE40" s="76" t="n">
+      <c r="AE40" s="78" t="n">
         <v>54440.5</v>
       </c>
       <c r="AF40" s="76" t="n">
@@ -9151,15 +9841,11 @@
         </is>
       </c>
       <c r="M41" s="76" t="n"/>
-      <c r="N41" s="76" t="n">
-        <v>2604892.609999999</v>
-      </c>
+      <c r="N41" s="76" t="n"/>
       <c r="O41" s="76" t="n"/>
       <c r="P41" s="76" t="n"/>
       <c r="Q41" s="76" t="n"/>
-      <c r="R41" s="76" t="n">
-        <v>2604892.609999999</v>
-      </c>
+      <c r="R41" s="76" t="n"/>
       <c r="S41" s="76" t="n"/>
       <c r="T41" s="76" t="n"/>
       <c r="U41" s="76" t="n"/>
@@ -9172,22 +9858,22 @@
       <c r="Z41" s="76" t="n">
         <v>2040975</v>
       </c>
-      <c r="AA41" s="76" t="n">
+      <c r="AA41" s="108" t="n">
         <v>387750</v>
       </c>
-      <c r="AB41" s="76" t="n">
+      <c r="AB41" s="78" t="n">
         <v>2199600</v>
       </c>
-      <c r="AC41" s="76" t="n">
+      <c r="AC41" s="78" t="n">
         <v>2553600</v>
       </c>
-      <c r="AD41" s="76" t="n">
+      <c r="AD41" s="78" t="n">
         <v>2019600</v>
       </c>
-      <c r="AE41" s="76" t="n">
+      <c r="AE41" s="78" t="n">
         <v>1920000</v>
       </c>
-      <c r="AF41" s="76" t="n">
+      <c r="AF41" s="78" t="n">
         <v>684892.6099999991</v>
       </c>
       <c r="AG41" s="76" t="n">
@@ -9570,7 +10256,7 @@
       </c>
       <c r="M43" s="76" t="n"/>
       <c r="N43" s="76" t="n">
-        <v>13500</v>
+        <v>10710</v>
       </c>
       <c r="O43" s="76" t="n"/>
       <c r="P43" s="76" t="n"/>
@@ -9581,7 +10267,7 @@
       <c r="U43" s="76" t="n"/>
       <c r="V43" s="76" t="n"/>
       <c r="W43" s="76" t="n">
-        <v>13500</v>
+        <v>10710</v>
       </c>
       <c r="X43" s="76" t="n"/>
       <c r="Y43" s="76" t="n">
@@ -9593,13 +10279,13 @@
       <c r="AA43" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AB43" s="76" t="n">
+      <c r="AB43" s="109" t="n">
         <v>3900</v>
       </c>
-      <c r="AC43" s="76" t="n">
+      <c r="AC43" s="78" t="n">
         <v>2400</v>
       </c>
-      <c r="AD43" s="76" t="n">
+      <c r="AD43" s="78" t="n">
         <v>7200</v>
       </c>
       <c r="AE43" s="76" t="n">
@@ -9781,7 +10467,7 @@
       </c>
       <c r="M44" s="76" t="n"/>
       <c r="N44" s="76" t="n"/>
-      <c r="O44" s="79" t="n"/>
+      <c r="O44" s="100" t="n"/>
       <c r="P44" s="76" t="n"/>
       <c r="Q44" s="76" t="n"/>
       <c r="R44" s="76" t="n"/>
@@ -9984,33 +10670,33 @@
       </c>
       <c r="M45" s="76" t="n"/>
       <c r="N45" s="76" t="n">
-        <v>43500</v>
+        <v>46270</v>
       </c>
       <c r="O45" s="76" t="n"/>
       <c r="P45" s="76" t="n"/>
       <c r="Q45" s="76" t="n"/>
       <c r="R45" s="76" t="n"/>
-      <c r="S45" s="76" t="n">
-        <v>43500</v>
-      </c>
+      <c r="S45" s="76" t="n"/>
       <c r="T45" s="76" t="n"/>
-      <c r="U45" s="76" t="n"/>
+      <c r="U45" s="76" t="n">
+        <v>46270</v>
+      </c>
       <c r="V45" s="76" t="n"/>
       <c r="W45" s="76" t="n"/>
       <c r="X45" s="76" t="n"/>
       <c r="Y45" s="76" t="n">
         <v>66100</v>
       </c>
-      <c r="Z45" s="76" t="n">
+      <c r="Z45" s="110" t="n">
         <v>22600</v>
       </c>
-      <c r="AA45" s="76" t="n">
+      <c r="AA45" s="78" t="n">
         <v>22700</v>
       </c>
-      <c r="AB45" s="76" t="n">
+      <c r="AB45" s="78" t="n">
         <v>5700</v>
       </c>
-      <c r="AC45" s="76" t="n">
+      <c r="AC45" s="78" t="n">
         <v>15100</v>
       </c>
       <c r="AD45" s="76" t="n">
@@ -10191,14 +10877,14 @@
       </c>
       <c r="M46" s="76" t="n"/>
       <c r="N46" s="76" t="n">
-        <v>662439.29</v>
+        <v>555407.503</v>
       </c>
       <c r="O46" s="76" t="n"/>
       <c r="P46" s="76" t="n"/>
       <c r="Q46" s="76" t="n"/>
       <c r="R46" s="76" t="n"/>
       <c r="S46" s="76" t="n">
-        <v>662439.29</v>
+        <v>555407.503</v>
       </c>
       <c r="T46" s="76" t="n"/>
       <c r="U46" s="76" t="n"/>
@@ -10214,13 +10900,13 @@
       <c r="AA46" s="76" t="n">
         <v>875</v>
       </c>
-      <c r="AB46" s="76" t="n">
+      <c r="AB46" s="111" t="n">
         <v>239000</v>
       </c>
-      <c r="AC46" s="76" t="n">
+      <c r="AC46" s="78" t="n">
         <v>422000</v>
       </c>
-      <c r="AD46" s="76" t="n">
+      <c r="AD46" s="78" t="n">
         <v>564.290000000037</v>
       </c>
       <c r="AE46" s="76" t="n">
@@ -10398,7 +11084,7 @@
       </c>
       <c r="M47" s="76" t="n"/>
       <c r="N47" s="76" t="n">
-        <v>1397362.4</v>
+        <v>1459265.92</v>
       </c>
       <c r="O47" s="76" t="n"/>
       <c r="P47" s="76" t="n"/>
@@ -10406,7 +11092,7 @@
       <c r="R47" s="76" t="n"/>
       <c r="S47" s="76" t="n"/>
       <c r="T47" s="76" t="n">
-        <v>1397362.4</v>
+        <v>1459265.92</v>
       </c>
       <c r="U47" s="76" t="n"/>
       <c r="V47" s="76" t="n"/>
@@ -10415,22 +11101,22 @@
       <c r="Y47" s="76" t="n">
         <v>1824082.4</v>
       </c>
-      <c r="Z47" s="76" t="n">
+      <c r="Z47" s="112" t="n">
         <v>426720</v>
       </c>
       <c r="AA47" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AB47" s="76" t="n">
+      <c r="AB47" s="78" t="n">
         <v>287136</v>
       </c>
-      <c r="AC47" s="76" t="n">
+      <c r="AC47" s="78" t="n">
         <v>528960</v>
       </c>
-      <c r="AD47" s="76" t="n">
+      <c r="AD47" s="78" t="n">
         <v>460480</v>
       </c>
-      <c r="AE47" s="76" t="n">
+      <c r="AE47" s="78" t="n">
         <v>120786.4</v>
       </c>
       <c r="AF47" s="76" t="n">
@@ -11014,11 +11700,15 @@
         </is>
       </c>
       <c r="M50" s="76" t="n"/>
-      <c r="N50" s="76" t="n"/>
+      <c r="N50" s="76" t="n">
+        <v>13160</v>
+      </c>
       <c r="O50" s="76" t="n"/>
       <c r="P50" s="76" t="n"/>
       <c r="Q50" s="76" t="n"/>
-      <c r="R50" s="76" t="n"/>
+      <c r="R50" s="76" t="n">
+        <v>13160</v>
+      </c>
       <c r="S50" s="76" t="n"/>
       <c r="T50" s="76" t="n"/>
       <c r="U50" s="76" t="n"/>
@@ -11034,7 +11724,7 @@
       <c r="AA50" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AB50" s="76" t="n">
+      <c r="AB50" s="113" t="n">
         <v>18800</v>
       </c>
       <c r="AC50" s="76" t="n">
@@ -11218,13 +11908,13 @@
       </c>
       <c r="M51" s="76" t="n"/>
       <c r="N51" s="76" t="n">
-        <v>292530.75</v>
+        <v>309631.525</v>
       </c>
       <c r="O51" s="76" t="n"/>
       <c r="P51" s="76" t="n"/>
       <c r="Q51" s="76" t="n"/>
       <c r="R51" s="76" t="n">
-        <v>292530.75</v>
+        <v>309631.525</v>
       </c>
       <c r="S51" s="76" t="n"/>
       <c r="T51" s="76" t="n"/>
@@ -11238,10 +11928,10 @@
       <c r="Z51" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AA51" s="76" t="n">
+      <c r="AA51" s="114" t="n">
         <v>149800</v>
       </c>
-      <c r="AB51" s="76" t="n">
+      <c r="AB51" s="78" t="n">
         <v>292530.75</v>
       </c>
       <c r="AC51" s="76" t="n">
@@ -11408,7 +12098,7 @@
           <t>曹</t>
         </is>
       </c>
-      <c r="H52" s="77" t="n">
+      <c r="H52" s="79" t="n">
         <v>100</v>
       </c>
       <c r="I52" s="54" t="inlineStr">
@@ -11427,119 +12117,119 @@
           <t>银承/电汇</t>
         </is>
       </c>
-      <c r="M52" s="77" t="n"/>
-      <c r="N52" s="77" t="n">
+      <c r="M52" s="79" t="n"/>
+      <c r="N52" s="79" t="n">
         <v>180000</v>
       </c>
-      <c r="O52" s="77" t="n"/>
-      <c r="P52" s="77" t="n"/>
-      <c r="Q52" s="77" t="n"/>
-      <c r="R52" s="77" t="n"/>
-      <c r="S52" s="77" t="n"/>
-      <c r="T52" s="77" t="n"/>
-      <c r="U52" s="77" t="n"/>
-      <c r="V52" s="77" t="n"/>
-      <c r="W52" s="77" t="n">
+      <c r="O52" s="79" t="n"/>
+      <c r="P52" s="79" t="n"/>
+      <c r="Q52" s="79" t="n"/>
+      <c r="R52" s="79" t="n"/>
+      <c r="S52" s="79" t="n"/>
+      <c r="T52" s="79" t="n"/>
+      <c r="U52" s="79" t="n"/>
+      <c r="V52" s="79" t="n"/>
+      <c r="W52" s="79" t="n">
         <v>180000</v>
       </c>
-      <c r="X52" s="77" t="n"/>
-      <c r="Y52" s="77" t="n">
+      <c r="X52" s="79" t="n"/>
+      <c r="Y52" s="79" t="n">
         <v>280000</v>
       </c>
-      <c r="Z52" s="77" t="n">
+      <c r="Z52" s="79" t="n">
         <v>100000</v>
       </c>
-      <c r="AA52" s="77" t="n">
+      <c r="AA52" s="79" t="n">
         <v>80000</v>
       </c>
-      <c r="AB52" s="77" t="n">
+      <c r="AB52" s="79" t="n">
         <v>100000</v>
       </c>
-      <c r="AC52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM52" s="77" t="n"/>
-      <c r="AN52" s="77" t="n">
+      <c r="AC52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM52" s="79" t="n"/>
+      <c r="AN52" s="79" t="n">
         <v>100</v>
       </c>
-      <c r="AO52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ52" s="77" t="n">
+      <c r="AO52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ52" s="79" t="n">
         <v>100</v>
       </c>
-      <c r="AR52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB52" s="77" t="inlineStr">
+      <c r="AR52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB52" s="79" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="BC52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE52" s="77" t="n">
+      <c r="BC52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE52" s="79" t="n">
         <v>0</v>
       </c>
       <c r="BF52" s="54" t="inlineStr">
@@ -11547,25 +12237,25 @@
           <t>曹</t>
         </is>
       </c>
-      <c r="BG52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI52" s="77" t="n">
+      <c r="BG52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI52" s="79" t="n">
         <v>100</v>
       </c>
-      <c r="BJ52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL52" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM52" s="77" t="n">
+      <c r="BJ52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL52" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM52" s="79" t="n">
         <v>0</v>
       </c>
       <c r="BN52" s="54" t="n">
@@ -11635,11 +12325,15 @@
         </is>
       </c>
       <c r="M53" s="76" t="n"/>
-      <c r="N53" s="76" t="n"/>
+      <c r="N53" s="76" t="n">
+        <v>28980</v>
+      </c>
       <c r="O53" s="76" t="n"/>
       <c r="P53" s="76" t="n"/>
       <c r="Q53" s="76" t="n"/>
-      <c r="R53" s="76" t="n"/>
+      <c r="R53" s="76" t="n">
+        <v>28980</v>
+      </c>
       <c r="S53" s="76" t="n"/>
       <c r="T53" s="76" t="n"/>
       <c r="U53" s="76" t="n"/>
@@ -11658,7 +12352,7 @@
       <c r="AB53" s="76" t="n">
         <v>0</v>
       </c>
-      <c r="AC53" s="76" t="n">
+      <c r="AC53" s="113" t="n">
         <v>41400</v>
       </c>
       <c r="AD53" s="76" t="n">
@@ -11818,7 +12512,7 @@
           <t>曹</t>
         </is>
       </c>
-      <c r="H54" s="77" t="n">
+      <c r="H54" s="79" t="n">
         <v>265200</v>
       </c>
       <c r="I54" s="54" t="inlineStr">
@@ -11837,119 +12531,119 @@
           <t>银承/电汇</t>
         </is>
       </c>
-      <c r="M54" s="77" t="n"/>
-      <c r="N54" s="77" t="n">
+      <c r="M54" s="79" t="n"/>
+      <c r="N54" s="79" t="n">
         <v>401171.05</v>
       </c>
-      <c r="O54" s="77" t="n"/>
-      <c r="P54" s="77" t="n"/>
-      <c r="Q54" s="77" t="n"/>
-      <c r="R54" s="77" t="n"/>
-      <c r="S54" s="77" t="n">
+      <c r="O54" s="79" t="n"/>
+      <c r="P54" s="79" t="n"/>
+      <c r="Q54" s="79" t="n"/>
+      <c r="R54" s="79" t="n"/>
+      <c r="S54" s="79" t="n">
         <v>401171.05</v>
       </c>
-      <c r="T54" s="77" t="n"/>
-      <c r="U54" s="77" t="n"/>
-      <c r="V54" s="77" t="n"/>
-      <c r="W54" s="77" t="n"/>
-      <c r="X54" s="77" t="n"/>
-      <c r="Y54" s="77" t="n">
+      <c r="T54" s="79" t="n"/>
+      <c r="U54" s="79" t="n"/>
+      <c r="V54" s="79" t="n"/>
+      <c r="W54" s="79" t="n"/>
+      <c r="X54" s="79" t="n"/>
+      <c r="Y54" s="79" t="n">
         <v>537171.05</v>
       </c>
-      <c r="Z54" s="77" t="n">
+      <c r="Z54" s="79" t="n">
         <v>136000</v>
       </c>
-      <c r="AA54" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB54" s="77" t="n">
+      <c r="AA54" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="79" t="n">
         <v>129200</v>
       </c>
-      <c r="AC54" s="77" t="n">
+      <c r="AC54" s="79" t="n">
         <v>271971.05</v>
       </c>
-      <c r="AD54" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE54" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF54" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG54" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH54" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI54" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ54" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK54" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL54" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM54" s="77" t="n"/>
-      <c r="AN54" s="77" t="n">
+      <c r="AD54" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK54" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL54" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM54" s="79" t="n"/>
+      <c r="AN54" s="79" t="n">
         <v>265200</v>
       </c>
-      <c r="AO54" s="77" t="n">
+      <c r="AO54" s="79" t="n">
         <v>136000</v>
       </c>
-      <c r="AP54" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ54" s="77" t="n">
+      <c r="AP54" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ54" s="79" t="n">
         <v>129200</v>
       </c>
-      <c r="AR54" s="77" t="n">
+      <c r="AR54" s="79" t="n">
         <v>272000</v>
       </c>
-      <c r="AS54" s="77" t="n">
+      <c r="AS54" s="79" t="n">
         <v>68000</v>
       </c>
-      <c r="AT54" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU54" s="77" t="n">
+      <c r="AT54" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU54" s="79" t="n">
         <v>204000</v>
       </c>
-      <c r="AV54" s="77" t="n">
+      <c r="AV54" s="79" t="n">
         <v>209000</v>
       </c>
-      <c r="AW54" s="77" t="n">
+      <c r="AW54" s="79" t="n">
         <v>34653.1</v>
       </c>
-      <c r="AX54" s="77" t="n">
+      <c r="AX54" s="79" t="n">
         <v>240900</v>
       </c>
-      <c r="AY54" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ54" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA54" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB54" s="77" t="inlineStr">
+      <c r="AY54" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ54" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA54" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB54" s="79" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="BC54" s="77" t="n">
+      <c r="BC54" s="79" t="n">
         <v>61888.76</v>
       </c>
-      <c r="BD54" s="77" t="n">
+      <c r="BD54" s="79" t="n">
         <v>381888.76</v>
       </c>
-      <c r="BE54" s="77" t="n">
+      <c r="BE54" s="79" t="n">
         <v>0</v>
       </c>
       <c r="BF54" s="54" t="inlineStr">
@@ -11957,25 +12651,25 @@
           <t>曹</t>
         </is>
       </c>
-      <c r="BG54" s="77" t="n">
+      <c r="BG54" s="79" t="n">
         <v>136000</v>
       </c>
-      <c r="BH54" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI54" s="77" t="n">
+      <c r="BH54" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI54" s="79" t="n">
         <v>129200</v>
       </c>
-      <c r="BJ54" s="77" t="n">
+      <c r="BJ54" s="79" t="n">
         <v>271971.05</v>
       </c>
-      <c r="BK54" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL54" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM54" s="77" t="n">
+      <c r="BK54" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL54" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM54" s="79" t="n">
         <v>0</v>
       </c>
       <c r="BN54" s="54" t="n">
@@ -12050,13 +12744,13 @@
       </c>
       <c r="M55" s="76" t="n"/>
       <c r="N55" s="76" t="n">
-        <v>680569.4</v>
+        <v>1041504.1</v>
       </c>
       <c r="O55" s="76" t="n"/>
       <c r="P55" s="76" t="n"/>
       <c r="Q55" s="76" t="n"/>
       <c r="R55" s="76" t="n">
-        <v>680569.4</v>
+        <v>1041504.1</v>
       </c>
       <c r="S55" s="76" t="n"/>
       <c r="T55" s="76" t="n"/>
@@ -12076,19 +12770,19 @@
       <c r="AB55" s="76" t="n">
         <v>182000.4</v>
       </c>
-      <c r="AC55" s="76" t="n">
+      <c r="AC55" s="115" t="n">
         <v>269077</v>
       </c>
-      <c r="AD55" s="76" t="n">
+      <c r="AD55" s="78" t="n">
         <v>297856.2</v>
       </c>
-      <c r="AE55" s="76" t="n">
+      <c r="AE55" s="78" t="n">
         <v>191478.6</v>
       </c>
-      <c r="AF55" s="76" t="n">
+      <c r="AF55" s="78" t="n">
         <v>298203.8</v>
       </c>
-      <c r="AG55" s="76" t="n">
+      <c r="AG55" s="78" t="n">
         <v>190887</v>
       </c>
       <c r="AH55" s="76" t="n">
@@ -12255,15 +12949,15 @@
           <t>商承/银承/电汇</t>
         </is>
       </c>
-      <c r="M56" s="79" t="n"/>
-      <c r="N56" s="79" t="n">
-        <v>2131070.419999999</v>
+      <c r="M56" s="100" t="n"/>
+      <c r="N56" s="100" t="n">
+        <v>6715326.709</v>
       </c>
       <c r="O56" s="76" t="n"/>
       <c r="P56" s="76" t="n"/>
       <c r="Q56" s="76" t="n"/>
       <c r="R56" s="76" t="n">
-        <v>2131070.419999999</v>
+        <v>6715326.709</v>
       </c>
       <c r="S56" s="76" t="n"/>
       <c r="T56" s="76" t="n"/>
@@ -12277,19 +12971,19 @@
       <c r="Z56" s="76" t="n">
         <v>2255371.36</v>
       </c>
-      <c r="AA56" s="76" t="n">
+      <c r="AA56" s="116" t="n">
         <v>1644765.37</v>
       </c>
-      <c r="AB56" s="76" t="n">
+      <c r="AB56" s="78" t="n">
         <v>1523110.66</v>
       </c>
-      <c r="AC56" s="76" t="n">
+      <c r="AC56" s="78" t="n">
         <v>2039006.06</v>
       </c>
-      <c r="AD56" s="76" t="n">
+      <c r="AD56" s="78" t="n">
         <v>1998484.56</v>
       </c>
-      <c r="AE56" s="76" t="n">
+      <c r="AE56" s="78" t="n">
         <v>132585.859999999</v>
       </c>
       <c r="AF56" s="76" t="n">
@@ -12450,7 +13144,7 @@
   <dimension ref="A1:B105"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col width="15.3846153846154" customWidth="1" style="81" min="1" max="1"/>
+    <col width="15.3846153846154" customWidth="1" style="117" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13520,8 +14214,8 @@
   <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col width="26.9134615384615" customWidth="1" style="81" min="2" max="2"/>
-    <col width="12.7692307692308" customWidth="1" style="81" min="3" max="3"/>
+    <col width="26.9134615384615" customWidth="1" style="117" min="2" max="2"/>
+    <col width="12.7692307692308" customWidth="1" style="117" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13544,7 +14238,7 @@
       <c r="E1" s="4" t="n"/>
       <c r="F1" s="4" t="n"/>
     </row>
-    <row r="2" ht="17.6" customHeight="1" s="81">
+    <row r="2" ht="17.6" customHeight="1" s="117">
       <c r="A2" s="53" t="n">
         <v>1</v>
       </c>
@@ -13556,9 +14250,9 @@
       <c r="C2" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="82" t="n"/>
-      <c r="E2" s="82" t="n"/>
-      <c r="F2" s="82" t="n"/>
+      <c r="D2" s="118" t="n"/>
+      <c r="E2" s="118" t="n"/>
+      <c r="F2" s="118" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="53" t="n">

--- a/AutoPaymentScheduleFile/TotalSheet/排款计划参照数据原表.xlsx
+++ b/AutoPaymentScheduleFile/TotalSheet/排款计划参照数据原表.xlsx
@@ -257,7 +257,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="187">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
@@ -461,2438 +461,6 @@
         <fgColor rgb="FFC6EFCE"/>
         <bgColor rgb="FFC6EFCE"/>
       </patternFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.1240697223126401">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.1241697223126401">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.4499500000000001">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.4500500000000001">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.6375374976889866">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.6376374976889866">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.4571452990533561">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.4572452990533561">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.02791955749354024">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.02801955749354024">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.8487299223323481">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.8488299223323481">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.3975876748907989">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.3976876748907989">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.49995">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.50005">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.4444462497893138">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.4445462497893138">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.1443406810035842">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.1444406810035842">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.1804670181280059">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.1805670181280059">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.4437670731707316">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.4438670731707316">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.2528508758160903">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.2529508758160903">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.4869039215686277">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.4870039215686277">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.08472102494063805">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.08482102494063803">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.2499499999999999">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.2500499999999999">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.02105670446473473">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.02115670446473473">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.01180100446428533">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.01190100446428533">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.4999499999999998">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.5000499999999998">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7483874999999999">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7484874999999999">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.3026509256779319">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.3027509256779319">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.2683985006518905">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.2684985006518905">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.4999499999999997">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.5000499999999997">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.5049037954545456">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.5050037954545455">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.2940676470588237">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.2941676470588237">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7975336573395372">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7976336573395372">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7495583545918367">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7496583545918367">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.5127332655432887">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.5128332655432887">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.98815">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.98825">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.2492441795468173">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.2493441795468173">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.9093989351403678">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.9094989351403678">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.135085135135135">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.135185135135135">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.973059243697479">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.973159243697479">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7327627684759158">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7328627684759158">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.1341724997769648">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.1342724997769648">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.74995">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.75005">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7363990470940305">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7364990470940305">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.08784625360230536">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.08794625360230535">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7397568669527897">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7398568669527897">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.6240701265822785">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.6241701265822784">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.968897311827957">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.968997311827957">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.3619962046204622">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.3620962046204622">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.5674824675324676">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.5675824675324675">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.9653666666666667">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.9654666666666667">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.2499500000000001">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.2500500000000001">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.9983650982758622">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.9984292120689656">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.2669664917541229">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.2670664917541229">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.5404800323119474">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.5405800323119474">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.71013">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.71023">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.2137830645161287">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.2138830645161287">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.2423413043478261">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.2424413043478261">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.4400250000000002">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.4401250000000002">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.1096313774630492">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.1097313774630492">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7737961538461539">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7738961538461538">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.5019319560878243">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.5020319560878242">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7492986823272069">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7493986823272069">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.1615489868287743">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.1616489868287743">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.1884383060163742">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.1885383060163742">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.4863861478396667">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.4864861478396667">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.4468790405904058">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.4469790405904058">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.5046167810308021">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.5047167810308021">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7131432995495496">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7132432995495496">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.6744629258268962">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.6745629258268961">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.1394101542416453">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.1395101542416453">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.3533359303090072">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.3534359303090072">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.3125896276595745">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.3126896276595745">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7708912201657537">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7709912201657537">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.1240697223126401">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.1241697223126401">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.4499500000000001">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.4500500000000001">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.6375374976889866">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.6376374976889866">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.4571452990533561">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.4572452990533561">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.02791955749354024">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.02801955749354024">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.8487299223323481">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.8488299223323481">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.3975876748907989">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.3976876748907989">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.49995">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.50005">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.4444462497893138">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.4445462497893138">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.1443406810035842">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.1444406810035842">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.1804670181280059">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.1805670181280059">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.4437670731707316">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.4438670731707316">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2528508758160903">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2529508758160903">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.4869039215686277">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.4870039215686277">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.08472102494063805">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.08482102494063803">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2499499999999999">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2500499999999999">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.02105670446473473">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.02115670446473473">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.01180100446428533">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.01190100446428533">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.4999499999999998">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.5000499999999998">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.7483874999999999">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.7484874999999999">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.3026509256779319">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.3027509256779319">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2683985006518905">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2684985006518905">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.4999499999999997">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.5000499999999997">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.5049037954545456">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.5050037954545455">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2940676470588237">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2941676470588237">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.7975336573395372">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.7976336573395372">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.7495583545918367">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.7496583545918367">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.5127332655432887">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.5128332655432887">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.98815">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.98825">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2492441795468173">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2493441795468173">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.9093989351403678">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.9094989351403678">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.135085135135135">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.135185135135135">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.973059243697479">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.973159243697479">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.7327627684759158">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.7328627684759158">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.1341724997769648">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.1342724997769648">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.74995">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.75005">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.7363990470940305">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.7364990470940305">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.08784625360230536">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.08794625360230535">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.7397568669527897">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.7398568669527897">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.6240701265822785">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.6241701265822784">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.968897311827957">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.968997311827957">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.3619962046204622">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.3620962046204622">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.5674824675324676">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.5675824675324675">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.9653666666666667">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.9654666666666667">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2499500000000001">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2500500000000001">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.9983650982758622">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.9984292120689656">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2669664917541229">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2670664917541229">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.5404800323119474">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.5405800323119474">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.71013">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.71023">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2137830645161287">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2138830645161287">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2423413043478261">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2424413043478261">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.4414514139114658">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.4415514139114658">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.8218862754926097">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.8219862754926097">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7173657303370787">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7174657303370787">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.9035175209580838">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.9036175209580838">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.89995">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.90005">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7252733278233553">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7253733278233553">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.6315868605215645">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.6316868605215645">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.8999499999999999">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.9000499999999999">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.8376476612032748">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.8377476612032748">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.9137883963802809">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.9138883963802809">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.5877056456399005">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.5878056456399005">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.9083502058554437">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.9084502058554437">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7079283383523208">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.7080283383523208">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.6134382716389943">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.6135382716389943">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.8278420308483291">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.8279420308483291">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.6620117110799441">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.662111711079944">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.4052285718978607">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.4053285718978606">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.8796353388020581">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="0.8797353388020581">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.1240697223126401">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.1241697223126401">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.4499500000000001">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.4500500000000001">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.02791955749354024">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.02801955749354024">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.3975876748907989">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.3976876748907989">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.1443406810035842">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.1444406810035842">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.1804670181280059">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.1805670181280059">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2528508758160903">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2529508758160903">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.02105670446473473">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.02115670446473473">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.01180100446428533">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.01190100446428533">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.3026509256779319">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.3027509256779319">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2492441795468173">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2493441795468173">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.135085135135135">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.135185135135135">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.1341724997769648">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.1342724997769648">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2499500000000001">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2500500000000001">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2137830645161287">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2138830645161287">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2423413043478261">
-          <color rgb="FFFFFFFF"/>
-        </stop>
-        <stop position="0.2424413043478261">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-        <stop position="1">
-          <color rgb="FFC6EFCE"/>
-        </stop>
-      </gradientFill>
     </fill>
   </fills>
   <borders count="22">
@@ -3322,7 +890,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="216">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3511,462 +1079,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="46" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="38" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="83" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="47" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="48" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="35" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="82" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="49" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="57" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="50" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="51" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="52" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="42" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="84" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="39" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="53" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="54" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="55" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="40" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="56" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="58" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="59" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="41" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="60" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="37" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="61" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="62" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="63" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="64" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="65" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="66" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="67" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="68" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="69" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="70" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="36" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="85" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="43" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="71" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="72" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="73" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="44" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="74" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="75" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="76" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="77" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="78" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="79" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="45" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="80" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="81" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="113" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="105" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="150" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="114" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="86" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="93" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="115" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="102" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="94" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="149" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="90" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="91" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="116" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="87" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="124" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="88" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="117" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="89" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="118" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="119" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="109" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="151" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="106" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="98" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="120" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="121" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="122" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="107" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="92" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="123" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="125" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="95" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="126" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="108" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="127" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="104" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="99" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="128" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="129" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="130" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="131" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="132" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="133" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="134" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="135" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="96" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="100" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="136" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="137" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="103" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="152" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="110" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="138" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="139" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="140" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="111" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="141" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="142" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="143" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="144" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="101" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="145" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="146" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="112" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="147" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="148" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="97" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="157" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="177" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="153" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="162" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="171" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="163" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="158" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="159" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="154" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="155" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="156" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="160" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="178" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="179" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="185" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="173" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="167" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="180" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="161" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="164" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="174" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="168" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="181" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="182" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="165" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="169" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="183" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="172" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="186" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="175" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="170" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="184" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="176" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="166" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -4989,22 +2101,22 @@
         </is>
       </c>
       <c r="R5" s="53" t="n">
-        <v>7924.672999999078</v>
+        <v>1132.54000000027</v>
       </c>
       <c r="S5" s="53" t="n">
-        <v>17977296.725</v>
+        <v>3056.439999998052</v>
       </c>
       <c r="T5" s="53" t="n">
-        <v>1000000</v>
+        <v>5091.350000000013</v>
       </c>
       <c r="U5" s="53" t="n">
-        <v>7056178.415</v>
+        <v>6112356.83</v>
       </c>
       <c r="V5" s="53" t="n">
-        <v>38276.98199999984</v>
+        <v>813588.97</v>
       </c>
       <c r="W5" s="53" t="n">
-        <v>3000000</v>
+        <v>7875.259999999776</v>
       </c>
       <c r="X5" s="53" t="n"/>
       <c r="Y5" s="26" t="n"/>
@@ -5396,15 +2508,15 @@
       </c>
       <c r="N9" s="36" t="n"/>
       <c r="O9" s="59" t="n">
-        <v>229993</v>
+        <v>459986</v>
       </c>
       <c r="P9" s="59" t="n"/>
       <c r="Q9" s="36" t="n"/>
-      <c r="R9" s="36" t="n">
-        <v>229993</v>
-      </c>
+      <c r="R9" s="36" t="n"/>
       <c r="S9" s="36" t="n"/>
-      <c r="T9" s="36" t="n"/>
+      <c r="T9" s="36" t="n">
+        <v>459986</v>
+      </c>
       <c r="U9" s="36" t="n"/>
       <c r="V9" s="36" t="n"/>
       <c r="W9" s="36" t="n"/>
@@ -5424,7 +2536,7 @@
       <c r="AC9" s="60" t="n">
         <v>131600</v>
       </c>
-      <c r="AD9" s="115" t="n">
+      <c r="AD9" s="60" t="n">
         <v>82000</v>
       </c>
       <c r="AE9" s="60" t="n">
@@ -5604,14 +2716,14 @@
       </c>
       <c r="N10" s="36" t="n"/>
       <c r="O10" s="59" t="n">
-        <v>192220.875</v>
+        <v>384441.75</v>
       </c>
       <c r="P10" s="59" t="n"/>
       <c r="Q10" s="36" t="n"/>
-      <c r="R10" s="36" t="n">
-        <v>192220.875</v>
-      </c>
-      <c r="S10" s="36" t="n"/>
+      <c r="R10" s="36" t="n"/>
+      <c r="S10" s="36" t="n">
+        <v>384441.75</v>
+      </c>
       <c r="T10" s="36" t="n"/>
       <c r="U10" s="36" t="n"/>
       <c r="V10" s="36" t="n"/>
@@ -5635,7 +2747,7 @@
       <c r="AD10" s="60" t="n">
         <v>149720</v>
       </c>
-      <c r="AE10" s="116" t="n">
+      <c r="AE10" s="60" t="n">
         <v>92960</v>
       </c>
       <c r="AF10" s="59" t="n">
@@ -5812,12 +2924,12 @@
       </c>
       <c r="N11" s="36" t="n"/>
       <c r="O11" s="59" t="n">
-        <v>3339.926</v>
+        <v>33399.26</v>
       </c>
       <c r="P11" s="61" t="n"/>
       <c r="Q11" s="36" t="n"/>
       <c r="R11" s="36" t="n">
-        <v>3339.926</v>
+        <v>33399.26</v>
       </c>
       <c r="S11" s="36" t="n"/>
       <c r="T11" s="36" t="n"/>
@@ -5834,7 +2946,7 @@
       <c r="AA11" s="59" t="n">
         <v>100232</v>
       </c>
-      <c r="AB11" s="182" t="n">
+      <c r="AB11" s="60" t="n">
         <v>33399.26</v>
       </c>
       <c r="AC11" s="59" t="n">
@@ -6222,15 +3334,15 @@
       </c>
       <c r="N13" s="36" t="n"/>
       <c r="O13" s="59" t="n">
-        <v>4438.625</v>
+        <v>8877.25</v>
       </c>
       <c r="P13" s="59" t="n"/>
       <c r="Q13" s="36" t="n"/>
-      <c r="R13" s="36" t="n">
-        <v>4438.625</v>
-      </c>
+      <c r="R13" s="36" t="n"/>
       <c r="S13" s="36" t="n"/>
-      <c r="T13" s="36" t="n"/>
+      <c r="T13" s="36" t="n">
+        <v>8877.25</v>
+      </c>
       <c r="U13" s="36" t="n"/>
       <c r="V13" s="36" t="n"/>
       <c r="W13" s="36" t="n"/>
@@ -6244,7 +3356,7 @@
       <c r="AA13" s="59" t="n">
         <v>11525</v>
       </c>
-      <c r="AB13" s="117" t="n">
+      <c r="AB13" s="60" t="n">
         <v>6250</v>
       </c>
       <c r="AC13" s="60" t="n">
@@ -6636,7 +3748,7 @@
       </c>
       <c r="N15" s="36" t="n"/>
       <c r="O15" s="59" t="n">
-        <v>386211.545</v>
+        <v>772423.09</v>
       </c>
       <c r="P15" s="59" t="n"/>
       <c r="Q15" s="36" t="n"/>
@@ -6644,7 +3756,7 @@
       <c r="S15" s="36" t="n"/>
       <c r="T15" s="36" t="n"/>
       <c r="U15" s="36" t="n">
-        <v>386211.545</v>
+        <v>772423.09</v>
       </c>
       <c r="V15" s="36" t="n"/>
       <c r="W15" s="36" t="n"/>
@@ -6670,7 +3782,7 @@
       <c r="AE15" s="60" t="n">
         <v>280034.4</v>
       </c>
-      <c r="AF15" s="183" t="n">
+      <c r="AF15" s="60" t="n">
         <v>419837</v>
       </c>
       <c r="AG15" s="60" t="n">
@@ -6844,12 +3956,12 @@
       </c>
       <c r="N16" s="36" t="n"/>
       <c r="O16" s="59" t="n">
-        <v>157013.5</v>
+        <v>1570135</v>
       </c>
       <c r="P16" s="59" t="n"/>
       <c r="Q16" s="36" t="n"/>
       <c r="R16" s="36" t="n">
-        <v>157013.5</v>
+        <v>1570135</v>
       </c>
       <c r="S16" s="36" t="n"/>
       <c r="T16" s="36" t="n"/>
@@ -6866,10 +3978,10 @@
       <c r="AA16" s="60" t="n">
         <v>389000</v>
       </c>
-      <c r="AB16" s="119" t="n">
+      <c r="AB16" s="60" t="n">
         <v>900000</v>
       </c>
-      <c r="AC16" s="184" t="n">
+      <c r="AC16" s="60" t="n">
         <v>281135</v>
       </c>
       <c r="AD16" s="59" t="n">
@@ -7258,14 +4370,14 @@
       </c>
       <c r="N18" s="36" t="n"/>
       <c r="O18" s="59" t="n">
-        <v>742531.96</v>
+        <v>7425319.6</v>
       </c>
       <c r="P18" s="59" t="n"/>
       <c r="Q18" s="36" t="n"/>
-      <c r="R18" s="36" t="n">
-        <v>742531.96</v>
-      </c>
-      <c r="S18" s="36" t="n"/>
+      <c r="R18" s="36" t="n"/>
+      <c r="S18" s="36" t="n">
+        <v>7425319.6</v>
+      </c>
       <c r="T18" s="36" t="n"/>
       <c r="U18" s="36" t="n"/>
       <c r="V18" s="36" t="n"/>
@@ -7286,10 +4398,10 @@
       <c r="AC18" s="60" t="n">
         <v>2544605</v>
       </c>
-      <c r="AD18" s="120" t="n">
+      <c r="AD18" s="60" t="n">
         <v>2401250</v>
       </c>
-      <c r="AE18" s="185" t="n">
+      <c r="AE18" s="60" t="n">
         <v>1900700</v>
       </c>
       <c r="AF18" s="60" t="n">
@@ -7466,18 +4578,18 @@
       </c>
       <c r="N19" s="36" t="n"/>
       <c r="O19" s="59" t="n">
-        <v>202669.3</v>
+        <v>405338.6</v>
       </c>
       <c r="P19" s="59" t="n"/>
       <c r="Q19" s="36" t="n"/>
-      <c r="R19" s="36" t="n">
-        <v>202669.3</v>
-      </c>
+      <c r="R19" s="36" t="n"/>
       <c r="S19" s="36" t="n"/>
       <c r="T19" s="36" t="n"/>
       <c r="U19" s="36" t="n"/>
       <c r="V19" s="36" t="n"/>
-      <c r="W19" s="36" t="n"/>
+      <c r="W19" s="36" t="n">
+        <v>405338.6</v>
+      </c>
       <c r="X19" s="36" t="n"/>
       <c r="Y19" s="59" t="n">
         <v>532838.6</v>
@@ -7494,7 +4606,7 @@
       <c r="AC19" s="60" t="n">
         <v>153000</v>
       </c>
-      <c r="AD19" s="121" t="n">
+      <c r="AD19" s="60" t="n">
         <v>102000</v>
       </c>
       <c r="AE19" s="60" t="n">
@@ -7880,17 +4992,17 @@
       </c>
       <c r="N21" s="36" t="n"/>
       <c r="O21" s="59" t="n">
-        <v>1042081.915</v>
+        <v>2084163.83</v>
       </c>
       <c r="P21" s="59" t="n"/>
       <c r="Q21" s="36" t="n"/>
       <c r="R21" s="36" t="n"/>
-      <c r="S21" s="36" t="n"/>
+      <c r="S21" s="36" t="n">
+        <v>2084163.83</v>
+      </c>
       <c r="T21" s="36" t="n"/>
       <c r="U21" s="36" t="n"/>
-      <c r="V21" s="36" t="n">
-        <v>1042081.915</v>
-      </c>
+      <c r="V21" s="36" t="n"/>
       <c r="W21" s="36" t="n"/>
       <c r="X21" s="36" t="n"/>
       <c r="Y21" s="59" t="n">
@@ -7932,7 +5044,7 @@
       <c r="AK21" s="60" t="n">
         <v>161700</v>
       </c>
-      <c r="AL21" s="186" t="n">
+      <c r="AL21" s="60" t="n">
         <v>1189753.83</v>
       </c>
       <c r="AM21" s="59" t="n"/>
@@ -8088,14 +5200,14 @@
       </c>
       <c r="N22" s="36" t="n"/>
       <c r="O22" s="59" t="n">
-        <v>99660</v>
+        <v>199320</v>
       </c>
       <c r="P22" s="59" t="n"/>
       <c r="Q22" s="36" t="n"/>
-      <c r="R22" s="36" t="n">
-        <v>99660</v>
-      </c>
-      <c r="S22" s="36" t="n"/>
+      <c r="R22" s="36" t="n"/>
+      <c r="S22" s="36" t="n">
+        <v>199320</v>
+      </c>
       <c r="T22" s="36" t="n"/>
       <c r="U22" s="36" t="n"/>
       <c r="V22" s="36" t="n"/>
@@ -8296,14 +5408,14 @@
       </c>
       <c r="N23" s="36" t="n"/>
       <c r="O23" s="59" t="n">
-        <v>145558.885</v>
+        <v>1455588.85</v>
       </c>
       <c r="P23" s="59" t="n"/>
       <c r="Q23" s="36" t="n"/>
-      <c r="R23" s="36" t="n">
-        <v>145558.885</v>
-      </c>
-      <c r="S23" s="36" t="n"/>
+      <c r="R23" s="36" t="n"/>
+      <c r="S23" s="36" t="n">
+        <v>1455588.85</v>
+      </c>
       <c r="T23" s="36" t="n"/>
       <c r="U23" s="36" t="n"/>
       <c r="V23" s="36" t="n"/>
@@ -8327,10 +5439,10 @@
       <c r="AD23" s="60" t="n">
         <v>425000</v>
       </c>
-      <c r="AE23" s="123" t="n">
+      <c r="AE23" s="60" t="n">
         <v>677500</v>
       </c>
-      <c r="AF23" s="187" t="n">
+      <c r="AF23" s="60" t="n">
         <v>353088.85</v>
       </c>
       <c r="AG23" s="59" t="n">
@@ -8503,15 +5615,11 @@
         </is>
       </c>
       <c r="N24" s="36" t="n"/>
-      <c r="O24" s="59" t="n">
-        <v>202942.465</v>
-      </c>
+      <c r="O24" s="59" t="n"/>
       <c r="P24" s="59" t="n"/>
       <c r="Q24" s="36" t="n"/>
       <c r="R24" s="36" t="n"/>
-      <c r="S24" s="36" t="n">
-        <v>202942.465</v>
-      </c>
+      <c r="S24" s="36" t="n"/>
       <c r="T24" s="36" t="n"/>
       <c r="U24" s="36" t="n"/>
       <c r="V24" s="36" t="n"/>
@@ -8541,7 +5649,7 @@
       <c r="AF24" s="60" t="n">
         <v>123984</v>
       </c>
-      <c r="AG24" s="124" t="n">
+      <c r="AG24" s="60" t="n">
         <v>146076</v>
       </c>
       <c r="AH24" s="60" t="n">
@@ -8710,14 +5818,14 @@
       </c>
       <c r="N25" s="36" t="n"/>
       <c r="O25" s="59" t="n">
-        <v>140032.483</v>
+        <v>1400324.83</v>
       </c>
       <c r="P25" s="59" t="n"/>
       <c r="Q25" s="36" t="n"/>
-      <c r="R25" s="36" t="n">
-        <v>140032.483</v>
-      </c>
-      <c r="S25" s="36" t="n"/>
+      <c r="R25" s="36" t="n"/>
+      <c r="S25" s="36" t="n">
+        <v>1400324.83</v>
+      </c>
       <c r="T25" s="36" t="n"/>
       <c r="U25" s="36" t="n"/>
       <c r="V25" s="36" t="n"/>
@@ -8738,10 +5846,10 @@
       <c r="AC25" s="60" t="n">
         <v>131079</v>
       </c>
-      <c r="AD25" s="125" t="n">
+      <c r="AD25" s="60" t="n">
         <v>759437.4</v>
       </c>
-      <c r="AE25" s="188" t="n">
+      <c r="AE25" s="60" t="n">
         <v>509808.43</v>
       </c>
       <c r="AF25" s="59" t="n">
@@ -9126,12 +6234,12 @@
       </c>
       <c r="N27" s="36" t="n"/>
       <c r="O27" s="59" t="n">
-        <v>36209.96400000001</v>
+        <v>362099.64</v>
       </c>
       <c r="P27" s="59" t="n"/>
       <c r="Q27" s="36" t="n"/>
       <c r="R27" s="36" t="n">
-        <v>36209.96400000001</v>
+        <v>362099.64</v>
       </c>
       <c r="S27" s="36" t="n"/>
       <c r="T27" s="36" t="n"/>
@@ -9151,10 +6259,10 @@
       <c r="AB27" s="60" t="n">
         <v>83200</v>
       </c>
-      <c r="AC27" s="126" t="n">
+      <c r="AC27" s="60" t="n">
         <v>98700</v>
       </c>
-      <c r="AD27" s="189" t="n">
+      <c r="AD27" s="60" t="n">
         <v>98299.64</v>
       </c>
       <c r="AE27" s="59" t="n">
@@ -9538,18 +6646,18 @@
       </c>
       <c r="N29" s="36" t="n"/>
       <c r="O29" s="59" t="n">
-        <v>224559.3</v>
+        <v>449118.6</v>
       </c>
       <c r="P29" s="59" t="n"/>
       <c r="Q29" s="36" t="n"/>
-      <c r="R29" s="36" t="n">
-        <v>224559.3</v>
-      </c>
+      <c r="R29" s="36" t="n"/>
       <c r="S29" s="36" t="n"/>
       <c r="T29" s="36" t="n"/>
       <c r="U29" s="36" t="n"/>
       <c r="V29" s="36" t="n"/>
-      <c r="W29" s="36" t="n"/>
+      <c r="W29" s="36" t="n">
+        <v>449118.6</v>
+      </c>
       <c r="X29" s="36" t="n"/>
       <c r="Y29" s="59" t="n">
         <v>993438.6</v>
@@ -9575,7 +6683,7 @@
       <c r="AF29" s="60" t="n">
         <v>101880</v>
       </c>
-      <c r="AG29" s="127" t="n">
+      <c r="AG29" s="60" t="n">
         <v>245358.6</v>
       </c>
       <c r="AH29" s="59" t="n">
@@ -9746,12 +6854,12 @@
       </c>
       <c r="N30" s="36" t="n"/>
       <c r="O30" s="59" t="n">
-        <v>22203.3</v>
+        <v>222033</v>
       </c>
       <c r="P30" s="59" t="n"/>
       <c r="Q30" s="36" t="n"/>
       <c r="R30" s="36" t="n">
-        <v>22203.3</v>
+        <v>222033</v>
       </c>
       <c r="S30" s="36" t="n"/>
       <c r="T30" s="36" t="n"/>
@@ -9768,7 +6876,7 @@
       <c r="AA30" s="60" t="n">
         <v>97340</v>
       </c>
-      <c r="AB30" s="190" t="n">
+      <c r="AB30" s="60" t="n">
         <v>124693</v>
       </c>
       <c r="AC30" s="59" t="n">
@@ -10367,15 +7475,11 @@
         </is>
       </c>
       <c r="N33" s="36" t="n"/>
-      <c r="O33" s="59" t="n">
-        <v>14625</v>
-      </c>
+      <c r="O33" s="59" t="n"/>
       <c r="P33" s="59" t="n"/>
       <c r="Q33" s="36" t="n"/>
       <c r="R33" s="36" t="n"/>
-      <c r="S33" s="36" t="n">
-        <v>14625</v>
-      </c>
+      <c r="S33" s="36" t="n"/>
       <c r="T33" s="36" t="n"/>
       <c r="U33" s="36" t="n"/>
       <c r="V33" s="36" t="n"/>
@@ -10393,7 +7497,7 @@
       <c r="AB33" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AC33" s="129" t="n">
+      <c r="AC33" s="60" t="n">
         <v>9750</v>
       </c>
       <c r="AD33" s="60" t="n">
@@ -11200,12 +8304,12 @@
       </c>
       <c r="N37" s="36" t="n"/>
       <c r="O37" s="59" t="n">
-        <v>25150</v>
+        <v>251500</v>
       </c>
       <c r="P37" s="59" t="n"/>
       <c r="Q37" s="36" t="n"/>
       <c r="R37" s="36" t="n">
-        <v>25150</v>
+        <v>251500</v>
       </c>
       <c r="S37" s="36" t="n"/>
       <c r="T37" s="36" t="n"/>
@@ -11216,10 +8320,10 @@
       <c r="Y37" s="59" t="n">
         <v>251500</v>
       </c>
-      <c r="Z37" s="130" t="n">
+      <c r="Z37" s="60" t="n">
         <v>162500</v>
       </c>
-      <c r="AA37" s="191" t="n">
+      <c r="AA37" s="60" t="n">
         <v>89000</v>
       </c>
       <c r="AB37" s="59" t="n">
@@ -11408,15 +8512,15 @@
       </c>
       <c r="N38" s="36" t="n"/>
       <c r="O38" s="59" t="n">
-        <v>36000</v>
+        <v>72000</v>
       </c>
       <c r="P38" s="59" t="n"/>
       <c r="Q38" s="36" t="n"/>
-      <c r="R38" s="36" t="n">
-        <v>36000</v>
-      </c>
+      <c r="R38" s="36" t="n"/>
       <c r="S38" s="36" t="n"/>
-      <c r="T38" s="36" t="n"/>
+      <c r="T38" s="36" t="n">
+        <v>72000</v>
+      </c>
       <c r="U38" s="36" t="n"/>
       <c r="V38" s="36" t="n"/>
       <c r="W38" s="36" t="n"/>
@@ -11436,7 +8540,7 @@
       <c r="AC38" s="60" t="n">
         <v>24000</v>
       </c>
-      <c r="AD38" s="131" t="n">
+      <c r="AD38" s="60" t="n">
         <v>48000</v>
       </c>
       <c r="AE38" s="59" t="n">
@@ -11616,12 +8720,12 @@
       </c>
       <c r="N39" s="36" t="n"/>
       <c r="O39" s="59" t="n">
-        <v>100597.184</v>
+        <v>1005971.84</v>
       </c>
       <c r="P39" s="59" t="n"/>
       <c r="Q39" s="36" t="n"/>
       <c r="R39" s="36" t="n">
-        <v>100597.184</v>
+        <v>1005971.84</v>
       </c>
       <c r="S39" s="36" t="n"/>
       <c r="T39" s="36" t="n"/>
@@ -11650,7 +8754,7 @@
       <c r="AE39" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AF39" s="192" t="n">
+      <c r="AF39" s="60" t="n">
         <v>1002000</v>
       </c>
       <c r="AG39" s="60" t="n">
@@ -12030,12 +9134,12 @@
       </c>
       <c r="N41" s="36" t="n"/>
       <c r="O41" s="59" t="n">
-        <v>12539.619</v>
+        <v>125396.19</v>
       </c>
       <c r="P41" s="59" t="n"/>
       <c r="Q41" s="36" t="n"/>
       <c r="R41" s="36" t="n">
-        <v>12539.619</v>
+        <v>125396.19</v>
       </c>
       <c r="S41" s="36" t="n"/>
       <c r="T41" s="36" t="n"/>
@@ -12055,7 +9159,7 @@
       <c r="AB41" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AC41" s="193" t="n">
+      <c r="AC41" s="60" t="n">
         <v>125396.19</v>
       </c>
       <c r="AD41" s="59" t="n">
@@ -12238,12 +9342,12 @@
       </c>
       <c r="N42" s="36" t="n"/>
       <c r="O42" s="59" t="n">
-        <v>72914.89599999999</v>
+        <v>729148.96</v>
       </c>
       <c r="P42" s="59" t="n"/>
       <c r="Q42" s="36" t="n"/>
       <c r="R42" s="36" t="n">
-        <v>72914.89599999999</v>
+        <v>729148.96</v>
       </c>
       <c r="S42" s="36" t="n"/>
       <c r="T42" s="36" t="n"/>
@@ -12257,7 +9361,7 @@
       <c r="Z42" s="59" t="n">
         <v>431000</v>
       </c>
-      <c r="AA42" s="182" t="n">
+      <c r="AA42" s="60" t="n">
         <v>729148.96</v>
       </c>
       <c r="AB42" s="59" t="n">
@@ -12856,18 +9960,18 @@
       </c>
       <c r="N45" s="36" t="n"/>
       <c r="O45" s="59" t="n">
-        <v>212788.095</v>
+        <v>425576.19</v>
       </c>
       <c r="P45" s="59" t="n"/>
       <c r="Q45" s="36" t="n"/>
       <c r="R45" s="36" t="n"/>
-      <c r="S45" s="36" t="n">
-        <v>212788.095</v>
-      </c>
+      <c r="S45" s="36" t="n"/>
       <c r="T45" s="36" t="n"/>
       <c r="U45" s="36" t="n"/>
       <c r="V45" s="36" t="n"/>
-      <c r="W45" s="36" t="n"/>
+      <c r="W45" s="36" t="n">
+        <v>425576.19</v>
+      </c>
       <c r="X45" s="36" t="n"/>
       <c r="Y45" s="59" t="n">
         <v>544076.1899999999</v>
@@ -12884,7 +9988,7 @@
       <c r="AC45" s="60" t="n">
         <v>114600</v>
       </c>
-      <c r="AD45" s="194" t="n">
+      <c r="AD45" s="60" t="n">
         <v>217376.19</v>
       </c>
       <c r="AE45" s="59" t="n">
@@ -13064,15 +10168,15 @@
       </c>
       <c r="N46" s="36" t="n"/>
       <c r="O46" s="59" t="n">
-        <v>107838.555</v>
+        <v>215677.11</v>
       </c>
       <c r="P46" s="59" t="n"/>
       <c r="Q46" s="36" t="n"/>
       <c r="R46" s="36" t="n"/>
-      <c r="S46" s="36" t="n">
-        <v>107838.555</v>
-      </c>
-      <c r="T46" s="36" t="n"/>
+      <c r="S46" s="36" t="n"/>
+      <c r="T46" s="36" t="n">
+        <v>215677.11</v>
+      </c>
       <c r="U46" s="36" t="n"/>
       <c r="V46" s="36" t="n"/>
       <c r="W46" s="36" t="n"/>
@@ -13089,7 +10193,7 @@
       <c r="AB46" s="60" t="n">
         <v>107520</v>
       </c>
-      <c r="AC46" s="195" t="n">
+      <c r="AC46" s="60" t="n">
         <v>26880</v>
       </c>
       <c r="AD46" s="60" t="n">
@@ -13474,18 +10578,18 @@
       </c>
       <c r="N48" s="36" t="n"/>
       <c r="O48" s="59" t="n">
-        <v>7625</v>
+        <v>15250</v>
       </c>
       <c r="P48" s="59" t="n"/>
       <c r="Q48" s="36" t="n"/>
       <c r="R48" s="36" t="n"/>
-      <c r="S48" s="36" t="n">
-        <v>7625</v>
-      </c>
+      <c r="S48" s="36" t="n"/>
       <c r="T48" s="36" t="n"/>
       <c r="U48" s="36" t="n"/>
       <c r="V48" s="36" t="n"/>
-      <c r="W48" s="36" t="n"/>
+      <c r="W48" s="36" t="n">
+        <v>15250</v>
+      </c>
       <c r="X48" s="36" t="n"/>
       <c r="Y48" s="59" t="n">
         <v>15250</v>
@@ -13493,7 +10597,7 @@
       <c r="Z48" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AA48" s="135" t="n">
+      <c r="AA48" s="60" t="n">
         <v>15250</v>
       </c>
       <c r="AB48" s="59" t="n">
@@ -13883,15 +10987,11 @@
         </is>
       </c>
       <c r="N50" s="36" t="n"/>
-      <c r="O50" s="59" t="n">
-        <v>44327.295</v>
-      </c>
+      <c r="O50" s="59" t="n"/>
       <c r="P50" s="59" t="n"/>
       <c r="Q50" s="36" t="n"/>
       <c r="R50" s="36" t="n"/>
-      <c r="S50" s="36" t="n">
-        <v>44327.295</v>
-      </c>
+      <c r="S50" s="36" t="n"/>
       <c r="T50" s="36" t="n"/>
       <c r="U50" s="36" t="n"/>
       <c r="V50" s="36" t="n"/>
@@ -13912,7 +11012,7 @@
       <c r="AC50" s="60" t="n">
         <v>19650</v>
       </c>
-      <c r="AD50" s="196" t="n">
+      <c r="AD50" s="60" t="n">
         <v>18600</v>
       </c>
       <c r="AE50" s="59" t="n">
@@ -14300,13 +11400,13 @@
       </c>
       <c r="N52" s="36" t="n"/>
       <c r="O52" s="59" t="n">
-        <v>106973</v>
+        <v>213946</v>
       </c>
       <c r="P52" s="59" t="n"/>
       <c r="Q52" s="36" t="n"/>
       <c r="R52" s="36" t="n"/>
       <c r="S52" s="36" t="n">
-        <v>106973</v>
+        <v>213946</v>
       </c>
       <c r="T52" s="36" t="n"/>
       <c r="U52" s="36" t="n"/>
@@ -14334,7 +11434,7 @@
       <c r="AE52" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AF52" s="197" t="n">
+      <c r="AF52" s="60" t="n">
         <v>99072</v>
       </c>
       <c r="AG52" s="60" t="n">
@@ -14714,14 +11814,14 @@
       </c>
       <c r="N54" s="36" t="n"/>
       <c r="O54" s="59" t="n">
-        <v>53560</v>
+        <v>535600</v>
       </c>
       <c r="P54" s="59" t="n"/>
       <c r="Q54" s="36" t="n"/>
-      <c r="R54" s="36" t="n">
-        <v>53560</v>
-      </c>
-      <c r="S54" s="36" t="n"/>
+      <c r="R54" s="36" t="n"/>
+      <c r="S54" s="36" t="n">
+        <v>535600</v>
+      </c>
       <c r="T54" s="36" t="n"/>
       <c r="U54" s="36" t="n"/>
       <c r="V54" s="36" t="n"/>
@@ -14748,7 +11848,7 @@
       <c r="AE54" s="60" t="n">
         <v>32200</v>
       </c>
-      <c r="AF54" s="198" t="n">
+      <c r="AF54" s="60" t="n">
         <v>311200</v>
       </c>
       <c r="AG54" s="59" t="n">
@@ -14922,18 +12022,18 @@
       </c>
       <c r="N55" s="36" t="n"/>
       <c r="O55" s="59" t="n">
-        <v>89925</v>
+        <v>179850</v>
       </c>
       <c r="P55" s="59" t="n"/>
       <c r="Q55" s="36" t="n"/>
-      <c r="R55" s="36" t="n">
-        <v>89925</v>
-      </c>
+      <c r="R55" s="36" t="n"/>
       <c r="S55" s="36" t="n"/>
       <c r="T55" s="36" t="n"/>
       <c r="U55" s="36" t="n"/>
       <c r="V55" s="36" t="n"/>
-      <c r="W55" s="36" t="n"/>
+      <c r="W55" s="36" t="n">
+        <v>179850</v>
+      </c>
       <c r="X55" s="36" t="n"/>
       <c r="Y55" s="59" t="n">
         <v>257725</v>
@@ -14950,7 +12050,7 @@
       <c r="AC55" s="60" t="n">
         <v>41500</v>
       </c>
-      <c r="AD55" s="139" t="n">
+      <c r="AD55" s="60" t="n">
         <v>56850</v>
       </c>
       <c r="AE55" s="60" t="n">
@@ -15538,18 +12638,18 @@
       </c>
       <c r="N58" s="36" t="n"/>
       <c r="O58" s="59" t="n">
-        <v>59925</v>
+        <v>119850</v>
       </c>
       <c r="P58" s="59" t="n"/>
       <c r="Q58" s="36" t="n"/>
-      <c r="R58" s="36" t="n">
-        <v>59925</v>
-      </c>
+      <c r="R58" s="36" t="n"/>
       <c r="S58" s="36" t="n"/>
       <c r="T58" s="36" t="n"/>
       <c r="U58" s="36" t="n"/>
       <c r="V58" s="36" t="n"/>
-      <c r="W58" s="36" t="n"/>
+      <c r="W58" s="36" t="n">
+        <v>119850</v>
+      </c>
       <c r="X58" s="36" t="n"/>
       <c r="Y58" s="59" t="n">
         <v>143850</v>
@@ -15566,7 +12666,7 @@
       <c r="AC58" s="60" t="n">
         <v>24000</v>
       </c>
-      <c r="AD58" s="140" t="n">
+      <c r="AD58" s="60" t="n">
         <v>48000</v>
       </c>
       <c r="AE58" s="60" t="n">
@@ -15746,15 +12846,15 @@
       </c>
       <c r="N59" s="36" t="n"/>
       <c r="O59" s="59" t="n">
-        <v>14136.895</v>
+        <v>28273.79</v>
       </c>
       <c r="P59" s="59" t="n"/>
       <c r="Q59" s="36" t="n"/>
-      <c r="R59" s="36" t="n">
-        <v>14136.895</v>
-      </c>
+      <c r="R59" s="36" t="n"/>
       <c r="S59" s="36" t="n"/>
-      <c r="T59" s="36" t="n"/>
+      <c r="T59" s="36" t="n">
+        <v>28273.79</v>
+      </c>
       <c r="U59" s="36" t="n"/>
       <c r="V59" s="36" t="n"/>
       <c r="W59" s="36" t="n"/>
@@ -15780,7 +12880,7 @@
       <c r="AE59" s="60" t="n">
         <v>8000</v>
       </c>
-      <c r="AF59" s="199" t="n">
+      <c r="AF59" s="60" t="n">
         <v>20273.79</v>
       </c>
       <c r="AG59" s="59" t="n">
@@ -15954,12 +13054,12 @@
       </c>
       <c r="N60" s="36" t="n"/>
       <c r="O60" s="59" t="n">
-        <v>8382</v>
+        <v>16764</v>
       </c>
       <c r="P60" s="59" t="n"/>
       <c r="Q60" s="36" t="n"/>
       <c r="R60" s="36" t="n">
-        <v>8382</v>
+        <v>16764</v>
       </c>
       <c r="S60" s="36" t="n"/>
       <c r="T60" s="36" t="n"/>
@@ -15982,7 +13082,7 @@
       <c r="AC60" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AD60" s="135" t="n">
+      <c r="AD60" s="60" t="n">
         <v>16764</v>
       </c>
       <c r="AE60" s="59" t="n">
@@ -16162,14 +13262,14 @@
       </c>
       <c r="N61" s="36" t="n"/>
       <c r="O61" s="59" t="n">
-        <v>104584</v>
+        <v>209168</v>
       </c>
       <c r="P61" s="59" t="n"/>
       <c r="Q61" s="36" t="n"/>
-      <c r="R61" s="36" t="n">
-        <v>104584</v>
-      </c>
-      <c r="S61" s="36" t="n"/>
+      <c r="R61" s="36" t="n"/>
+      <c r="S61" s="36" t="n">
+        <v>209168</v>
+      </c>
       <c r="T61" s="36" t="n"/>
       <c r="U61" s="36" t="n"/>
       <c r="V61" s="36" t="n"/>
@@ -16196,7 +13296,7 @@
       <c r="AE61" s="60" t="n">
         <v>46008</v>
       </c>
-      <c r="AF61" s="142" t="n">
+      <c r="AF61" s="60" t="n">
         <v>69012</v>
       </c>
       <c r="AG61" s="60" t="n">
@@ -16370,13 +13470,13 @@
       </c>
       <c r="N62" s="36" t="n"/>
       <c r="O62" s="59" t="n">
-        <v>890</v>
+        <v>1780</v>
       </c>
       <c r="P62" s="59" t="n"/>
       <c r="Q62" s="36" t="n"/>
       <c r="R62" s="36" t="n"/>
       <c r="S62" s="36" t="n">
-        <v>890</v>
+        <v>1780</v>
       </c>
       <c r="T62" s="36" t="n"/>
       <c r="U62" s="36" t="n"/>
@@ -16578,14 +13678,14 @@
       </c>
       <c r="N63" s="36" t="n"/>
       <c r="O63" s="59" t="n">
-        <v>30229.304</v>
+        <v>302293.04</v>
       </c>
       <c r="P63" s="59" t="n"/>
       <c r="Q63" s="36" t="n"/>
-      <c r="R63" s="36" t="n">
-        <v>30229.304</v>
-      </c>
-      <c r="S63" s="36" t="n"/>
+      <c r="R63" s="36" t="n"/>
+      <c r="S63" s="36" t="n">
+        <v>302293.04</v>
+      </c>
       <c r="T63" s="36" t="n"/>
       <c r="U63" s="36" t="n"/>
       <c r="V63" s="36" t="n"/>
@@ -16609,7 +13709,7 @@
       <c r="AD63" s="60" t="n">
         <v>22440</v>
       </c>
-      <c r="AE63" s="200" t="n">
+      <c r="AE63" s="60" t="n">
         <v>186253.04</v>
       </c>
       <c r="AF63" s="59" t="n">
@@ -16990,18 +14090,18 @@
       </c>
       <c r="N65" s="36" t="n"/>
       <c r="O65" s="59" t="n">
-        <v>105206.25</v>
+        <v>210412.5</v>
       </c>
       <c r="P65" s="59" t="n"/>
       <c r="Q65" s="36" t="n"/>
       <c r="R65" s="36" t="n"/>
-      <c r="S65" s="36" t="n">
-        <v>105206.25</v>
-      </c>
+      <c r="S65" s="36" t="n"/>
       <c r="T65" s="36" t="n"/>
       <c r="U65" s="36" t="n"/>
       <c r="V65" s="36" t="n"/>
-      <c r="W65" s="36" t="n"/>
+      <c r="W65" s="36" t="n">
+        <v>210412.5</v>
+      </c>
       <c r="X65" s="36" t="n"/>
       <c r="Y65" s="59" t="n">
         <v>298657.5</v>
@@ -17021,7 +14121,7 @@
       <c r="AD65" s="60" t="n">
         <v>61560</v>
       </c>
-      <c r="AE65" s="144" t="n">
+      <c r="AE65" s="60" t="n">
         <v>143812.5</v>
       </c>
       <c r="AF65" s="59" t="n">
@@ -17197,15 +14297,11 @@
         </is>
       </c>
       <c r="N66" s="36" t="n"/>
-      <c r="O66" s="59" t="n">
-        <v>33390</v>
-      </c>
+      <c r="O66" s="59" t="n"/>
       <c r="P66" s="59" t="n"/>
       <c r="Q66" s="36" t="n"/>
       <c r="R66" s="36" t="n"/>
-      <c r="S66" s="36" t="n">
-        <v>33390</v>
-      </c>
+      <c r="S66" s="36" t="n"/>
       <c r="T66" s="36" t="n"/>
       <c r="U66" s="36" t="n"/>
       <c r="V66" s="36" t="n"/>
@@ -17229,7 +14325,7 @@
       <c r="AD66" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AE66" s="129" t="n">
+      <c r="AE66" s="60" t="n">
         <v>22260</v>
       </c>
       <c r="AF66" s="59" t="n">
@@ -17405,14 +14501,10 @@
         </is>
       </c>
       <c r="N67" s="36" t="n"/>
-      <c r="O67" s="59" t="n">
-        <v>111089.835</v>
-      </c>
+      <c r="O67" s="59" t="n"/>
       <c r="P67" s="59" t="n"/>
       <c r="Q67" s="36" t="n"/>
-      <c r="R67" s="36" t="n">
-        <v>111089.835</v>
-      </c>
+      <c r="R67" s="36" t="n"/>
       <c r="S67" s="36" t="n"/>
       <c r="T67" s="36" t="n"/>
       <c r="U67" s="36" t="n"/>
@@ -17437,7 +14529,7 @@
       <c r="AD67" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AE67" s="145" t="n">
+      <c r="AE67" s="60" t="n">
         <v>220000</v>
       </c>
       <c r="AF67" s="59" t="n">
@@ -17611,14 +14703,10 @@
         </is>
       </c>
       <c r="N68" s="36" t="n"/>
-      <c r="O68" s="59" t="n">
-        <v>16350</v>
-      </c>
+      <c r="O68" s="59" t="n"/>
       <c r="P68" s="59" t="n"/>
       <c r="Q68" s="36" t="n"/>
-      <c r="R68" s="36" t="n">
-        <v>16350</v>
-      </c>
+      <c r="R68" s="36" t="n"/>
       <c r="S68" s="36" t="n"/>
       <c r="T68" s="36" t="n"/>
       <c r="U68" s="36" t="n"/>
@@ -17637,7 +14725,7 @@
       <c r="AB68" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AC68" s="135" t="n">
+      <c r="AC68" s="60" t="n">
         <v>32700</v>
       </c>
       <c r="AD68" s="59" t="n">
@@ -18228,12 +15316,12 @@
       </c>
       <c r="N71" s="36" t="n"/>
       <c r="O71" s="59" t="n">
-        <v>13238.419</v>
+        <v>132384.19</v>
       </c>
       <c r="P71" s="59" t="n"/>
       <c r="Q71" s="36" t="n"/>
       <c r="R71" s="36" t="n">
-        <v>13238.419</v>
+        <v>132384.19</v>
       </c>
       <c r="S71" s="36" t="n"/>
       <c r="T71" s="36" t="n"/>
@@ -18256,7 +15344,7 @@
       <c r="AC71" s="59" t="n">
         <v>67075</v>
       </c>
-      <c r="AD71" s="201" t="n">
+      <c r="AD71" s="60" t="n">
         <v>131160</v>
       </c>
       <c r="AE71" s="60" t="n">
@@ -18433,14 +15521,10 @@
         </is>
       </c>
       <c r="N72" s="36" t="n"/>
-      <c r="O72" s="59" t="n">
-        <v>38400</v>
-      </c>
+      <c r="O72" s="59" t="n"/>
       <c r="P72" s="59" t="n"/>
       <c r="Q72" s="36" t="n"/>
-      <c r="R72" s="36" t="n">
-        <v>38400</v>
-      </c>
+      <c r="R72" s="36" t="n"/>
       <c r="S72" s="36" t="n"/>
       <c r="T72" s="36" t="n"/>
       <c r="U72" s="36" t="n"/>
@@ -18468,7 +15552,7 @@
       <c r="AE72" s="60" t="n">
         <v>22400</v>
       </c>
-      <c r="AF72" s="147" t="n">
+      <c r="AF72" s="60" t="n">
         <v>54400</v>
       </c>
       <c r="AG72" s="59" t="n">
@@ -19262,14 +16346,14 @@
       </c>
       <c r="N76" s="36" t="n"/>
       <c r="O76" s="59" t="n">
-        <v>98890.86500000001</v>
+        <v>197781.73</v>
       </c>
       <c r="P76" s="59" t="n"/>
       <c r="Q76" s="36" t="n"/>
-      <c r="R76" s="36" t="n">
-        <v>98890.86500000001</v>
-      </c>
-      <c r="S76" s="36" t="n"/>
+      <c r="R76" s="36" t="n"/>
+      <c r="S76" s="36" t="n">
+        <v>197781.73</v>
+      </c>
       <c r="T76" s="36" t="n"/>
       <c r="U76" s="36" t="n"/>
       <c r="V76" s="36" t="n"/>
@@ -19290,7 +16374,7 @@
       <c r="AC76" s="60" t="n">
         <v>33610</v>
       </c>
-      <c r="AD76" s="202" t="n">
+      <c r="AD76" s="60" t="n">
         <v>164171.73</v>
       </c>
       <c r="AE76" s="59" t="n">
@@ -19469,14 +16553,10 @@
         </is>
       </c>
       <c r="N77" s="36" t="n"/>
-      <c r="O77" s="59" t="n">
-        <v>62566.45</v>
-      </c>
+      <c r="O77" s="59" t="n"/>
       <c r="P77" s="59" t="n"/>
       <c r="Q77" s="36" t="n"/>
-      <c r="R77" s="36" t="n">
-        <v>62566.45</v>
-      </c>
+      <c r="R77" s="36" t="n"/>
       <c r="S77" s="36" t="n"/>
       <c r="T77" s="36" t="n"/>
       <c r="U77" s="36" t="n"/>
@@ -19498,7 +16578,7 @@
       <c r="AC77" s="59" t="n">
         <v>59765</v>
       </c>
-      <c r="AD77" s="149" t="n">
+      <c r="AD77" s="60" t="n">
         <v>78445</v>
       </c>
       <c r="AE77" s="60" t="n">
@@ -19682,7 +16762,7 @@
       </c>
       <c r="N78" s="36" t="n"/>
       <c r="O78" s="59" t="n">
-        <v>557610.04</v>
+        <v>1115220.08</v>
       </c>
       <c r="P78" s="59" t="n"/>
       <c r="Q78" s="36" t="n"/>
@@ -19690,7 +16770,7 @@
       <c r="S78" s="36" t="n"/>
       <c r="T78" s="36" t="n"/>
       <c r="U78" s="36" t="n">
-        <v>557610.04</v>
+        <v>1115220.08</v>
       </c>
       <c r="V78" s="36" t="n"/>
       <c r="W78" s="36" t="n"/>
@@ -19710,7 +16790,7 @@
       <c r="AC78" s="60" t="n">
         <v>264476</v>
       </c>
-      <c r="AD78" s="150" t="n">
+      <c r="AD78" s="60" t="n">
         <v>459755</v>
       </c>
       <c r="AE78" s="60" t="n">
@@ -20298,12 +17378,12 @@
       </c>
       <c r="N81" s="36" t="n"/>
       <c r="O81" s="59" t="n">
-        <v>2409.5</v>
+        <v>24095</v>
       </c>
       <c r="P81" s="59" t="n"/>
       <c r="Q81" s="36" t="n"/>
       <c r="R81" s="36" t="n">
-        <v>2409.5</v>
+        <v>24095</v>
       </c>
       <c r="S81" s="36" t="n"/>
       <c r="T81" s="36" t="n"/>
@@ -20341,10 +17421,10 @@
       <c r="AH81" s="60" t="n">
         <v>2925</v>
       </c>
-      <c r="AI81" s="151" t="n">
+      <c r="AI81" s="60" t="n">
         <v>7605</v>
       </c>
-      <c r="AJ81" s="203" t="n">
+      <c r="AJ81" s="60" t="n">
         <v>7130</v>
       </c>
       <c r="AK81" s="59" t="n">
@@ -20505,14 +17585,10 @@
         </is>
       </c>
       <c r="N82" s="36" t="n"/>
-      <c r="O82" s="59" t="n">
-        <v>58769.295</v>
-      </c>
+      <c r="O82" s="59" t="n"/>
       <c r="P82" s="59" t="n"/>
       <c r="Q82" s="36" t="n"/>
-      <c r="R82" s="36" t="n">
-        <v>58769.295</v>
-      </c>
+      <c r="R82" s="36" t="n"/>
       <c r="S82" s="36" t="n"/>
       <c r="T82" s="36" t="n"/>
       <c r="U82" s="36" t="n"/>
@@ -20540,7 +17616,7 @@
       <c r="AE82" s="59" t="n">
         <v>4420</v>
       </c>
-      <c r="AF82" s="152" t="n">
+      <c r="AF82" s="60" t="n">
         <v>78400</v>
       </c>
       <c r="AG82" s="60" t="n">
@@ -20713,14 +17789,10 @@
         </is>
       </c>
       <c r="N83" s="36" t="n"/>
-      <c r="O83" s="59" t="n">
-        <v>21575</v>
-      </c>
+      <c r="O83" s="59" t="n"/>
       <c r="P83" s="59" t="n"/>
       <c r="Q83" s="36" t="n"/>
-      <c r="R83" s="36" t="n">
-        <v>21575</v>
-      </c>
+      <c r="R83" s="36" t="n"/>
       <c r="S83" s="36" t="n"/>
       <c r="T83" s="36" t="n"/>
       <c r="U83" s="36" t="n"/>
@@ -20754,7 +17826,7 @@
       <c r="AG83" s="60" t="n">
         <v>2800</v>
       </c>
-      <c r="AH83" s="153" t="n">
+      <c r="AH83" s="60" t="n">
         <v>17210</v>
       </c>
       <c r="AI83" s="60" t="n">
@@ -20921,14 +17993,10 @@
         </is>
       </c>
       <c r="N84" s="36" t="n"/>
-      <c r="O84" s="59" t="n">
-        <v>24705</v>
-      </c>
+      <c r="O84" s="59" t="n"/>
       <c r="P84" s="59" t="n"/>
       <c r="Q84" s="36" t="n"/>
-      <c r="R84" s="36" t="n">
-        <v>24705</v>
-      </c>
+      <c r="R84" s="36" t="n"/>
       <c r="S84" s="36" t="n"/>
       <c r="T84" s="36" t="n"/>
       <c r="U84" s="36" t="n"/>
@@ -20947,7 +18015,7 @@
       <c r="AB84" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AC84" s="154" t="n">
+      <c r="AC84" s="60" t="n">
         <v>25000</v>
       </c>
       <c r="AD84" s="59" t="n">
@@ -21129,15 +18197,11 @@
         </is>
       </c>
       <c r="N85" s="36" t="n"/>
-      <c r="O85" s="59" t="n">
-        <v>22457.77</v>
-      </c>
+      <c r="O85" s="59" t="n"/>
       <c r="P85" s="59" t="n"/>
       <c r="Q85" s="36" t="n"/>
       <c r="R85" s="36" t="n"/>
-      <c r="S85" s="36" t="n">
-        <v>22457.77</v>
-      </c>
+      <c r="S85" s="36" t="n"/>
       <c r="T85" s="36" t="n"/>
       <c r="U85" s="36" t="n"/>
       <c r="V85" s="36" t="n"/>
@@ -21161,7 +18225,7 @@
       <c r="AD85" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AE85" s="204" t="n">
+      <c r="AE85" s="60" t="n">
         <v>29915.54</v>
       </c>
       <c r="AF85" s="59" t="n">
@@ -21337,15 +18401,11 @@
         </is>
       </c>
       <c r="N86" s="36" t="n"/>
-      <c r="O86" s="59" t="n">
-        <v>37578.43</v>
-      </c>
+      <c r="O86" s="59" t="n"/>
       <c r="P86" s="59" t="n"/>
       <c r="Q86" s="36" t="n"/>
       <c r="R86" s="36" t="n"/>
-      <c r="S86" s="36" t="n">
-        <v>37578.43</v>
-      </c>
+      <c r="S86" s="36" t="n"/>
       <c r="T86" s="36" t="n"/>
       <c r="U86" s="36" t="n"/>
       <c r="V86" s="36" t="n"/>
@@ -21372,7 +18432,7 @@
       <c r="AE86" s="59" t="n">
         <v>43940</v>
       </c>
-      <c r="AF86" s="156" t="n">
+      <c r="AF86" s="60" t="n">
         <v>41320</v>
       </c>
       <c r="AG86" s="60" t="n">
@@ -21545,15 +18605,11 @@
         </is>
       </c>
       <c r="N87" s="36" t="n"/>
-      <c r="O87" s="59" t="n">
-        <v>24500</v>
-      </c>
+      <c r="O87" s="59" t="n"/>
       <c r="P87" s="59" t="n"/>
       <c r="Q87" s="36" t="n"/>
       <c r="R87" s="36" t="n"/>
-      <c r="S87" s="36" t="n">
-        <v>24500</v>
-      </c>
+      <c r="S87" s="36" t="n"/>
       <c r="T87" s="36" t="n"/>
       <c r="U87" s="36" t="n"/>
       <c r="V87" s="36" t="n"/>
@@ -21583,7 +18639,7 @@
       <c r="AF87" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AG87" s="205" t="n">
+      <c r="AG87" s="60" t="n">
         <v>18500</v>
       </c>
       <c r="AH87" s="60" t="n">
@@ -21753,15 +18809,11 @@
         </is>
       </c>
       <c r="N88" s="36" t="n"/>
-      <c r="O88" s="59" t="n">
-        <v>46320</v>
-      </c>
+      <c r="O88" s="59" t="n"/>
       <c r="P88" s="59" t="n"/>
       <c r="Q88" s="36" t="n"/>
       <c r="R88" s="36" t="n"/>
-      <c r="S88" s="36" t="n">
-        <v>46320</v>
-      </c>
+      <c r="S88" s="36" t="n"/>
       <c r="T88" s="36" t="n"/>
       <c r="U88" s="36" t="n"/>
       <c r="V88" s="36" t="n"/>
@@ -21776,7 +18828,7 @@
       <c r="AA88" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AB88" s="158" t="n">
+      <c r="AB88" s="60" t="n">
         <v>47600</v>
       </c>
       <c r="AC88" s="60" t="n">
@@ -21961,15 +19013,11 @@
         </is>
       </c>
       <c r="N89" s="36" t="n"/>
-      <c r="O89" s="59" t="n">
-        <v>170042</v>
-      </c>
+      <c r="O89" s="59" t="n"/>
       <c r="P89" s="59" t="n"/>
       <c r="Q89" s="36" t="n"/>
       <c r="R89" s="36" t="n"/>
-      <c r="S89" s="36" t="n">
-        <v>170042</v>
-      </c>
+      <c r="S89" s="36" t="n"/>
       <c r="T89" s="36" t="n"/>
       <c r="U89" s="36" t="n"/>
       <c r="V89" s="36" t="n"/>
@@ -21996,7 +19044,7 @@
       <c r="AE89" s="60" t="n">
         <v>54890</v>
       </c>
-      <c r="AF89" s="159" t="n">
+      <c r="AF89" s="60" t="n">
         <v>157137</v>
       </c>
       <c r="AG89" s="60" t="n">
@@ -22170,13 +19218,13 @@
       </c>
       <c r="N90" s="36" t="n"/>
       <c r="O90" s="59" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="P90" s="59" t="n"/>
       <c r="Q90" s="36" t="n"/>
       <c r="R90" s="36" t="n"/>
       <c r="S90" s="36" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="T90" s="36" t="n"/>
       <c r="U90" s="36" t="n"/>
@@ -22192,7 +19240,7 @@
       <c r="AA90" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AB90" s="135" t="n">
+      <c r="AB90" s="60" t="n">
         <v>600</v>
       </c>
       <c r="AC90" s="59" t="n">
@@ -22378,14 +19426,14 @@
       </c>
       <c r="N91" s="36" t="n"/>
       <c r="O91" s="59" t="n">
-        <v>16164.313</v>
+        <v>161643.13</v>
       </c>
       <c r="P91" s="59" t="n"/>
       <c r="Q91" s="36" t="n"/>
-      <c r="R91" s="36" t="n">
-        <v>16164.313</v>
-      </c>
-      <c r="S91" s="36" t="n"/>
+      <c r="R91" s="36" t="n"/>
+      <c r="S91" s="36" t="n">
+        <v>161643.13</v>
+      </c>
       <c r="T91" s="36" t="n"/>
       <c r="U91" s="36" t="n"/>
       <c r="V91" s="36" t="n"/>
@@ -22406,10 +19454,10 @@
       <c r="AC91" s="60" t="n">
         <v>17490</v>
       </c>
-      <c r="AD91" s="160" t="n">
+      <c r="AD91" s="60" t="n">
         <v>88800</v>
       </c>
-      <c r="AE91" s="206" t="n">
+      <c r="AE91" s="60" t="n">
         <v>55353.13</v>
       </c>
       <c r="AF91" s="59" t="n">
@@ -22585,15 +19633,11 @@
         </is>
       </c>
       <c r="N92" s="36" t="n"/>
-      <c r="O92" s="59" t="n">
-        <v>15000</v>
-      </c>
+      <c r="O92" s="59" t="n"/>
       <c r="P92" s="59" t="n"/>
       <c r="Q92" s="36" t="n"/>
       <c r="R92" s="36" t="n"/>
-      <c r="S92" s="36" t="n">
-        <v>15000</v>
-      </c>
+      <c r="S92" s="36" t="n"/>
       <c r="T92" s="36" t="n"/>
       <c r="U92" s="36" t="n"/>
       <c r="V92" s="36" t="n"/>
@@ -22620,7 +19664,7 @@
       <c r="AE92" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AF92" s="135" t="n">
+      <c r="AF92" s="60" t="n">
         <v>30000</v>
       </c>
       <c r="AG92" s="59" t="n">
@@ -22793,15 +19837,11 @@
         </is>
       </c>
       <c r="N93" s="36" t="n"/>
-      <c r="O93" s="59" t="n">
-        <v>22240</v>
-      </c>
+      <c r="O93" s="59" t="n"/>
       <c r="P93" s="59" t="n"/>
       <c r="Q93" s="36" t="n"/>
       <c r="R93" s="36" t="n"/>
-      <c r="S93" s="36" t="n">
-        <v>22240</v>
-      </c>
+      <c r="S93" s="36" t="n"/>
       <c r="T93" s="36" t="n"/>
       <c r="U93" s="36" t="n"/>
       <c r="V93" s="36" t="n"/>
@@ -22813,7 +19853,7 @@
       <c r="Z93" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AA93" s="135" t="n">
+      <c r="AA93" s="60" t="n">
         <v>44480</v>
       </c>
       <c r="AB93" s="59" t="n">
@@ -23002,14 +20042,14 @@
       </c>
       <c r="N94" s="36" t="n"/>
       <c r="O94" s="59" t="n">
-        <v>86446.655</v>
+        <v>864466.55</v>
       </c>
       <c r="P94" s="59" t="n"/>
       <c r="Q94" s="36" t="n"/>
-      <c r="R94" s="36" t="n">
-        <v>86446.655</v>
-      </c>
-      <c r="S94" s="36" t="n"/>
+      <c r="R94" s="36" t="n"/>
+      <c r="S94" s="36" t="n">
+        <v>864466.55</v>
+      </c>
       <c r="T94" s="36" t="n"/>
       <c r="U94" s="36" t="n"/>
       <c r="V94" s="36" t="n"/>
@@ -23033,10 +20073,10 @@
       <c r="AD94" s="60" t="n">
         <v>301750</v>
       </c>
-      <c r="AE94" s="161" t="n">
+      <c r="AE94" s="60" t="n">
         <v>417360</v>
       </c>
-      <c r="AF94" s="207" t="n">
+      <c r="AF94" s="60" t="n">
         <v>145356.55</v>
       </c>
       <c r="AG94" s="59" t="n">
@@ -23209,15 +20249,11 @@
         </is>
       </c>
       <c r="N95" s="36" t="n"/>
-      <c r="O95" s="59" t="n">
-        <v>48522.5</v>
-      </c>
+      <c r="O95" s="59" t="n"/>
       <c r="P95" s="59" t="n"/>
       <c r="Q95" s="36" t="n"/>
       <c r="R95" s="36" t="n"/>
-      <c r="S95" s="36" t="n">
-        <v>48522.5</v>
-      </c>
+      <c r="S95" s="36" t="n"/>
       <c r="T95" s="36" t="n"/>
       <c r="U95" s="36" t="n"/>
       <c r="V95" s="36" t="n"/>
@@ -23238,7 +20274,7 @@
       <c r="AC95" s="60" t="n">
         <v>41000</v>
       </c>
-      <c r="AD95" s="208" t="n">
+      <c r="AD95" s="60" t="n">
         <v>56045</v>
       </c>
       <c r="AE95" s="59" t="n">
@@ -23620,13 +20656,13 @@
       </c>
       <c r="N97" s="36" t="n"/>
       <c r="O97" s="59" t="n">
-        <v>4375</v>
+        <v>8750</v>
       </c>
       <c r="P97" s="59" t="n"/>
       <c r="Q97" s="36" t="n"/>
       <c r="R97" s="36" t="n"/>
       <c r="S97" s="36" t="n">
-        <v>4375</v>
+        <v>8750</v>
       </c>
       <c r="T97" s="36" t="n"/>
       <c r="U97" s="36" t="n"/>
@@ -23642,7 +20678,7 @@
       <c r="AA97" s="59" t="n">
         <v>8750</v>
       </c>
-      <c r="AB97" s="135" t="n">
+      <c r="AB97" s="60" t="n">
         <v>8750</v>
       </c>
       <c r="AC97" s="59" t="n">
@@ -24030,12 +21066,12 @@
       </c>
       <c r="N99" s="36" t="n"/>
       <c r="O99" s="59" t="n">
-        <v>315</v>
+        <v>630</v>
       </c>
       <c r="P99" s="59" t="n"/>
       <c r="Q99" s="36" t="n"/>
       <c r="R99" s="36" t="n">
-        <v>315</v>
+        <v>630</v>
       </c>
       <c r="S99" s="36" t="n"/>
       <c r="T99" s="36" t="n"/>
@@ -24058,7 +21094,7 @@
       <c r="AC99" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AD99" s="163" t="n">
+      <c r="AD99" s="60" t="n">
         <v>420</v>
       </c>
       <c r="AE99" s="60" t="n">
@@ -24238,14 +21274,14 @@
       </c>
       <c r="N100" s="36" t="n"/>
       <c r="O100" s="59" t="n">
-        <v>27550</v>
+        <v>55100</v>
       </c>
       <c r="P100" s="59" t="n"/>
       <c r="Q100" s="36" t="n"/>
-      <c r="R100" s="36" t="n">
-        <v>27550</v>
-      </c>
-      <c r="S100" s="36" t="n"/>
+      <c r="R100" s="36" t="n"/>
+      <c r="S100" s="36" t="n">
+        <v>55100</v>
+      </c>
       <c r="T100" s="36" t="n"/>
       <c r="U100" s="36" t="n"/>
       <c r="V100" s="36" t="n"/>
@@ -24266,7 +21302,7 @@
       <c r="AC100" s="60" t="n">
         <v>19000</v>
       </c>
-      <c r="AD100" s="209" t="n">
+      <c r="AD100" s="60" t="n">
         <v>19000</v>
       </c>
       <c r="AE100" s="59" t="n">
@@ -24647,15 +21683,11 @@
         </is>
       </c>
       <c r="N102" s="36" t="n"/>
-      <c r="O102" s="59" t="n">
-        <v>12936</v>
-      </c>
+      <c r="O102" s="59" t="n"/>
       <c r="P102" s="59" t="n"/>
       <c r="Q102" s="36" t="n"/>
       <c r="R102" s="36" t="n"/>
-      <c r="S102" s="36" t="n">
-        <v>12936</v>
-      </c>
+      <c r="S102" s="36" t="n"/>
       <c r="T102" s="36" t="n"/>
       <c r="U102" s="36" t="n"/>
       <c r="V102" s="36" t="n"/>
@@ -24676,7 +21708,7 @@
       <c r="AC102" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AD102" s="210" t="n">
+      <c r="AD102" s="60" t="n">
         <v>7360</v>
       </c>
       <c r="AE102" s="60" t="n">
@@ -24856,18 +21888,18 @@
       </c>
       <c r="N103" s="36" t="n"/>
       <c r="O103" s="59" t="n">
-        <v>593364.425</v>
+        <v>1186728.85</v>
       </c>
       <c r="P103" s="59" t="n"/>
       <c r="Q103" s="36" t="n"/>
-      <c r="R103" s="36" t="n">
-        <v>593364.425</v>
-      </c>
+      <c r="R103" s="36" t="n"/>
       <c r="S103" s="36" t="n"/>
       <c r="T103" s="36" t="n"/>
       <c r="U103" s="36" t="n"/>
       <c r="V103" s="36" t="n"/>
-      <c r="W103" s="36" t="n"/>
+      <c r="W103" s="36" t="n">
+        <v>1186728.85</v>
+      </c>
       <c r="X103" s="36" t="n"/>
       <c r="Y103" s="59" t="n">
         <v>2382359.5</v>
@@ -24890,7 +21922,7 @@
       <c r="AE103" s="60" t="n">
         <v>435132.65</v>
       </c>
-      <c r="AF103" s="166" t="n">
+      <c r="AF103" s="60" t="n">
         <v>355980</v>
       </c>
       <c r="AG103" s="60" t="n">
@@ -25063,15 +22095,11 @@
         </is>
       </c>
       <c r="N104" s="36" t="n"/>
-      <c r="O104" s="59" t="n">
-        <v>46757.14999999999</v>
-      </c>
+      <c r="O104" s="59" t="n"/>
       <c r="P104" s="59" t="n"/>
       <c r="Q104" s="36" t="n"/>
       <c r="R104" s="36" t="n"/>
-      <c r="S104" s="36" t="n">
-        <v>46757.14999999999</v>
-      </c>
+      <c r="S104" s="36" t="n"/>
       <c r="T104" s="36" t="n"/>
       <c r="U104" s="36" t="n"/>
       <c r="V104" s="36" t="n"/>
@@ -25092,7 +22120,7 @@
       <c r="AC104" s="59" t="n">
         <v>34500</v>
       </c>
-      <c r="AD104" s="167" t="n">
+      <c r="AD104" s="60" t="n">
         <v>63490</v>
       </c>
       <c r="AE104" s="60" t="n">
@@ -25271,15 +22299,11 @@
         </is>
       </c>
       <c r="N105" s="36" t="n"/>
-      <c r="O105" s="59" t="n">
-        <v>82900</v>
-      </c>
+      <c r="O105" s="59" t="n"/>
       <c r="P105" s="59" t="n"/>
       <c r="Q105" s="36" t="n"/>
       <c r="R105" s="36" t="n"/>
-      <c r="S105" s="36" t="n">
-        <v>82900</v>
-      </c>
+      <c r="S105" s="36" t="n"/>
       <c r="T105" s="36" t="n"/>
       <c r="U105" s="36" t="n"/>
       <c r="V105" s="36" t="n"/>
@@ -25306,7 +22330,7 @@
       <c r="AE105" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AF105" s="168" t="n">
+      <c r="AF105" s="60" t="n">
         <v>69400</v>
       </c>
       <c r="AG105" s="59" t="n">
@@ -25479,15 +22503,11 @@
         </is>
       </c>
       <c r="N106" s="36" t="n"/>
-      <c r="O106" s="59" t="n">
-        <v>17237.5</v>
-      </c>
+      <c r="O106" s="59" t="n"/>
       <c r="P106" s="59" t="n"/>
       <c r="Q106" s="36" t="n"/>
       <c r="R106" s="36" t="n"/>
-      <c r="S106" s="36" t="n">
-        <v>17237.5</v>
-      </c>
+      <c r="S106" s="36" t="n"/>
       <c r="T106" s="36" t="n"/>
       <c r="U106" s="36" t="n"/>
       <c r="V106" s="36" t="n"/>
@@ -25496,7 +22516,7 @@
       <c r="Y106" s="59" t="n">
         <v>34475</v>
       </c>
-      <c r="Z106" s="169" t="n">
+      <c r="Z106" s="60" t="n">
         <v>23300</v>
       </c>
       <c r="AA106" s="59" t="n">
@@ -25892,15 +22912,15 @@
       </c>
       <c r="N108" s="36" t="n"/>
       <c r="O108" s="59" t="n">
-        <v>41228.5</v>
+        <v>82457</v>
       </c>
       <c r="P108" s="59" t="n"/>
       <c r="Q108" s="36" t="n"/>
-      <c r="R108" s="36" t="n">
-        <v>41228.5</v>
-      </c>
+      <c r="R108" s="36" t="n"/>
       <c r="S108" s="36" t="n"/>
-      <c r="T108" s="36" t="n"/>
+      <c r="T108" s="36" t="n">
+        <v>82457</v>
+      </c>
       <c r="U108" s="36" t="n"/>
       <c r="V108" s="36" t="n"/>
       <c r="W108" s="36" t="n"/>
@@ -25926,7 +22946,7 @@
       <c r="AE108" s="60" t="n">
         <v>37200</v>
       </c>
-      <c r="AF108" s="211" t="n">
+      <c r="AF108" s="60" t="n">
         <v>27900</v>
       </c>
       <c r="AG108" s="60" t="n">
@@ -26097,15 +23117,11 @@
         </is>
       </c>
       <c r="N109" s="36" t="n"/>
-      <c r="O109" s="59" t="n">
-        <v>11233.425</v>
-      </c>
+      <c r="O109" s="59" t="n"/>
       <c r="P109" s="59" t="n"/>
       <c r="Q109" s="36" t="n"/>
       <c r="R109" s="36" t="n"/>
-      <c r="S109" s="36" t="n">
-        <v>11233.425</v>
-      </c>
+      <c r="S109" s="36" t="n"/>
       <c r="T109" s="36" t="n"/>
       <c r="U109" s="36" t="n"/>
       <c r="V109" s="36" t="n"/>
@@ -26117,7 +23133,7 @@
       <c r="Z109" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AA109" s="135" t="n">
+      <c r="AA109" s="60" t="n">
         <v>22466.85</v>
       </c>
       <c r="AB109" s="59" t="n">
@@ -26306,12 +23322,12 @@
       </c>
       <c r="N110" s="36" t="n"/>
       <c r="O110" s="59" t="n">
-        <v>1400</v>
+        <v>2800</v>
       </c>
       <c r="P110" s="59" t="n"/>
       <c r="Q110" s="36" t="n"/>
       <c r="R110" s="36" t="n">
-        <v>1400</v>
+        <v>2800</v>
       </c>
       <c r="S110" s="36" t="n"/>
       <c r="T110" s="36" t="n"/>
@@ -26334,7 +23350,7 @@
       <c r="AC110" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AD110" s="135" t="n">
+      <c r="AD110" s="60" t="n">
         <v>2800</v>
       </c>
       <c r="AE110" s="59" t="n">
@@ -26518,7 +23534,7 @@
       </c>
       <c r="N111" s="36" t="n"/>
       <c r="O111" s="59" t="n">
-        <v>29641.103</v>
+        <v>296411.03</v>
       </c>
       <c r="P111" s="59" t="n"/>
       <c r="Q111" s="36" t="n"/>
@@ -26527,7 +23543,7 @@
       <c r="T111" s="36" t="n"/>
       <c r="U111" s="36" t="n"/>
       <c r="V111" s="36" t="n">
-        <v>29641.103</v>
+        <v>296411.03</v>
       </c>
       <c r="W111" s="36" t="n"/>
       <c r="X111" s="36" t="n"/>
@@ -26549,7 +23565,7 @@
       <c r="AD111" s="59" t="n">
         <v>378694</v>
       </c>
-      <c r="AE111" s="182" t="n">
+      <c r="AE111" s="60" t="n">
         <v>296411.03</v>
       </c>
       <c r="AF111" s="59" t="n">
@@ -26725,15 +23741,11 @@
         </is>
       </c>
       <c r="N112" s="36" t="n"/>
-      <c r="O112" s="59" t="n">
-        <v>52302.745</v>
-      </c>
+      <c r="O112" s="59" t="n"/>
       <c r="P112" s="59" t="n"/>
       <c r="Q112" s="36" t="n"/>
       <c r="R112" s="36" t="n"/>
-      <c r="S112" s="36" t="n">
-        <v>52302.745</v>
-      </c>
+      <c r="S112" s="36" t="n"/>
       <c r="T112" s="36" t="n"/>
       <c r="U112" s="36" t="n"/>
       <c r="V112" s="36" t="n"/>
@@ -26754,7 +23766,7 @@
       <c r="AC112" s="60" t="n">
         <v>11850</v>
       </c>
-      <c r="AD112" s="171" t="n">
+      <c r="AD112" s="60" t="n">
         <v>39500</v>
       </c>
       <c r="AE112" s="60" t="n">
@@ -26933,15 +23945,11 @@
         </is>
       </c>
       <c r="N113" s="36" t="n"/>
-      <c r="O113" s="59" t="n">
-        <v>45056.05</v>
-      </c>
+      <c r="O113" s="59" t="n"/>
       <c r="P113" s="59" t="n"/>
       <c r="Q113" s="36" t="n"/>
       <c r="R113" s="36" t="n"/>
-      <c r="S113" s="36" t="n">
-        <v>45056.05</v>
-      </c>
+      <c r="S113" s="36" t="n"/>
       <c r="T113" s="36" t="n"/>
       <c r="U113" s="36" t="n"/>
       <c r="V113" s="36" t="n"/>
@@ -26956,7 +23964,7 @@
       <c r="AA113" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AB113" s="172" t="n">
+      <c r="AB113" s="60" t="n">
         <v>46500</v>
       </c>
       <c r="AC113" s="59" t="n">
@@ -27343,15 +24351,11 @@
         </is>
       </c>
       <c r="N115" s="36" t="n"/>
-      <c r="O115" s="59" t="n">
-        <v>44112.5</v>
-      </c>
+      <c r="O115" s="59" t="n"/>
       <c r="P115" s="59" t="n"/>
       <c r="Q115" s="36" t="n"/>
       <c r="R115" s="36" t="n"/>
-      <c r="S115" s="36" t="n">
-        <v>44112.5</v>
-      </c>
+      <c r="S115" s="36" t="n"/>
       <c r="T115" s="36" t="n"/>
       <c r="U115" s="36" t="n"/>
       <c r="V115" s="36" t="n"/>
@@ -27375,7 +24379,7 @@
       <c r="AD115" s="60" t="n">
         <v>3500</v>
       </c>
-      <c r="AE115" s="173" t="n">
+      <c r="AE115" s="60" t="n">
         <v>37875</v>
       </c>
       <c r="AF115" s="60" t="n">
@@ -27551,15 +24555,11 @@
         </is>
       </c>
       <c r="N116" s="36" t="n"/>
-      <c r="O116" s="59" t="n">
-        <v>49425</v>
-      </c>
+      <c r="O116" s="59" t="n"/>
       <c r="P116" s="59" t="n"/>
       <c r="Q116" s="36" t="n"/>
       <c r="R116" s="36" t="n"/>
-      <c r="S116" s="36" t="n">
-        <v>49425</v>
-      </c>
+      <c r="S116" s="36" t="n"/>
       <c r="T116" s="36" t="n"/>
       <c r="U116" s="36" t="n"/>
       <c r="V116" s="36" t="n"/>
@@ -27589,7 +24589,7 @@
       <c r="AF116" s="60" t="n">
         <v>19250</v>
       </c>
-      <c r="AG116" s="174" t="n">
+      <c r="AG116" s="60" t="n">
         <v>19250</v>
       </c>
       <c r="AH116" s="60" t="n">
@@ -27964,14 +24964,14 @@
       </c>
       <c r="N118" s="36" t="n"/>
       <c r="O118" s="59" t="n">
-        <v>144154.663</v>
+        <v>1441546.63</v>
       </c>
       <c r="P118" s="59" t="n"/>
       <c r="Q118" s="36" t="n"/>
-      <c r="R118" s="36" t="n">
-        <v>144154.663</v>
-      </c>
-      <c r="S118" s="36" t="n"/>
+      <c r="R118" s="36" t="n"/>
+      <c r="S118" s="36" t="n">
+        <v>1441546.63</v>
+      </c>
       <c r="T118" s="36" t="n"/>
       <c r="U118" s="36" t="n"/>
       <c r="V118" s="36" t="n"/>
@@ -27992,10 +24992,10 @@
       <c r="AC118" s="59" t="n">
         <v>488038.58</v>
       </c>
-      <c r="AD118" s="175" t="n">
+      <c r="AD118" s="60" t="n">
         <v>934926.42</v>
       </c>
-      <c r="AE118" s="212" t="n">
+      <c r="AE118" s="60" t="n">
         <v>412040</v>
       </c>
       <c r="AF118" s="60" t="n">
@@ -28172,13 +25172,13 @@
       </c>
       <c r="N119" s="36" t="n"/>
       <c r="O119" s="59" t="n">
-        <v>5792.5</v>
+        <v>11585</v>
       </c>
       <c r="P119" s="59" t="n"/>
       <c r="Q119" s="36" t="n"/>
       <c r="R119" s="36" t="n"/>
       <c r="S119" s="36" t="n">
-        <v>5792.5</v>
+        <v>11585</v>
       </c>
       <c r="T119" s="36" t="n"/>
       <c r="U119" s="36" t="n"/>
@@ -28197,7 +25197,7 @@
       <c r="AB119" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AC119" s="176" t="n">
+      <c r="AC119" s="60" t="n">
         <v>6000</v>
       </c>
       <c r="AD119" s="59" t="n">
@@ -28380,12 +25380,12 @@
       </c>
       <c r="N120" s="36" t="n"/>
       <c r="O120" s="59" t="n">
-        <v>3744</v>
+        <v>37440</v>
       </c>
       <c r="P120" s="59" t="n"/>
       <c r="Q120" s="36" t="n"/>
       <c r="R120" s="36" t="n">
-        <v>3744</v>
+        <v>37440</v>
       </c>
       <c r="S120" s="36" t="n"/>
       <c r="T120" s="36" t="n"/>
@@ -28399,7 +25399,7 @@
       <c r="Z120" s="59" t="n">
         <v>38160</v>
       </c>
-      <c r="AA120" s="182" t="n">
+      <c r="AA120" s="60" t="n">
         <v>37440</v>
       </c>
       <c r="AB120" s="59" t="n">
@@ -28791,15 +25791,11 @@
         </is>
       </c>
       <c r="N122" s="36" t="n"/>
-      <c r="O122" s="59" t="n">
-        <v>25625</v>
-      </c>
+      <c r="O122" s="59" t="n"/>
       <c r="P122" s="59" t="n"/>
       <c r="Q122" s="36" t="n"/>
       <c r="R122" s="36" t="n"/>
-      <c r="S122" s="36" t="n">
-        <v>25625</v>
-      </c>
+      <c r="S122" s="36" t="n"/>
       <c r="T122" s="36" t="n"/>
       <c r="U122" s="36" t="n"/>
       <c r="V122" s="36" t="n"/>
@@ -28832,7 +25828,7 @@
       <c r="AG122" s="60" t="n">
         <v>6500</v>
       </c>
-      <c r="AH122" s="213" t="n">
+      <c r="AH122" s="60" t="n">
         <v>6500</v>
       </c>
       <c r="AI122" s="60" t="n">
@@ -29206,15 +26202,15 @@
       </c>
       <c r="N124" s="36" t="n"/>
       <c r="O124" s="59" t="n">
-        <v>63818.75</v>
+        <v>127637.5</v>
       </c>
       <c r="P124" s="59" t="n"/>
       <c r="Q124" s="36" t="n"/>
-      <c r="R124" s="36" t="n">
-        <v>63818.75</v>
-      </c>
+      <c r="R124" s="36" t="n"/>
       <c r="S124" s="36" t="n"/>
-      <c r="T124" s="36" t="n"/>
+      <c r="T124" s="36" t="n">
+        <v>127637.5</v>
+      </c>
       <c r="U124" s="36" t="n"/>
       <c r="V124" s="36" t="n"/>
       <c r="W124" s="36" t="n"/>
@@ -29231,7 +26227,7 @@
       <c r="AB124" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AC124" s="214" t="n">
+      <c r="AC124" s="60" t="n">
         <v>54060</v>
       </c>
       <c r="AD124" s="60" t="n">
@@ -29413,15 +26409,11 @@
         </is>
       </c>
       <c r="N125" s="36" t="n"/>
-      <c r="O125" s="59" t="n">
-        <v>57907.035</v>
-      </c>
+      <c r="O125" s="59" t="n"/>
       <c r="P125" s="59" t="n"/>
       <c r="Q125" s="36" t="n"/>
       <c r="R125" s="36" t="n"/>
-      <c r="S125" s="36" t="n">
-        <v>57907.035</v>
-      </c>
+      <c r="S125" s="36" t="n"/>
       <c r="T125" s="36" t="n"/>
       <c r="U125" s="36" t="n"/>
       <c r="V125" s="36" t="n"/>
@@ -29439,7 +26431,7 @@
       <c r="AB125" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="AC125" s="179" t="n">
+      <c r="AC125" s="60" t="n">
         <v>58000</v>
       </c>
       <c r="AD125" s="60" t="n">
@@ -30235,15 +27227,11 @@
         </is>
       </c>
       <c r="N129" s="36" t="n"/>
-      <c r="O129" s="59" t="n">
-        <v>24445</v>
-      </c>
+      <c r="O129" s="59" t="n"/>
       <c r="P129" s="59" t="n"/>
       <c r="Q129" s="36" t="n"/>
       <c r="R129" s="36" t="n"/>
-      <c r="S129" s="36" t="n">
-        <v>24445</v>
-      </c>
+      <c r="S129" s="36" t="n"/>
       <c r="T129" s="36" t="n"/>
       <c r="U129" s="36" t="n"/>
       <c r="V129" s="36" t="n"/>
@@ -30270,7 +27258,7 @@
       <c r="AE129" s="60" t="n">
         <v>15540</v>
       </c>
-      <c r="AF129" s="180" t="n">
+      <c r="AF129" s="60" t="n">
         <v>33350</v>
       </c>
       <c r="AG129" s="59" t="n">
@@ -30852,14 +27840,14 @@
       </c>
       <c r="N132" s="36" t="n"/>
       <c r="O132" s="59" t="n">
-        <v>272449.2609999999</v>
+        <v>2724492.609999999</v>
       </c>
       <c r="P132" s="59" t="n"/>
       <c r="Q132" s="36" t="n"/>
-      <c r="R132" s="36" t="n">
-        <v>272449.2609999999</v>
-      </c>
-      <c r="S132" s="36" t="n"/>
+      <c r="R132" s="36" t="n"/>
+      <c r="S132" s="36" t="n">
+        <v>2724492.609999999</v>
+      </c>
       <c r="T132" s="36" t="n"/>
       <c r="U132" s="36" t="n"/>
       <c r="V132" s="36" t="n"/>
@@ -30883,10 +27871,10 @@
       <c r="AD132" s="59" t="n">
         <v>2553600</v>
       </c>
-      <c r="AE132" s="181" t="n">
+      <c r="AE132" s="60" t="n">
         <v>2019600</v>
       </c>
-      <c r="AF132" s="215" t="n">
+      <c r="AF132" s="60" t="n">
         <v>704892.6099999991</v>
       </c>
       <c r="AG132" s="59" t="n">
